--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1348,6 +1348,920 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Deepa B</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Senior Customer Onboarding Advisor</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>JP BHATT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ImpactQA</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jin Seon Baek</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ERP Manager</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>H Mart Companies, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Stefan Baeuerle</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SVP | Chief Product Officer, SAP HAN…</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Paul Baines</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Programme Direct…</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>YORK TELECOM LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Staci Baker</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PricewaterhouseCoopers LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Divya Balaji</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Value Advisor</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Alvar Baldarrama</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Procurement Consultant</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>State of Louisiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Christie Balestra</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Senior Ind…</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SAP America Inc. (Hudson Yards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Mithun Bangad</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sr Manager Finance IT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NRG Energy, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sahil Bansal</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Senior Manager</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tricopp LLC dba CloudPaths</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Paul Baraniuk</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Global Solution…</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Florida Crystals Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Horacio Barbosa</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Proce…</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Techint Cia Tecnica Internacional SACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Devraj Bardhan</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SAP AI Leader</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>IBM United Kingdom Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Paul Barrett</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Senior Manager, Channel Sa…</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SPS Commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Pam Barrowcliffe</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Product Marketing,…</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SAP Canada - Waterloo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Alejandro Basigalup</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Jefe de infraestructura corporativo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Grupo HZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Martin Bava</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>IT Bus…</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Techint Cia Tecnica Internacional SACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Lynn Bayer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Procurement…</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Securian Financial Group, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Justin Beachnau</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Senior Account Exe…</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Pittsburgh, SAP America</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Benjamin Beberness</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Business Architect</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Proquire LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Chris Becker</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Director, Finance Tr…</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Cintas Corporation No. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Andy Bell</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Head of Consulting</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>RESULTING LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Carrie Bennett</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SVP, Technology Deli…</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ascentium Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Marissa Bennett</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Director, Global People Solutio…</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PepsiCo, Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>James Benson</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Solutions Sales Executiv…</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Dan Berard</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>International Business Machines Corporation…</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ethan Berceli</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Director of Sales Engineer</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mediafly, Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Frederic Berg</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>VP SAP UI Technologies &amp; Mobile</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Nick Berg</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SVP Digital Platforms</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Softserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Elliot Berger</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Managing Partner, bp</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SAP UK Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kerry Jo Berger</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase Bank, NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Catalina Bernal</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Seller Partner Manager</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SAP CANADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Kori Betsalel</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Senior accountant executive</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SAP CANADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Pallav Bhatnagar</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sr. Director</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Nitin Bhide</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Regional Sales lead</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Incture LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Raja Sekhar Bhomadi</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Manager/Head of Dept</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Verizon Sourcing LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Marco Bickel</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Vice President IT Program Manage…</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bayer AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Amos Biegun</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Vistex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Alex Birle</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Senior Sales Development</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Confido</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Justin Bisesi</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Business A…</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>The Davey Tree Expert Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ron Blackburn</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EVP of Sales and GTM</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CloudPaths</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Eric Blondin</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Head of Business Te…</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SimpleFi Solutions, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Matt Blyth</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Vice President, Global Pr…</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sanjeev Bode</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>HCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Arndt-Alexander Boehnert</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Global VP CAS…</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Beverley Den Boestert</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Director - Technology…</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EY Global Services Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Kate Bollard</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Consulting Manager</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Collective Insights</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Raju Bolledla</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SAP Strategic Advisor</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SAP Australia Pty Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Jackson Borges</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>RVP Finance &amp; Spend</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SAP International Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Patrick Boruta</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Partner - Business Consultin…</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Grant Thornton</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Babs Bouchillon</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NA Tradeshows and Event Manager</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Serrala</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Megan Boulter</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Director of Strategic…</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>The Silicon Partners Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Kailen Boumal</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sr. Channel Manger</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ADP, Inc.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2262,6 +2262,929 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Art Boyd</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SVP Growth Partnerships</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mirakl</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Joanne Bradford</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Procurement Data &amp; Capability Manager</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>JLR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Holger Brammer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>VP AI Ecosystem</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Stephen Brandes</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Confido</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Chuck Bratton</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Vice President of Solutions</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>FPT USA CORP</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Gary Braunscheidel</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Chief Technology Offic…</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Baillie Lumber Co Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Adam Breiterman</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Maryland &amp; Virginia Milk Producers Cooperati…</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Oscar Brennan</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Global Head of Growth for Digital Appli…</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Atos</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Renee Brewer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Dir Finc Trans.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Carrier World Headquarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Tim Brewer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Technology Solutions Manager</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Corevist, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Paul Britter</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SAP Program Mana…</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Caterpillar Logistics, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Drew Brooks</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Chief Development Officer</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ergon</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Jean-F. Brossard</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Partner &amp; VP Business Development</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Ian Brown</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Field Risk Management</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Jay Brown</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ConsultingNetwork Business Solutions, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Jesse Brown</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sr Success Executive</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PartnerTap</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Michelle Brown</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Director Supply Chain</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Raytheon</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Mitch Brown</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>VP, North America</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Acuiti Labs</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Holger Bruchelt</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Eduardo Brunetti</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Value Advisor</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SAP Brasil Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Franklin Bruno</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Solution Advisor Manager -…</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SAP Brasil Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Renee Bruno</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>IT Manager</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Prime Conduit, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ann Bryant</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Director - Financi…</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Old Dominion Freight Line</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Patricia Buchholz</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Gl…</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SUSE Software Solutions Germany GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sneha Budhwani</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Senior Solution Archi…</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tricentis Americas, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Phillip Budidharma</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>IS Mana…</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Charlotte Pipe &amp; Foundry Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Mitchell Burkart</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Globalsource, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Alice Burrell</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Data Analytics Senior Manager</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>JLR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Eamonn Burton</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TPM</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Erin Buss</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Globalsource Information Technology III, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Tara Butler-Krgovic</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>VP, NA Experience and E…</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Shawn Byers</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>VP, Digital Product Marketing</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SAPinsider</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>YOUNA CHOI</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Assistant Manager</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>sunjin</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Juan Carlos Caballero</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>System Developer M…</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PAN AMERICAN GRAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Lisa Cabarcos</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>America's SAP Allianc…</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ernst &amp; Young U.S. LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Bobby Cain</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SVP &amp; CIO - North America</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Schneider Electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Elidan Calvo</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SAP Manager</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Align Technology Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Phil Cameron</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Growth Officer,…</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SAP NEW ZEALAND LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Stefan Camp Angell</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SAP P…</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Komatsu-Mitsui Maquinarias Perú S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Mariano Caniglia</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Industry Executive Advis…</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SAP Chile Limitada</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Amanda Cantu</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Schneider Electric USA, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Seila Carcavilla</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Innovation Manager</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>JLR</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Pat Carmody</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Senior Manag…</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Sharp Electronics Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Tyler Carr</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Sr. Capabilities Manag…</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Matias Romero Carranza</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Sales Solution Director</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Veritas Prime, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Sergio Carriero</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Bell Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Chrissy Caruso</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Client Engagement Manag…</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Veritas Prime, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Mariana Carvajal</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mobile App Lead</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Gabriele Casalena</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Aubay Italia S.p.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Sumner Case</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Syntax Systems Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Margarita Castillo</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Marketing Director</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Sam Castro</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Global Product Marketin…</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Vy Cates</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Director, HR PM/Produ…</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Phillips 66 Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>William Cdebaca</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Group operations Control…</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Fluor Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Donatella Cechet</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Chief Product Expert — Cloud ERP Fi…</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C163"/>
+  <dimension ref="A1:C218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3185,6 +3185,933 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Anirban Chatterjee Chatterjee</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SAP SLED Leader</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>IBM Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Karan Chauhan</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Life Sciences Solutions</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sanjay Chavan</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Head Enterpri…</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Abraham Cherian</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Director Security Govern…</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Kontoor Brands Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Venu Cherupillil</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Systems Engineer Sr Princi…</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Jeff Cheung</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SAP Platform Ow…</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Ionis Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Michelle Chew</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Sr. Project Coordinator</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Marine Atlantic Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Taiseer Chirakkal</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>International Business Machines Corporation…</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Karen Chirico</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Executive Director Enterprise Services</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>RTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Will Chisholm</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Southwest Airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Flora Choi</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Director, ERP…</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BioMarin Pharmaceutical, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>JongYun Choi</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BSG partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Parinda Choksi</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>CIO - Enablement</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Ball Horticultural Co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Sanjay Choubey</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Global Chief Digital an…</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Sylvamo Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Nicolas Christiaen Christiaen</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Dealside</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Saurabh Chug</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Solution Advisor</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Yoon Chung</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Solution Engineer Manager</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Douglas Ciolli</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>IT Principal Mana…</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Southern California Edison</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Tania Cirone-Fenyes</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Sr. Director Alliances</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>GyanSys, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Odércio Claro</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CIO</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Klabin SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Greg Clausing</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Director SAP COE</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>The Andersons, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Zach Clement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>American Equity Investment Li fe Insurance C…</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Michael Cobler</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Sr. Account Executive</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Cognitus Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Tim Coffey</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sr. AE</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Alinne Cogrossi</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Product Manager, ERP Procure to P…</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Arc'teryx</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Chad Cohen</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Client Engagement Manger</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Veritas Prime, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Allan Colaco</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>ERP Transfor…</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>HellermannTyton Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Colin Cole</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>JBS USA Food Company Holdings</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Clay Coleman</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Global Service Director, BPO</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Wipro Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Andrew Collins</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SVP ERP Transformation</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Kelli Collins</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>BlackJet Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Oisin Collins</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Mark Colosimo</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Director of Strategic Acc…</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>The Silicon Partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Tom Coltrain</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Dominion Energy, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Sean Comer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Senior Project…</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>TAMKO Building Products LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Meena Confait</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Global Business &amp; Engagem…</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Alex Connor</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Senior Develo…</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Lantech.com Coöperatie U.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Adam Conrad</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Bus Proc Architect</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Eileen Conway</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Global Head Strategic Partnerships</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Qualitest</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Julie Cooper</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Client Relationship Executive</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>BravoTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Michael Coppola</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>VP, Finance &amp; Treasury</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Ashland Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Juan Correa</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Sharp Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Manoel Costa</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Demo Solutions Expert</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SAP Brasil Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Sophie-Anne Cote</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Finance Director</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Barrette-Chapais</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Maryanne Coughlin</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Robert Coutu</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sr. Accoun…</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>System Design Analysis (SDA) inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Julie Craig</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Spon…</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SPARKS MARKETING (EMEA) LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Bill Cranston</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SAP Sales Director</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Techwave</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Keith Creech</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Director, Enterprise Sales</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SPS Commerce, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Philippe Cretier</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Head Finance and Spend Manage…</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Chris Crosby</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Founder | Managing Partner</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Adoptlab</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Ademar Crotti Junior</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Principal Technical Cons…</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>metaphacts GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Ken Crovetti</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Business Development Manager-…</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Vertex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Miguel Cruz</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Gerente de Calidad</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Michael Cugliari</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Senior Account Exec…</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>The Silicon Partners Inc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C218"/>
+  <dimension ref="A1:C228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3188,925 +3188,1095 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Anirban Chatterjee Chatterjee</t>
+          <t>Ekta Chadha</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SAP SLED Leader</t>
+          <t>Head of Cloud Delivery,…</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>IBM Corporation</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Karan Chauhan</t>
+          <t>Joydeep Chakraborty</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Life Sciences Solutions</t>
+          <t>Head of ECS CAA…</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SAP LABS INDIA PVT. LTD.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sanjay Chavan</t>
+          <t>Arun Chakravarthi</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Head Enterpri…</t>
+          <t>Enterprise Account M…</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Limited</t>
+          <t>Kaar Technologies Inc</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Abraham Cherian</t>
+          <t>Kamlesh Chalasani</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Director Security Govern…</t>
+          <t>Vice President, Manufacturing</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Kontoor Brands Inc</t>
+          <t>Tech Mahindra</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Venu Cherupillil</t>
+          <t>Greg Chamberland</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Systems Engineer Sr Princi…</t>
+          <t>IT, Enterprise…</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Ocean Spray Cranberries, Inc.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Jeff Cheung</t>
+          <t>Chris Chamberlin</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SAP Platform Ow…</t>
+          <t>Relationship Manager</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ionis Pharmaceuticals, Inc.</t>
+          <t>Moody's Corporation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Michelle Chew</t>
+          <t>Prasanna Chand</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Sr. Project Coordinator</t>
+          <t>Director - Enterprise Tech</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Marine Atlantic Inc.</t>
+          <t>Wayfair</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Taiseer Chirakkal</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
+          <t>Srinivasan Chandramohan</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation…</t>
+          <t>Cardinal Health Inc.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Karen Chirico</t>
+          <t>Matt Charleston</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Executive Director Enterprise Services</t>
+          <t>Sr Manager Fi…</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Performance Food Group, Inc.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Will Chisholm</t>
+          <t>Alexandra Charris</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Business Relationsh…</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>Softtek Renovation SAS</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Flora Choi</t>
+          <t>Anirban Chatterjee Chatterjee</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Director, ERP…</t>
+          <t>SAP SLED Leader</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BioMarin Pharmaceutical, Inc.</t>
+          <t>IBM Corporation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>JongYun Choi</t>
+          <t>Karan Chauhan</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Life Sciences Solutions</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BSG partners</t>
+          <t>Cognizant</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Parinda Choksi</t>
+          <t>Sanjay Chavan</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CIO - Enablement</t>
+          <t>Head Enterpri…</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ball Horticultural Co.</t>
+          <t>Mahindra &amp; Mahindra Limited</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sanjay Choubey</t>
+          <t>Abraham Cherian</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Global Chief Digital an…</t>
+          <t>Director Security Govern…</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sylvamo Corporation</t>
+          <t>Kontoor Brands Inc</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Nicolas Christiaen Christiaen</t>
+          <t>Venu Cherupillil</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Systems Engineer Sr Princi…</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Dealside</t>
+          <t>The Home Depot</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Saurabh Chug</t>
+          <t>Jeff Cheung</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Solution Advisor</t>
+          <t>SAP Platform Ow…</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Ionis Pharmaceuticals, Inc.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Yoon Chung</t>
+          <t>Michelle Chew</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Solution Engineer Manager</t>
+          <t>Sr. Project Coordinator</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Marine Atlantic Inc.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Douglas Ciolli</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>IT Principal Mana…</t>
-        </is>
-      </c>
+          <t>Taiseer Chirakkal</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Southern California Edison</t>
+          <t>International Business Machines Corporation…</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Tania Cirone-Fenyes</t>
+          <t>Karen Chirico</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Sr. Director Alliances</t>
+          <t>Executive Director Enterprise Services</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>GyanSys, Inc.</t>
+          <t>RTX</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Odércio Claro</t>
+          <t>Will Chisholm</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CIO</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Klabin SA</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Greg Clausing</t>
+          <t>Flora Choi</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Director SAP COE</t>
+          <t>Director, ERP…</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>The Andersons, Inc.</t>
+          <t>BioMarin Pharmaceutical, Inc.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Zach Clement</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr"/>
+          <t>JongYun Choi</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>American Equity Investment Li fe Insurance C…</t>
+          <t>BSG partners</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Michael Cobler</t>
+          <t>Parinda Choksi</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Sr. Account Executive</t>
+          <t>CIO - Enablement</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cognitus Ltd</t>
+          <t>Ball Horticultural Co.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Tim Coffey</t>
+          <t>Sanjay Choubey</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sr. AE</t>
+          <t>Global Chief Digital an…</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Sylvamo Corporation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Alinne Cogrossi</t>
+          <t>Nicolas Christiaen Christiaen</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Product Manager, ERP Procure to P…</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Arc'teryx</t>
+          <t>Dealside</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Chad Cohen</t>
+          <t>Saurabh Chug</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Client Engagement Manger</t>
+          <t>Solution Advisor</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Veritas Prime, LLC</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Allan Colaco</t>
+          <t>Yoon Chung</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ERP Transfor…</t>
+          <t>Solution Engineer Manager</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>HellermannTyton Corporation</t>
+          <t>Precisely</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Colin Cole</t>
+          <t>Douglas Ciolli</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>IT Principal Mana…</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>JBS USA Food Company Holdings</t>
+          <t>Southern California Edison</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Clay Coleman</t>
+          <t>Tania Cirone-Fenyes</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Global Service Director, BPO</t>
+          <t>Sr. Director Alliances</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Wipro Limited</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Andrew Collins</t>
+          <t>Odércio Claro</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SVP ERP Transformation</t>
+          <t>CIO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Klabin SA</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Kelli Collins</t>
+          <t>Greg Clausing</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Director SAP COE</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BlackJet Marketing</t>
+          <t>The Andersons, Inc.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Oisin Collins</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
+          <t>Zach Clement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Equity Investment Li fe Insurance C…</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Mark Colosimo</t>
+          <t>Michael Cobler</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Director of Strategic Acc…</t>
+          <t>Sr. Account Executive</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>The Silicon Partners</t>
+          <t>Cognitus Ltd</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Tom Coltrain</t>
+          <t>Tim Coffey</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Sr. AE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Dominion Energy, Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Sean Comer</t>
+          <t>Alinne Cogrossi</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Senior Project…</t>
+          <t>Product Manager, ERP Procure to P…</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TAMKO Building Products LLC</t>
+          <t>Arc'teryx</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Meena Confait</t>
+          <t>Chad Cohen</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Global Business &amp; Engagem…</t>
+          <t>Client Engagement Manger</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>Veritas Prime, LLC</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Alex Connor</t>
+          <t>Allan Colaco</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Senior Develo…</t>
+          <t>ERP Transfor…</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Lantech.com Coöperatie U.A.</t>
+          <t>HellermannTyton Corporation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Adam Conrad</t>
+          <t>Colin Cole</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Bus Proc Architect</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>JBS USA Food Company Holdings</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Eileen Conway</t>
+          <t>Clay Coleman</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Global Head Strategic Partnerships</t>
+          <t>Global Service Director, BPO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Wipro Limited</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Julie Cooper</t>
+          <t>Andrew Collins</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Client Relationship Executive</t>
+          <t>SVP ERP Transformation</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BravoTECH</t>
+          <t>BP</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Michael Coppola</t>
+          <t>Kelli Collins</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>VP, Finance &amp; Treasury</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ashland Inc.</t>
+          <t>BlackJet Marketing</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Juan Correa</t>
+          <t>Oisin Collins</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Sharp Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Manoel Costa</t>
+          <t>Mark Colosimo</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Demo Solutions Expert</t>
+          <t>Director of Strategic Acc…</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SAP Brasil Ltda.</t>
+          <t>The Silicon Partners</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Sophie-Anne Cote</t>
+          <t>Tom Coltrain</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Finance Director</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Barrette-Chapais</t>
+          <t>Dominion Energy, Inc.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Maryanne Coughlin</t>
+          <t>Sean Comer</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Senior Project…</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>TAMKO Building Products LLC</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Robert Coutu</t>
+          <t>Meena Confait</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Sr. Accoun…</t>
+          <t>Global Business &amp; Engagem…</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>System Design Analysis (SDA) inc.</t>
+          <t>SAP MENA LLC</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Julie Craig</t>
+          <t>Alex Connor</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Spon…</t>
+          <t>Senior Develo…</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SPARKS MARKETING (EMEA) LIMITED</t>
+          <t>Lantech.com Coöperatie U.A.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Bill Cranston</t>
+          <t>Adam Conrad</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SAP Sales Director</t>
+          <t>Bus Proc Architect</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Techwave</t>
+          <t>McKesson</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Keith Creech</t>
+          <t>Eileen Conway</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Director, Enterprise Sales</t>
+          <t>Global Head Strategic Partnerships</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SPS Commerce, Inc.</t>
+          <t>Qualitest</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Philippe Cretier</t>
+          <t>Julie Cooper</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Head Finance and Spend Manage…</t>
+          <t>Client Relationship Executive</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>BravoTECH</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Chris Crosby</t>
+          <t>Michael Coppola</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Founder | Managing Partner</t>
+          <t>VP, Finance &amp; Treasury</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Adoptlab</t>
+          <t>Ashland Inc.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Ademar Crotti Junior</t>
+          <t>Juan Correa</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Principal Technical Cons…</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>metaphacts GmbH</t>
+          <t>Sharp Corporation</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ken Crovetti</t>
+          <t>Manoel Costa</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Business Development Manager-…</t>
+          <t>Demo Solutions Expert</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Vertex, Inc.</t>
+          <t>SAP Brasil Ltda.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Miguel Cruz</t>
+          <t>Sophie-Anne Cote</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Gerente de Calidad</t>
+          <t>Finance Director</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Barrette-Chapais</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
+          <t>Maryanne Coughlin</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Robert Coutu</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Sr. Accoun…</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>System Design Analysis (SDA) inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Julie Craig</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Spon…</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SPARKS MARKETING (EMEA) LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Bill Cranston</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SAP Sales Director</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Techwave</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Keith Creech</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Director, Enterprise Sales</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SPS Commerce, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Philippe Cretier</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Head Finance and Spend Manage…</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Chris Crosby</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Founder | Managing Partner</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Adoptlab</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Ademar Crotti Junior</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Principal Technical Cons…</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>metaphacts GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Ken Crovetti</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Business Development Manager-…</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Vertex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Miguel Cruz</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Gerente de Calidad</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
           <t>Michael Cugliari</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>Senior Account Exec…</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>The Silicon Partners Inc</t>
         </is>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C228"/>
+  <dimension ref="A1:C281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4282,6 +4282,903 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Christy Weaver</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Global Demand Generation Man…</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Vertex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Mike Weaver</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Senior I…</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>True Commerce Inc. TrueCommerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Chris Webster</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SVP IT Strategy &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Matt Webster</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Director of…</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Gardner White Furniture Co., Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Patrick Weil</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Metrie Canada Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Sarah Weiler</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Manager, Busine…</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Ball Horticultural Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Adam Werner</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>VP, Corporate Technology</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Crocs, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Maddie Werner</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Director of Delivery Solutions</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Robra IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Katherine West</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>CX Account Executive</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Anja Wettling</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>anuwo GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Charleen Wetzstein</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SAP Principal Architect</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>PROSPECTOR, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Peter Wheatley</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Enterprise Architect…</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SAP America (Houston)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Robb White</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Peter Widmer</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Chief of Staff to the Global Head of S…</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Chad Wiech</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Director of Solution…</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Pittsburgh, SAP America</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Chamnida Wijetilleke</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>The Ducats Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Pete Wilkins</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>NA Partner Manager</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SAP America(Bellevue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Mark Willey</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Vice…</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Ed Williamson</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Client Services Lead</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>XMATERIA LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Monica Willis</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HR Strategy and Value A…</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Plano- Legacy West</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Charlotte Wilson</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Senior Manager Strategic Cha…</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Direct Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Emily Wisemiller</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Molex</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Julia Wolfe</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Analyst Relations Manager</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Jennifer Workman</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Techn…</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Universal Destinations &amp; Experiences</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Steven Wright Wright</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>VP Sales</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Acuiti Labs Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Monty Wurth</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>VP of Operations</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Optima Consulting L.L.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Brad Wylie</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>KAORI YASHIKI</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Business Resear…</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Hitachi Digital Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>YOUNGHO YOO</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Team Leader</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>LG CNS Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Mohamed YUSUF</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Head of Integrated Toolchain</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Hikaru Yafuso</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Senior Alliance Director</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Sonoko Yamamoto</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Partner Business Manager</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Osamu Yamazaki</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Co…</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Kenji Yanagi</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Group Leader</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>ASAHI GROUP JAPAN, LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>EJ Yang</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>IT Deputy Director</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>MediaTek Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Kiran Yarlagadda Yarlagadda</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Managing…</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Adroix Corp DBA CodeForce 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Takayuki Yasuda</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>JFE Systems, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Tomoki Yasuda</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>AssistantMana…</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>NTT DATA Japan Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Kazuhiro Yonekawa</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Chief/Proj…</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>CANON MARKETING JAPAN INC.,</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Sungeui Yoon</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Senior Specialist</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Christopher Yope</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SAP Supply C…</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>DXC Technology Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Kohei Yoshimatsu</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>アズビル株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>taichi yoshida</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Senior Ma…</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>BENIC SOLUTION CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>nakajima yuki</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Nitori Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Stefan Zach</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>VP Global IT</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Wieland Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Beau Zaremski</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Yuan Zhang</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Senior Project Manager, SAP AI RIG</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Cathy Zhou</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>IT Director, EBS</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Ecolab Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Gustavo Zintak</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Manager/Head of Dept</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SWISS MEDICAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Alina Zuberi</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Global Content Strategist</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Yoshiaki Agata 縣</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>AJS株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>裕紀 阿保</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>FORTIENCE CONSULTING INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>謙介 青木</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Manager, Uvance Market Developme…</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Fujitsu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C281"/>
+  <dimension ref="A1:C326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4285,895 +4285,1652 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Christy Weaver</t>
+          <t>Suman Varma</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Global Demand Generation Man…</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Vertex, Inc.</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Mike Weaver</t>
+          <t>Chris Vassalotti</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Senior I…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>True Commerce Inc. TrueCommerce</t>
+          <t>Opentext</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Chris Webster</t>
+          <t>Raju Vedala</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SVP IT Strategy &amp; Architecture</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ahold Delhaize</t>
+          <t>CES Business Technologies, LLC</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Matt Webster</t>
+          <t>Asier Vega Sanchez</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Director of…</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Gardner White Furniture Co., Inc.</t>
+          <t>Arkyn</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Patrick Weil</t>
+          <t>Jennifer Veillon</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Dir Project Controls</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Metrie Canada Ltd</t>
+          <t>Fluor Corporation</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Sarah Weiler</t>
+          <t>Ajay Reddy Velampudi</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Manager, Busine…</t>
+          <t>Senior VP - Sa…</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Ball Horticultural Company</t>
+          <t>Miracle Software Systems Inc.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Adam Werner</t>
+          <t>William Velastegui</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>VP, Corporate Technology</t>
+          <t>JEFE DE TI Y PR…</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Crocs, Inc.</t>
+          <t>Plasticaucho Industrial S.A.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Maddie Werner</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Director of Delivery Solutions</t>
-        </is>
-      </c>
+          <t>Rajiv Vemula</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Robra IT</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Katherine West</t>
+          <t>Sundu Venkataramani</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>CX Account Executive</t>
+          <t>Industry Val…</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Anja Wettling</t>
+          <t>Venkat Venkataramani</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>anuwo GmbH</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Charleen Wetzstein</t>
+          <t>Tom Venner-Crysell</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SAP Principal Architect</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>PROSPECTOR, LLC</t>
+          <t>ERPeople Solutions Ltd</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Peter Wheatley</t>
+          <t>Eduardo Vergara</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Enterprise Architect…</t>
+          <t>Manager/Head of Dept</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>SAP America (Houston)</t>
+          <t>Agrosuper S.A.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Robb White</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr"/>
+          <t>Amit Verma</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>RVP, Head of CFO Advisory…</t>
+        </is>
+      </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Peter Widmer</t>
+          <t>Kumar Vidit</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Chief of Staff to the Global Head of S…</t>
+          <t>Product Marketing M…</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Chad Wiech</t>
+          <t>Lakshmi Vidyashankar</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Director of Solution…</t>
+          <t>VP of IT</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>Marvin Engineering Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Chamnida Wijetilleke</t>
+          <t>Jayant Vikram</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Cloud Delivery Lead</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>The Ducats Group LLC</t>
+          <t>Accenture LLP</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Pete Wilkins</t>
+          <t>Yeni Villanueva</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>NA Partner Manager</t>
+          <t>Supervisora…</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>Compañia Minera Antamina S.A.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Mark Willey</t>
+          <t>Robert Vinyard</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Vice…</t>
+          <t>VP and Senior Partner</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Ed Williamson</t>
+          <t>Thomas Vioux</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Client Services Lead</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>XMATERIA LTD</t>
+          <t>PwC</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Monica Willis</t>
+          <t>Anil Visal</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>HR Strategy and Value A…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Plano- Legacy West</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Charlotte Wilson</t>
+          <t>Clara Viscido</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Senior Manager Strategic Cha…</t>
+          <t>Consulting Services Director</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Direct Energy</t>
+          <t>GEONOSIS</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Emily Wisemiller</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst</t>
-        </is>
-      </c>
+          <t>Paulo Vita Vita</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Julia Wolfe</t>
+          <t>Ranjan Vitt</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Analyst Relations Manager</t>
+          <t>AI Compliance Governance Program…</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Jennifer Workman</t>
+          <t>Jose Voisin</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Techn…</t>
+          <t>Global CIO</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Universal Destinations &amp; Experiences</t>
+          <t>Carmeuse</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Steven Wright Wright</t>
+          <t>Christina Volk</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>VP Sales</t>
+          <t>Head of Strate…</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Acuiti Labs Limited</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Monty Wurth</t>
+          <t>Jessica Voyles</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>VP of Operations</t>
+          <t>Account Executive, South</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Optima Consulting L.L.C.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Brad Wylie</t>
+          <t>Sandeep Vyas</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Solutio…</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Incture Technologies Private Limited</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>KAORI YASHIKI</t>
+          <t>Thomas von Alm</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Business Resear…</t>
+          <t>SVP Cross-Solution Services</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services LLC</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>YOUNGHO YOO</t>
+          <t>Markus von Quast</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Team Leader</t>
+          <t>Global Head Industry Ecosystem</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>LG CNS Co., Ltd.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Mohamed YUSUF</t>
+          <t>TATSUO WATANABE</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Head of Integrated Toolchain</t>
+          <t>Principal Cons…</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>D I SQUARE CORPORATION.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Hikaru Yafuso</t>
+          <t>Masayuki Wada</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Senior Alliance Director</t>
+          <t>SVP, Head of Corporate Digit…</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Fujitsu Limited</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Sonoko Yamamoto</t>
+          <t>Stephen Wagenheim</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Partner Business Manager</t>
+          <t>Senior Sales Executive - Suppl…</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>Dallas (Allen)</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Osamu Yamazaki</t>
+          <t>Neha Wahi</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Co…</t>
+          <t>Global Alliance Lead</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+          <t>A.T. Kearney, Inc.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Kenji Yanagi</t>
+          <t>Waka Wakabayashi</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Group Leader</t>
+          <t>Associate Partner</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ASAHI GROUP JAPAN, LTD.</t>
+          <t>KPMG Consulting Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>EJ Yang</t>
+          <t>Gustavo Waldfogiel</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>IT Deputy Director</t>
+          <t>LAC HCM Head</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>MediaTek Inc.</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Kiran Yarlagadda Yarlagadda</t>
+          <t>Shashikant Walimbe</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Managing…</t>
+          <t>Vice President &amp; Global Head -…</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Adroix Corp DBA CodeForce 360</t>
+          <t>LTM LIMITED</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Takayuki Yasuda</t>
+          <t>Julie Walker</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>Sr. Director, Enterprise Applicatio…</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>JFE Systems, Inc.</t>
+          <t>Armstrong</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Tomoki Yasuda</t>
+          <t>Rob Wallace</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>AssistantMana…</t>
+          <t>Senior Manager Digital &amp; In…</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>NTT DATA Japan Corporation</t>
+          <t>Jaguarlandrover</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Kazuhiro Yonekawa</t>
+          <t>Enzhou Wang</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Chief/Proj…</t>
+          <t>Chief Technology Officer</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>CANON MARKETING JAPAN INC.,</t>
+          <t>City of Tacoma</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Sungeui Yoon</t>
+          <t>May Wang</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Senior Specialist</t>
+          <t>Direc…</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Christopher Yope</t>
+          <t>Adam Warner</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SAP Supply C…</t>
+          <t>Cost Analyst</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DXC Technology Services LLC</t>
+          <t>Marathon Cheese Corporation</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Kohei Yoshimatsu</t>
+          <t>Kosuke Watanabe</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>アズビル株式会社</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>taichi yoshida</t>
+          <t>Takashi Watanabe</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Senior Ma…</t>
+          <t>執行役員</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>BENIC SOLUTION CORPORATION</t>
+          <t>JFE Systems,Inc.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>nakajima yuki</t>
+          <t>Robert Watson</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Sr Account Executive</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Nitori Co., Ltd.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Stefan Zach</t>
+          <t>Ashley Waxman</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>VP Global IT</t>
+          <t>Strategic Sales Executive</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Wieland Group</t>
+          <t>Aevitas IT LLC</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Beau Zaremski</t>
+          <t>Christy Weaver</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>VP of Sales</t>
+          <t>Global Demand Generation Man…</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Vertex, Inc.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Yuan Zhang</t>
+          <t>Mike Weaver</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Senior Project Manager, SAP AI RIG</t>
+          <t>Senior I…</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>True Commerce Inc. TrueCommerce</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Cathy Zhou</t>
+          <t>Chris Webster</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>IT Director, EBS</t>
+          <t>SVP IT Strategy &amp; Architecture</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>Ahold Delhaize</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Gustavo Zintak</t>
+          <t>Matt Webster</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>Director of…</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>SWISS MEDICAL S.A.</t>
+          <t>Gardner White Furniture Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Alina Zuberi</t>
+          <t>Patrick Weil</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Global Content Strategist</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>Metrie Canada Ltd</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Yoshiaki Agata 縣</t>
+          <t>Sarah Weiler</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>Manager, Busine…</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>AJS株式会社</t>
+          <t>Ball Horticultural Company</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>裕紀 阿保</t>
+          <t>Adam Werner</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>VP, Corporate Technology</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>FORTIENCE CONSULTING INC.</t>
+          <t>Crocs, Inc.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
+          <t>Maddie Werner</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Director of Delivery Solutions</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Robra IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Katherine West</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>CX Account Executive</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Anja Wettling</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>anuwo GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Charleen Wetzstein</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>SAP Principal Architect</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>PROSPECTOR, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Peter Wheatley</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Enterprise Architect…</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SAP America (Houston)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Robb White</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Peter Widmer</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Chief of Staff to the Global Head of S…</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Chad Wiech</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Director of Solution…</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Pittsburgh, SAP America</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Chamnida Wijetilleke</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>The Ducats Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Pete Wilkins</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>NA Partner Manager</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>SAP America(Bellevue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Mark Willey</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Vice…</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Ed Williamson</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Client Services Lead</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>XMATERIA LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Monica Willis</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HR Strategy and Value A…</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Plano- Legacy West</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Charlotte Wilson</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Senior Manager Strategic Cha…</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Direct Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Emily Wisemiller</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Molex</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Julia Wolfe</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Analyst Relations Manager</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Jennifer Workman</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Techn…</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Universal Destinations &amp; Experiences</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Steven Wright Wright</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>VP Sales</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Acuiti Labs Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Monty Wurth</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>VP of Operations</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Optima Consulting L.L.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Brad Wylie</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>KAORI YASHIKI</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Business Resear…</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Hitachi Digital Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>YOUNGHO YOO</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Team Leader</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>LG CNS Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Mohamed YUSUF</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Head of Integrated Toolchain</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Hikaru Yafuso</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Senior Alliance Director</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Sonoko Yamamoto</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Partner Business Manager</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Osamu Yamazaki</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Co…</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Kenji Yanagi</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Group Leader</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>ASAHI GROUP JAPAN, LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>EJ Yang</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>IT Deputy Director</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>MediaTek Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Kiran Yarlagadda Yarlagadda</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Managing…</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Adroix Corp DBA CodeForce 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Takayuki Yasuda</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>JFE Systems, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Tomoki Yasuda</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>AssistantMana…</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>NTT DATA Japan Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Kazuhiro Yonekawa</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Chief/Proj…</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>CANON MARKETING JAPAN INC.,</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Sungeui Yoon</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Senior Specialist</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Christopher Yope</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>SAP Supply C…</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>DXC Technology Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Kohei Yoshimatsu</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>アズビル株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>taichi yoshida</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Senior Ma…</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>BENIC SOLUTION CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>nakajima yuki</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Nitori Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Stefan Zach</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>VP Global IT</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Wieland Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Beau Zaremski</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Yuan Zhang</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Senior Project Manager, SAP AI RIG</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Cathy Zhou</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>IT Director, EBS</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Ecolab Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Gustavo Zintak</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Manager/Head of Dept</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>SWISS MEDICAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Alina Zuberi</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Global Content Strategist</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Yoshiaki Agata 縣</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>AJS株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>裕紀 阿保</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>FORTIENCE CONSULTING INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
           <t>謙介 青木</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>Manager, Uvance Market Developme…</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C326" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C326"/>
+  <dimension ref="A1:C380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4285,7 +4285,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Suman Varma</t>
+          <t>Ahmed Taher</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4295,1642 +4295,2556 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Al Daajan Trading</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Chris Vassalotti</t>
+          <t>Chieko Takahata</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Chief</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Opentext</t>
+          <t>BROTHER INDUSTRIES,LTD.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Raju Vedala</t>
+          <t>Arai Takahiro</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Services Delivery Manag…</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>CES Business Technologies, LLC</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Asier Vega Sanchez</t>
+          <t>Eiji Takashina</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Arkyn</t>
+          <t>Kyndryl Japan KK</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Jennifer Veillon</t>
+          <t>Tetsushi Takino</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Dir Project Controls</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Fluor Corporation</t>
+          <t>大和ハウス工業株式会社</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ajay Reddy Velampudi</t>
+          <t>Makoto Tamura</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Senior VP - Sa…</t>
+          <t>Alliance Group Director</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Miracle Software Systems Inc.</t>
+          <t>FUJITSU LIMITED</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>William Velastegui</t>
+          <t>Chiyuki Tanaka</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>JEFE DE TI Y PR…</t>
+          <t>Team leader</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Plasticaucho Industrial S.A.</t>
+          <t>Recruit Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Rajiv Vemula</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr"/>
+          <t>Steve Tanaka</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Sr Vice Presid…</t>
+        </is>
+      </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions U.S. Corporat…</t>
+          <t>Blommer Chocolate Company</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Sundu Venkataramani</t>
+          <t>Yasuhiro Tanaka</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Industry Val…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>SAP Industries (Washington DC)</t>
+          <t>Recuruit Co.,Ltd.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Venkat Venkataramani</t>
+          <t>Kristin Taner</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>Chief Marke…</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Vortex Software Consulting, LLC</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Tom Venner-Crysell</t>
+          <t>Mitchell Tauer</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Services Account Execut…</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ERPeople Solutions Ltd</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Eduardo Vergara</t>
+          <t>Roxanna Tavares</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>Director, Gl…</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Agrosuper S.A.</t>
+          <t>The Nielsen Company (US), LLC.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Amit Verma</t>
+          <t>Theo Tavrides</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>RVP, Head of CFO Advisory…</t>
+          <t>Vice Presi…</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>NTT Data Business Solutions, Inc.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Kumar Vidit</t>
+          <t>Jamie Taylor</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Product Marketing M…</t>
+          <t>Global VP, Strategic Partnerships</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Lakshmi Vidyashankar</t>
+          <t>Meghan Taylor</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>VP of IT</t>
+          <t>Industry Account Ex…</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Marvin Engineering Co., Inc.</t>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Jayant Vikram</t>
+          <t>Samantha Taylor</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Cloud Delivery Lead</t>
+          <t>Senior Solutions Account Exec…</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Accenture LLP</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Yeni Villanueva</t>
+          <t>Sarah Taylor</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Supervisora…</t>
+          <t>Solution Advisor</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Compañia Minera Antamina S.A.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Robert Vinyard</t>
+          <t>Jorge Tercero</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>VP and Senior Partner</t>
+          <t>Manager/H…</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Asociacion Mutual Sancor Salud</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Thomas Vioux</t>
+          <t>Michael Teti</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Carlisle Construction Materials</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Anil Visal</t>
+          <t>Suji Thampi</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>MINDSPRINT PTE. LTD.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Clara Viscido</t>
+          <t>Le Thanh Phong</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Consulting Services Director</t>
+          <t>Managing Direc…</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>GEONOSIS</t>
+          <t>FPT Japan Holdings Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Paulo Vita Vita</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr"/>
+          <t>Michael Theis</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Senior Director, Healthcare Life Scien…</t>
+        </is>
+      </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
+          <t>Icertis</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Ranjan Vitt</t>
+          <t>Rene Theriault</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>AI Compliance Governance Program…</t>
+          <t>IT Program Director</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>BRP INC</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Jose Voisin</t>
+          <t>Barbara Thrasher</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Global CIO</t>
+          <t>SR STAFF ARCHITECT</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Christina Volk</t>
+          <t>Nissim Titan</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Head of Strate…</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>4CAST SYSTEMS LTD</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Jessica Voyles</t>
+          <t>James Tiwari</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Account Executive, South</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Intellioz LLC</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Sandeep Vyas</t>
+          <t>Shuhei Toba</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Solutio…</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Incture Technologies Private Limited</t>
+          <t>Business Engineering Corporation</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Thomas von Alm</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>SVP Cross-Solution Services</t>
-        </is>
-      </c>
+          <t>John Tocci</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Cbs Corporate Business Solutions America In…</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Markus von Quast</t>
+          <t>Oliver Toloui</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Global Head Industry Ecosystem</t>
+          <t>Director - AI…</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Ibase Operations Corp Qualitest</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TATSUO WATANABE</t>
+          <t>Ray Toma</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Principal Cons…</t>
+          <t>Senior Principal — Global Strategic Initia…</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>D I SQUARE CORPORATION.</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Masayuki Wada</t>
+          <t>Yuko Tominaga</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SVP, Head of Corporate Digit…</t>
+          <t>Research Writer</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Fujitsu Limited</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Stephen Wagenheim</t>
+          <t>Laura Tozzo</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Senior Sales Executive - Suppl…</t>
+          <t>AI Product Lead SAP IBP</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Dallas (Allen)</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Neha Wahi</t>
+          <t>Eero Traagel</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Global Alliance Lead</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>A.T. Kearney, Inc.</t>
+          <t>IBM Canada Limited</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Waka Wakabayashi</t>
+          <t>Adam Trahan</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Associate Partner</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>KPMG Consulting Co., Ltd.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Gustavo Waldfogiel</t>
+          <t>Evgeny Treskin</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>LAC HCM Head</t>
+          <t>SAP Alliances Director</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>SAP Argentina - Buenos Aires</t>
+          <t>Argano</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Shashikant Walimbe</t>
+          <t>Chetan Tripathi</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Vice President &amp; Global Head -…</t>
+          <t>oCFO Adoption expert</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>LTM LIMITED</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Julie Walker</t>
+          <t>Seshagiri Tripurana</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Sr. Director, Enterprise Applicatio…</t>
+          <t>Senior Director</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Armstrong</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Rob Wallace</t>
+          <t>Masaru Tsukahira</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Senior Manager Digital &amp; In…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Jaguarlandrover</t>
+          <t>TOKYO ELECTRON LIMITED.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Enzhou Wang</t>
+          <t>Lindsay Tucker</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Chief Technology Officer</t>
+          <t>Solution Consultant</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>City of Tacoma</t>
+          <t>Docusign</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>May Wang</t>
+          <t>Paul Turbes</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Direc…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
+          <t>KPMG LLP</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Adam Warner</t>
+          <t>Treaver Tyler</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Cost Analyst</t>
+          <t>Tech…</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Marathon Cheese Corporation</t>
+          <t>Meijer Great Lakes Limited Partnership</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Kosuke Watanabe</t>
+          <t>Kotaro Ueda</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>JSUG</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Takashi Watanabe</t>
+          <t>Rajkishore Una</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>執行役員</t>
+          <t>President/CEO</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>JFE Systems,Inc.</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Robert Watson</t>
+          <t>Bala Parameswara Rao Upadhyay…</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Sr Account Executive</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Stefanini, Inc.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Ashley Waxman</t>
+          <t>Oscar Uribe</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Strategic Sales Executive</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Aevitas IT LLC</t>
+          <t>EDUARDONO S A S</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Christy Weaver</t>
+          <t>SACHIN VAIDYA</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Global Demand Generation Man…</t>
+          <t>Director - Enterprise Commercial…</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Vertex, Inc.</t>
+          <t>Pfizer, Inc.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Mike Weaver</t>
+          <t>Jonathan VON RUEDEN</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Senior I…</t>
+          <t>Chief AI Officer</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>True Commerce Inc. TrueCommerce</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Chris Webster</t>
+          <t>Wagner Valentin</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SVP IT Strategy &amp; Architecture</t>
+          <t>Director of Regulated Indust…</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Ahold Delhaize</t>
+          <t>SAP Brasil Ltda.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Matt Webster</t>
+          <t>Jorge Valles Velásquez</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Director of…</t>
+          <t>KMMP…</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Gardner White Furniture Co., Inc.</t>
+          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Patrick Weil</t>
+          <t>Henri Vallet</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>VP Sales, Americas B2B</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Metrie Canada Ltd</t>
+          <t>Mirakl</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Sarah Weiler</t>
+          <t>Jeff Van Pelt</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Manager, Busine…</t>
+          <t>Founder / Managing Dire…</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ball Horticultural Company</t>
+          <t>Javelin Consulting</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Adam Werner</t>
+          <t>Meredith Van Wyk</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>VP, Corporate Technology</t>
+          <t>Americas Field Partner…</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Crocs, Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Maddie Werner</t>
+          <t>Joris Van der Donck</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Director of Delivery Solutions</t>
+          <t>Sr Manag…</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Robra IT</t>
+          <t>Commscope Connectivity Belgium</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Katherine West</t>
+          <t>Vijay Varee</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>CX Account Executive</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Petsmart LLC</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Anja Wettling</t>
+          <t>Suman Varma</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>anuwo GmbH</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Charleen Wetzstein</t>
+          <t>Chris Vassalotti</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SAP Principal Architect</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>PROSPECTOR, LLC</t>
+          <t>Opentext</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Peter Wheatley</t>
+          <t>Raju Vedala</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Enterprise Architect…</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>SAP America (Houston)</t>
+          <t>CES Business Technologies, LLC</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Robb White</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr"/>
+          <t>Asier Vega Sanchez</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Implementation Consultant</t>
+        </is>
+      </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+          <t>Arkyn</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Peter Widmer</t>
+          <t>Jennifer Veillon</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Chief of Staff to the Global Head of S…</t>
+          <t>Dir Project Controls</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Fluor Corporation</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Chad Wiech</t>
+          <t>Ajay Reddy Velampudi</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Director of Solution…</t>
+          <t>Senior VP - Sa…</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>Miracle Software Systems Inc.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Chamnida Wijetilleke</t>
+          <t>William Velastegui</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>JEFE DE TI Y PR…</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>The Ducats Group LLC</t>
+          <t>Plasticaucho Industrial S.A.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Pete Wilkins</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>NA Partner Manager</t>
-        </is>
-      </c>
+          <t>Rajiv Vemula</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Mark Willey</t>
+          <t>Sundu Venkataramani</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Vice…</t>
+          <t>Industry Val…</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Ed Williamson</t>
+          <t>Venkat Venkataramani</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Client Services Lead</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>XMATERIA LTD</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Monica Willis</t>
+          <t>Tom Venner-Crysell</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>HR Strategy and Value A…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Plano- Legacy West</t>
+          <t>ERPeople Solutions Ltd</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Charlotte Wilson</t>
+          <t>Eduardo Vergara</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Senior Manager Strategic Cha…</t>
+          <t>Manager/Head of Dept</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Direct Energy</t>
+          <t>Agrosuper S.A.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Emily Wisemiller</t>
+          <t>Amit Verma</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>RVP, Head of CFO Advisory…</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Julia Wolfe</t>
+          <t>Kumar Vidit</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Analyst Relations Manager</t>
+          <t>Product Marketing M…</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Jennifer Workman</t>
+          <t>Lakshmi Vidyashankar</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Techn…</t>
+          <t>VP of IT</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Universal Destinations &amp; Experiences</t>
+          <t>Marvin Engineering Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Steven Wright Wright</t>
+          <t>Jayant Vikram</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>VP Sales</t>
+          <t>Cloud Delivery Lead</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Acuiti Labs Limited</t>
+          <t>Accenture LLP</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Monty Wurth</t>
+          <t>Yeni Villanueva</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>VP of Operations</t>
+          <t>Supervisora…</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Optima Consulting L.L.C.</t>
+          <t>Compañia Minera Antamina S.A.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Brad Wylie</t>
+          <t>Robert Vinyard</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>VP and Senior Partner</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>KAORI YASHIKI</t>
+          <t>Thomas Vioux</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Business Resear…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services LLC</t>
+          <t>PwC</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>YOUNGHO YOO</t>
+          <t>Anil Visal</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Team Leader</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>LG CNS Co., Ltd.</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Mohamed YUSUF</t>
+          <t>Clara Viscido</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Head of Integrated Toolchain</t>
+          <t>Consulting Services Director</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>GEONOSIS</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Hikaru Yafuso</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Senior Alliance Director</t>
-        </is>
-      </c>
+          <t>Paulo Vita Vita</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Sonoko Yamamoto</t>
+          <t>Ranjan Vitt</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Partner Business Manager</t>
+          <t>AI Compliance Governance Program…</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Osamu Yamazaki</t>
+          <t>Jose Voisin</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Co…</t>
+          <t>Global CIO</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+          <t>Carmeuse</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Kenji Yanagi</t>
+          <t>Christina Volk</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Group Leader</t>
+          <t>Head of Strate…</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>ASAHI GROUP JAPAN, LTD.</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>EJ Yang</t>
+          <t>Jessica Voyles</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>IT Deputy Director</t>
+          <t>Account Executive, South</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>MediaTek Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Kiran Yarlagadda Yarlagadda</t>
+          <t>Sandeep Vyas</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Managing…</t>
+          <t>Solutio…</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Adroix Corp DBA CodeForce 360</t>
+          <t>Incture Technologies Private Limited</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Takayuki Yasuda</t>
+          <t>Thomas von Alm</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>SVP Cross-Solution Services</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>JFE Systems, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Tomoki Yasuda</t>
+          <t>Markus von Quast</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>AssistantMana…</t>
+          <t>Global Head Industry Ecosystem</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>NTT DATA Japan Corporation</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Kazuhiro Yonekawa</t>
+          <t>TATSUO WATANABE</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Chief/Proj…</t>
+          <t>Principal Cons…</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>CANON MARKETING JAPAN INC.,</t>
+          <t>D I SQUARE CORPORATION.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Sungeui Yoon</t>
+          <t>Masayuki Wada</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Senior Specialist</t>
+          <t>SVP, Head of Corporate Digit…</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Fujitsu Limited</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Christopher Yope</t>
+          <t>Stephen Wagenheim</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>SAP Supply C…</t>
+          <t>Senior Sales Executive - Suppl…</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>DXC Technology Services LLC</t>
+          <t>Dallas (Allen)</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Kohei Yoshimatsu</t>
+          <t>Neha Wahi</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Global Alliance Lead</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>アズビル株式会社</t>
+          <t>A.T. Kearney, Inc.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>taichi yoshida</t>
+          <t>Waka Wakabayashi</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Senior Ma…</t>
+          <t>Associate Partner</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>BENIC SOLUTION CORPORATION</t>
+          <t>KPMG Consulting Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>nakajima yuki</t>
+          <t>Gustavo Waldfogiel</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>LAC HCM Head</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Nitori Co., Ltd.</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Stefan Zach</t>
+          <t>Shashikant Walimbe</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>VP Global IT</t>
+          <t>Vice President &amp; Global Head -…</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Wieland Group</t>
+          <t>LTM LIMITED</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Beau Zaremski</t>
+          <t>Julie Walker</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>VP of Sales</t>
+          <t>Sr. Director, Enterprise Applicatio…</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Armstrong</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Yuan Zhang</t>
+          <t>Rob Wallace</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Senior Project Manager, SAP AI RIG</t>
+          <t>Senior Manager Digital &amp; In…</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Jaguarlandrover</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Cathy Zhou</t>
+          <t>Enzhou Wang</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>IT Director, EBS</t>
+          <t>Chief Technology Officer</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>City of Tacoma</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Gustavo Zintak</t>
+          <t>May Wang</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>Direc…</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>SWISS MEDICAL S.A.</t>
+          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Alina Zuberi</t>
+          <t>Adam Warner</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Global Content Strategist</t>
+          <t>Cost Analyst</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>Marathon Cheese Corporation</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Yoshiaki Agata 縣</t>
+          <t>Kosuke Watanabe</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>AJS株式会社</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>裕紀 阿保</t>
+          <t>Takashi Watanabe</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>執行役員</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>FORTIENCE CONSULTING INC.</t>
+          <t>JFE Systems,Inc.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
+          <t>Robert Watson</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Sr Account Executive</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Ashley Waxman</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Strategic Sales Executive</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Aevitas IT LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Christy Weaver</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Global Demand Generation Man…</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Vertex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Mike Weaver</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Senior I…</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>True Commerce Inc. TrueCommerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Chris Webster</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>SVP IT Strategy &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Matt Webster</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Director of…</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Gardner White Furniture Co., Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Patrick Weil</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Metrie Canada Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Sarah Weiler</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Manager, Busine…</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Ball Horticultural Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Adam Werner</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>VP, Corporate Technology</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Crocs, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Maddie Werner</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Director of Delivery Solutions</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Robra IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Katherine West</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>CX Account Executive</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Anja Wettling</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>anuwo GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Charleen Wetzstein</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>SAP Principal Architect</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>PROSPECTOR, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Peter Wheatley</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Enterprise Architect…</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>SAP America (Houston)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Robb White</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Peter Widmer</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Chief of Staff to the Global Head of S…</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Chad Wiech</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Director of Solution…</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Pittsburgh, SAP America</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Chamnida Wijetilleke</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>The Ducats Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Pete Wilkins</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>NA Partner Manager</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>SAP America(Bellevue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Mark Willey</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Vice…</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Ed Williamson</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Client Services Lead</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>XMATERIA LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Monica Willis</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>HR Strategy and Value A…</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Plano- Legacy West</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Charlotte Wilson</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Senior Manager Strategic Cha…</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Direct Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Emily Wisemiller</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Molex</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Julia Wolfe</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Analyst Relations Manager</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Jennifer Workman</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Techn…</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Universal Destinations &amp; Experiences</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Steven Wright Wright</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>VP Sales</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Acuiti Labs Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Monty Wurth</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>VP of Operations</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Optima Consulting L.L.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Brad Wylie</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>KAORI YASHIKI</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Business Resear…</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Hitachi Digital Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>YOUNGHO YOO</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Team Leader</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>LG CNS Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Mohamed YUSUF</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Head of Integrated Toolchain</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Hikaru Yafuso</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Senior Alliance Director</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Sonoko Yamamoto</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Partner Business Manager</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Osamu Yamazaki</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Co…</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Kenji Yanagi</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Group Leader</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>ASAHI GROUP JAPAN, LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>EJ Yang</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>IT Deputy Director</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>MediaTek Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Kiran Yarlagadda Yarlagadda</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Managing…</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Adroix Corp DBA CodeForce 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Takayuki Yasuda</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>JFE Systems, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Tomoki Yasuda</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>AssistantMana…</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>NTT DATA Japan Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Kazuhiro Yonekawa</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Chief/Proj…</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>CANON MARKETING JAPAN INC.,</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Sungeui Yoon</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Senior Specialist</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Christopher Yope</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SAP Supply C…</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>DXC Technology Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Kohei Yoshimatsu</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>アズビル株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>taichi yoshida</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Senior Ma…</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>BENIC SOLUTION CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>nakajima yuki</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Nitori Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Stefan Zach</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>VP Global IT</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Wieland Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Beau Zaremski</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Yuan Zhang</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Senior Project Manager, SAP AI RIG</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Cathy Zhou</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>IT Director, EBS</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Ecolab Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Gustavo Zintak</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Manager/Head of Dept</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>SWISS MEDICAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Alina Zuberi</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Global Content Strategist</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Yoshiaki Agata 縣</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>AJS株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>裕紀 阿保</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>FORTIENCE CONSULTING INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
           <t>謙介 青木</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B380" t="inlineStr">
         <is>
           <t>Manager, Uvance Market Developme…</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
+      <c r="C380" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C380"/>
+  <dimension ref="A1:C426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4285,1343 +4285,1339 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Ahmed Taher</t>
+          <t>Sukhbir Singh</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>S…</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Al Daajan Trading</t>
+          <t>The School Board of Duval County Florida</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Chieko Takahata</t>
+          <t>Vikrant Sisodia</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Chief</t>
+          <t>Sr. Product Manager</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>BROTHER INDUSTRIES,LTD.</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Arai Takahiro</t>
+          <t>David Smith</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Services Delivery Manag…</t>
+          <t>VP, Chief Enterprise Ar…</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>SAP America (Reston)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Eiji Takashina</t>
+          <t>Rachel Smith</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Associate Director</t>
+          <t>Partner Sales Manager</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Kyndryl Japan KK</t>
+          <t>Docusign Inc</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Tetsushi Takino</t>
+          <t>Mark Smysor</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Business Systems Analyst in Enterpri…</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>大和ハウス工業株式会社</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Makoto Tamura</t>
+          <t>Delaiah Snowden</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Alliance Group Director</t>
+          <t>IT Ana…</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>FUJITSU LIMITED</t>
+          <t>South Florida Water Management Dist</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Chiyuki Tanaka</t>
+          <t>Jairo Soares De Matos</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Team leader</t>
+          <t>Analyst - SAP Busi…</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Recruit Co., Ltd.</t>
+          <t>Canadian Blood Services</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Steve Tanaka</t>
+          <t>Michael Somerville</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Sr Vice Presid…</t>
+          <t>Sales Executive</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Blommer Chocolate Company</t>
+          <t>Checkout.com</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Yasuhiro Tanaka</t>
+          <t>YoonWon Song</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Recuruit Co.,Ltd.</t>
+          <t>i-SENS, Inc.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Kristin Taner</t>
+          <t>Dag Terje Sorlie</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Chief Marke…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Vortex Software Consulting, LLC</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Mitchell Tauer</t>
+          <t>Thiago Souza</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Services Account Execut…</t>
+          <t>IT CO…</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>MINERACAO SERRAS DO OESTE LTDA</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Roxanna Tavares</t>
+          <t>Meik Spanowsky</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Director, Gl…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>The Nielsen Company (US), LLC.</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Theo Tavrides</t>
+          <t>Thorsten Spihlmann</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Vice Presi…</t>
+          <t>Head of Business Development for T…</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>NTT Data Business Solutions, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Jamie Taylor</t>
+          <t>TD Srinivasan</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Global VP, Strategic Partnerships</t>
+          <t>Industry…</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>SAP Public Services, Inc. (Hudson Y</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Meghan Taylor</t>
+          <t>Mike Stafford</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Industry Account Ex…</t>
+          <t>Senior ABAP Developer</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>Titan Ventures LLC</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Samantha Taylor</t>
+          <t>Jennifer Stapleton</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Senior Solutions Account Exec…</t>
+          <t>VP of Accounting Strategy &amp;…</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>American Equity</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Sarah Taylor</t>
+          <t>John Stark</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Solution Advisor</t>
+          <t>Global Head of SAP Alliance</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Loftware</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Jorge Tercero</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Manager/H…</t>
-        </is>
-      </c>
+          <t>Denis Staudt</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Asociacion Mutual Sancor Salud</t>
+          <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Michael Teti</t>
+          <t>Maximilian Stein</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>SAP Product Owner - Treasury CPIT</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Carlisle Construction Materials</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Suji Thampi</t>
+          <t>Amanda Steiner</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Business Process Architect</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>MINDSPRINT PTE. LTD.</t>
+          <t>McKesson</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Le Thanh Phong</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Managing Direc…</t>
-        </is>
-      </c>
+          <t>Dieter Steinmann</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
-          <t>FPT Japan Holdings Co., Ltd.</t>
+          <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Michael Theis</t>
+          <t>Jorrit Steinz</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Senior Director, Healthcare Life Scien…</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Icertis</t>
+          <t>ChannelEngine.com</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Rene Theriault</t>
+          <t>Robert Stemmler</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>IT Program Director</t>
+          <t>Global Alliances &amp; Ec…</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>BRP INC</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Barbara Thrasher</t>
+          <t>Yonathan Stephanos</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SR STAFF ARCHITECT</t>
+          <t>SAP Data &amp; AI Business Group Le…</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Tyson Foods, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Nissim Titan</t>
+          <t>Patrick Stewart</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4CAST SYSTEMS LTD</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>James Tiwari</t>
+          <t>Jochen Stiebe</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Head of Sales Treas…</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Intellioz LLC</t>
+          <t>Target-Networks GmbH</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Shuhei Toba</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
+          <t>Leslie Stoffel</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Business Engineering Corporation</t>
+          <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>John Tocci</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr"/>
+          <t>Miodrag Stojanov</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Lead Engineer</t>
+        </is>
+      </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Cbs Corporate Business Solutions America In…</t>
+          <t>SEMOS SOFTWARE LLC</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Oliver Toloui</t>
+          <t>Bojana Stojanovich</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Director - AI…</t>
+          <t>VP, NA Strategic Partnerships</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Ibase Operations Corp Qualitest</t>
+          <t>Tricentis</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Ray Toma</t>
+          <t>Seda Strate</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Senior Principal — Global Strategic Initia…</t>
+          <t>Partner Innovation Lead</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Yuko Tominaga</t>
+          <t>Divya Struebing</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Research Writer</t>
+          <t>Supply Chain Customer…</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Laura Tozzo</t>
+          <t>Kevin Stupp</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>AI Product Lead SAP IBP</t>
+          <t>Director S4 Platform</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Eero Traagel</t>
+          <t>Harish Subramanian</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Principal Enterprise Arch…</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>IBM Canada Limited</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Adam Trahan</t>
+          <t>Marc Sudjian</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Enterprise Architect, SAP So…</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Bombardier Inc.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Evgeny Treskin</t>
+          <t>Hirofumi Sugimoto</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SAP Alliances Director</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>ABeam Systems Ltd.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Chetan Tripathi</t>
+          <t>Michael Sukachev</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>oCFO Adoption expert</t>
+          <t>Sr. EA</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Teranet Inc</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Seshagiri Tripurana</t>
+          <t>Som Suresh</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Senior Director</t>
+          <t>Man…</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Masaru Tsukahira</t>
+          <t>Jain Sushant</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Chief Revenue Officer, F&amp;S…</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>TOKYO ELECTRON LIMITED.</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Lindsay Tucker</t>
+          <t>Scott Sutker</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Solution Consultant</t>
+          <t>Vice President Customer Success…</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Docusign</t>
+          <t>Alpharetta</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Paul Turbes</t>
+          <t>Mergenthaler Sven</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Global Head of Strategic Central Ser…</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>KPMG LLP</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Treaver Tyler</t>
+          <t>Jereme Swoboda</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Tech…</t>
+          <t>Segment Director</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Meijer Great Lakes Limited Partnership</t>
+          <t>Avvale, Inc.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Kotaro Ueda</t>
+          <t>Debra Syring</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Senior IT Manager</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>JSUG</t>
+          <t>Entegris, Inc.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Rajkishore Una</t>
+          <t>Kai Szatkowski</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>President/CEO</t>
+          <t>Head of Product Sales</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>GyanSys, Inc.</t>
+          <t>Natuvion GmbH</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Bala Parameswara Rao Upadhyay…</t>
+          <t>MARCO TOMBOLINI</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Associate Director</t>
+          <t>Global He…</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Stefanini, Inc.</t>
+          <t>DOLCE &amp; GABBANA BEAUTY SRL</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Oscar Uribe</t>
+          <t>KAZUSHI TOYOMASU</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>Global Direct…</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>EDUARDONO S A S</t>
+          <t>MOL Chemical Tankers Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>SACHIN VAIDYA</t>
+          <t>Stacey Taborelli</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Director - Enterprise Commercial…</t>
+          <t>Executive Business Partn…</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Pfizer, Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Jonathan VON RUEDEN</t>
+          <t>Ahmed Taher</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Chief AI Officer</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Al Daajan Trading</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Wagner Valentin</t>
+          <t>Chieko Takahata</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Director of Regulated Indust…</t>
+          <t>Chief</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>SAP Brasil Ltda.</t>
+          <t>BROTHER INDUSTRIES,LTD.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Jorge Valles Velásquez</t>
+          <t>Arai Takahiro</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>KMMP…</t>
+          <t>Services Delivery Manag…</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Henri Vallet</t>
+          <t>Eiji Takashina</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>VP Sales, Americas B2B</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Mirakl</t>
+          <t>Kyndryl Japan KK</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Jeff Van Pelt</t>
+          <t>Tetsushi Takino</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Founder / Managing Dire…</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Javelin Consulting</t>
+          <t>大和ハウス工業株式会社</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Meredith Van Wyk</t>
+          <t>Makoto Tamura</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Americas Field Partner…</t>
+          <t>Alliance Group Director</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>FUJITSU LIMITED</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Joris Van der Donck</t>
+          <t>Chiyuki Tanaka</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Sr Manag…</t>
+          <t>Team leader</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Commscope Connectivity Belgium</t>
+          <t>Recruit Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Vijay Varee</t>
+          <t>Steve Tanaka</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Sr Vice Presid…</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Petsmart LLC</t>
+          <t>Blommer Chocolate Company</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Suman Varma</t>
+          <t>Yasuhiro Tanaka</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Recuruit Co.,Ltd.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Chris Vassalotti</t>
+          <t>Kristin Taner</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Chief Marke…</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Opentext</t>
+          <t>Vortex Software Consulting, LLC</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Raju Vedala</t>
+          <t>Mitchell Tauer</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Services Account Execut…</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>CES Business Technologies, LLC</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Asier Vega Sanchez</t>
+          <t>Roxanna Tavares</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Director, Gl…</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Arkyn</t>
+          <t>The Nielsen Company (US), LLC.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Jennifer Veillon</t>
+          <t>Theo Tavrides</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Dir Project Controls</t>
+          <t>Vice Presi…</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Fluor Corporation</t>
+          <t>NTT Data Business Solutions, Inc.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Ajay Reddy Velampudi</t>
+          <t>Jamie Taylor</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Senior VP - Sa…</t>
+          <t>Global VP, Strategic Partnerships</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Miracle Software Systems Inc.</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>William Velastegui</t>
+          <t>Meghan Taylor</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>JEFE DE TI Y PR…</t>
+          <t>Industry Account Ex…</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Plasticaucho Industrial S.A.</t>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Rajiv Vemula</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr"/>
+          <t>Samantha Taylor</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Senior Solutions Account Exec…</t>
+        </is>
+      </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions U.S. Corporat…</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Sundu Venkataramani</t>
+          <t>Sarah Taylor</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Industry Val…</t>
+          <t>Solution Advisor</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>SAP Industries (Washington DC)</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Venkat Venkataramani</t>
+          <t>Jorge Tercero</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>Manager/H…</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Asociacion Mutual Sancor Salud</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Tom Venner-Crysell</t>
+          <t>Michael Teti</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ERPeople Solutions Ltd</t>
+          <t>Carlisle Construction Materials</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Eduardo Vergara</t>
+          <t>Suji Thampi</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Agrosuper S.A.</t>
+          <t>MINDSPRINT PTE. LTD.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Amit Verma</t>
+          <t>Le Thanh Phong</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>RVP, Head of CFO Advisory…</t>
+          <t>Managing Direc…</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>FPT Japan Holdings Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Kumar Vidit</t>
+          <t>Michael Theis</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Product Marketing M…</t>
+          <t>Senior Director, Healthcare Life Scien…</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>Icertis</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Lakshmi Vidyashankar</t>
+          <t>Rene Theriault</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>VP of IT</t>
+          <t>IT Program Director</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Marvin Engineering Co., Inc.</t>
+          <t>BRP INC</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Jayant Vikram</t>
+          <t>Barbara Thrasher</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Cloud Delivery Lead</t>
+          <t>SR STAFF ARCHITECT</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Accenture LLP</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Yeni Villanueva</t>
+          <t>Nissim Titan</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Supervisora…</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Compañia Minera Antamina S.A.</t>
+          <t>4CAST SYSTEMS LTD</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Robert Vinyard</t>
+          <t>James Tiwari</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>VP and Senior Partner</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Intellioz LLC</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Thomas Vioux</t>
+          <t>Shuhei Toba</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Business Engineering Corporation</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Anil Visal</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
+          <t>John Tocci</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>Cbs Corporate Business Solutions America In…</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Clara Viscido</t>
+          <t>Oliver Toloui</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Consulting Services Director</t>
+          <t>Director - AI…</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>GEONOSIS</t>
+          <t>Ibase Operations Corp Qualitest</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Paulo Vita Vita</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr"/>
+          <t>Ray Toma</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Senior Principal — Global Strategic Initia…</t>
+        </is>
+      </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Ranjan Vitt</t>
+          <t>Yuko Tominaga</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>AI Compliance Governance Program…</t>
+          <t>Research Writer</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Jose Voisin</t>
+          <t>Laura Tozzo</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Global CIO</t>
+          <t>AI Product Lead SAP IBP</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Christina Volk</t>
+          <t>Eero Traagel</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Head of Strate…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>IBM Canada Limited</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Jessica Voyles</t>
+          <t>Adam Trahan</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Account Executive, South</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -5633,301 +5629,301 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Sandeep Vyas</t>
+          <t>Evgeny Treskin</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Solutio…</t>
+          <t>SAP Alliances Director</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Incture Technologies Private Limited</t>
+          <t>Argano</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Thomas von Alm</t>
+          <t>Chetan Tripathi</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>SVP Cross-Solution Services</t>
+          <t>oCFO Adoption expert</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Markus von Quast</t>
+          <t>Seshagiri Tripurana</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Global Head Industry Ecosystem</t>
+          <t>Senior Director</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>TATSUO WATANABE</t>
+          <t>Masaru Tsukahira</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Principal Cons…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>D I SQUARE CORPORATION.</t>
+          <t>TOKYO ELECTRON LIMITED.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Masayuki Wada</t>
+          <t>Lindsay Tucker</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>SVP, Head of Corporate Digit…</t>
+          <t>Solution Consultant</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Fujitsu Limited</t>
+          <t>Docusign</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Stephen Wagenheim</t>
+          <t>Paul Turbes</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Senior Sales Executive - Suppl…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Dallas (Allen)</t>
+          <t>KPMG LLP</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Neha Wahi</t>
+          <t>Treaver Tyler</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Global Alliance Lead</t>
+          <t>Tech…</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>A.T. Kearney, Inc.</t>
+          <t>Meijer Great Lakes Limited Partnership</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Waka Wakabayashi</t>
+          <t>Kotaro Ueda</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Associate Partner</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>KPMG Consulting Co., Ltd.</t>
+          <t>JSUG</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Gustavo Waldfogiel</t>
+          <t>Rajkishore Una</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>LAC HCM Head</t>
+          <t>President/CEO</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>SAP Argentina - Buenos Aires</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Shashikant Walimbe</t>
+          <t>Bala Parameswara Rao Upadhyay…</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Vice President &amp; Global Head -…</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>LTM LIMITED</t>
+          <t>Stefanini, Inc.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Julie Walker</t>
+          <t>Oscar Uribe</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Sr. Director, Enterprise Applicatio…</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Armstrong</t>
+          <t>EDUARDONO S A S</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Rob Wallace</t>
+          <t>SACHIN VAIDYA</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Senior Manager Digital &amp; In…</t>
+          <t>Director - Enterprise Commercial…</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Jaguarlandrover</t>
+          <t>Pfizer, Inc.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Enzhou Wang</t>
+          <t>Jonathan VON RUEDEN</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Chief Technology Officer</t>
+          <t>Chief AI Officer</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>City of Tacoma</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>May Wang</t>
+          <t>Wagner Valentin</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Direc…</t>
+          <t>Director of Regulated Indust…</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
+          <t>SAP Brasil Ltda.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Adam Warner</t>
+          <t>Jorge Valles Velásquez</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Cost Analyst</t>
+          <t>KMMP…</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Marathon Cheese Corporation</t>
+          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Kosuke Watanabe</t>
+          <t>Henri Vallet</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>VP Sales, Americas B2B</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>Mirakl</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Takashi Watanabe</t>
+          <t>Jeff Van Pelt</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>執行役員</t>
+          <t>Founder / Managing Dire…</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>JFE Systems,Inc.</t>
+          <t>Javelin Consulting</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Robert Watson</t>
+          <t>Meredith Van Wyk</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Sr Account Executive</t>
+          <t>Americas Field Partner…</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -5939,912 +5935,1686 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Ashley Waxman</t>
+          <t>Joris Van der Donck</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Strategic Sales Executive</t>
+          <t>Sr Manag…</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Aevitas IT LLC</t>
+          <t>Commscope Connectivity Belgium</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Christy Weaver</t>
+          <t>Vijay Varee</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Global Demand Generation Man…</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Vertex, Inc.</t>
+          <t>Petsmart LLC</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Mike Weaver</t>
+          <t>Suman Varma</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Senior I…</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>True Commerce Inc. TrueCommerce</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Chris Webster</t>
+          <t>Chris Vassalotti</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>SVP IT Strategy &amp; Architecture</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Ahold Delhaize</t>
+          <t>Opentext</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Matt Webster</t>
+          <t>Raju Vedala</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Director of…</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Gardner White Furniture Co., Inc.</t>
+          <t>CES Business Technologies, LLC</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Patrick Weil</t>
+          <t>Asier Vega Sanchez</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Metrie Canada Ltd</t>
+          <t>Arkyn</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Sarah Weiler</t>
+          <t>Jennifer Veillon</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Manager, Busine…</t>
+          <t>Dir Project Controls</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Ball Horticultural Company</t>
+          <t>Fluor Corporation</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Adam Werner</t>
+          <t>Ajay Reddy Velampudi</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>VP, Corporate Technology</t>
+          <t>Senior VP - Sa…</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Crocs, Inc.</t>
+          <t>Miracle Software Systems Inc.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Maddie Werner</t>
+          <t>William Velastegui</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Director of Delivery Solutions</t>
+          <t>JEFE DE TI Y PR…</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Robra IT</t>
+          <t>Plasticaucho Industrial S.A.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Katherine West</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>CX Account Executive</t>
-        </is>
-      </c>
+          <t>Rajiv Vemula</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Anja Wettling</t>
+          <t>Sundu Venkataramani</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Industry Val…</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>anuwo GmbH</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Charleen Wetzstein</t>
+          <t>Venkat Venkataramani</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>SAP Principal Architect</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>PROSPECTOR, LLC</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Peter Wheatley</t>
+          <t>Tom Venner-Crysell</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Enterprise Architect…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>SAP America (Houston)</t>
+          <t>ERPeople Solutions Ltd</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Robb White</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr"/>
+          <t>Eduardo Vergara</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Manager/Head of Dept</t>
+        </is>
+      </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+          <t>Agrosuper S.A.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Peter Widmer</t>
+          <t>Amit Verma</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Chief of Staff to the Global Head of S…</t>
+          <t>RVP, Head of CFO Advisory…</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Chad Wiech</t>
+          <t>Kumar Vidit</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Director of Solution…</t>
+          <t>Product Marketing M…</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Chamnida Wijetilleke</t>
+          <t>Lakshmi Vidyashankar</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>VP of IT</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>The Ducats Group LLC</t>
+          <t>Marvin Engineering Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Pete Wilkins</t>
+          <t>Jayant Vikram</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>NA Partner Manager</t>
+          <t>Cloud Delivery Lead</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>Accenture LLP</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Mark Willey</t>
+          <t>Yeni Villanueva</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Vice…</t>
+          <t>Supervisora…</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>Compañia Minera Antamina S.A.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ed Williamson</t>
+          <t>Robert Vinyard</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Client Services Lead</t>
+          <t>VP and Senior Partner</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>XMATERIA LTD</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Monica Willis</t>
+          <t>Thomas Vioux</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>HR Strategy and Value A…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Plano- Legacy West</t>
+          <t>PwC</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Charlotte Wilson</t>
+          <t>Anil Visal</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Senior Manager Strategic Cha…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Direct Energy</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Emily Wisemiller</t>
+          <t>Clara Viscido</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Consulting Services Director</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>GEONOSIS</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Julia Wolfe</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Analyst Relations Manager</t>
-        </is>
-      </c>
+          <t>Paulo Vita Vita</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Jennifer Workman</t>
+          <t>Ranjan Vitt</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Techn…</t>
+          <t>AI Compliance Governance Program…</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Universal Destinations &amp; Experiences</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Steven Wright Wright</t>
+          <t>Jose Voisin</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>VP Sales</t>
+          <t>Global CIO</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Acuiti Labs Limited</t>
+          <t>Carmeuse</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Monty Wurth</t>
+          <t>Christina Volk</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>VP of Operations</t>
+          <t>Head of Strate…</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Optima Consulting L.L.C.</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Brad Wylie</t>
+          <t>Jessica Voyles</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Account Executive, South</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>KAORI YASHIKI</t>
+          <t>Sandeep Vyas</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Business Resear…</t>
+          <t>Solutio…</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services LLC</t>
+          <t>Incture Technologies Private Limited</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>YOUNGHO YOO</t>
+          <t>Thomas von Alm</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Team Leader</t>
+          <t>SVP Cross-Solution Services</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>LG CNS Co., Ltd.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Mohamed YUSUF</t>
+          <t>Markus von Quast</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Head of Integrated Toolchain</t>
+          <t>Global Head Industry Ecosystem</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Hikaru Yafuso</t>
+          <t>TATSUO WATANABE</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Senior Alliance Director</t>
+          <t>Principal Cons…</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>D I SQUARE CORPORATION.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Sonoko Yamamoto</t>
+          <t>Masayuki Wada</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Partner Business Manager</t>
+          <t>SVP, Head of Corporate Digit…</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>Fujitsu Limited</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Osamu Yamazaki</t>
+          <t>Stephen Wagenheim</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Co…</t>
+          <t>Senior Sales Executive - Suppl…</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+          <t>Dallas (Allen)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Kenji Yanagi</t>
+          <t>Neha Wahi</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Group Leader</t>
+          <t>Global Alliance Lead</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>ASAHI GROUP JAPAN, LTD.</t>
+          <t>A.T. Kearney, Inc.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>EJ Yang</t>
+          <t>Waka Wakabayashi</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>IT Deputy Director</t>
+          <t>Associate Partner</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>MediaTek Inc.</t>
+          <t>KPMG Consulting Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Kiran Yarlagadda Yarlagadda</t>
+          <t>Gustavo Waldfogiel</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Managing…</t>
+          <t>LAC HCM Head</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Adroix Corp DBA CodeForce 360</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Takayuki Yasuda</t>
+          <t>Shashikant Walimbe</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>Vice President &amp; Global Head -…</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>JFE Systems, Inc.</t>
+          <t>LTM LIMITED</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Tomoki Yasuda</t>
+          <t>Julie Walker</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>AssistantMana…</t>
+          <t>Sr. Director, Enterprise Applicatio…</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>NTT DATA Japan Corporation</t>
+          <t>Armstrong</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Kazuhiro Yonekawa</t>
+          <t>Rob Wallace</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Chief/Proj…</t>
+          <t>Senior Manager Digital &amp; In…</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>CANON MARKETING JAPAN INC.,</t>
+          <t>Jaguarlandrover</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Sungeui Yoon</t>
+          <t>Enzhou Wang</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Senior Specialist</t>
+          <t>Chief Technology Officer</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>City of Tacoma</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Christopher Yope</t>
+          <t>May Wang</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>SAP Supply C…</t>
+          <t>Direc…</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>DXC Technology Services LLC</t>
+          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Kohei Yoshimatsu</t>
+          <t>Adam Warner</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cost Analyst</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>アズビル株式会社</t>
+          <t>Marathon Cheese Corporation</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>taichi yoshida</t>
+          <t>Kosuke Watanabe</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Senior Ma…</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>BENIC SOLUTION CORPORATION</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>nakajima yuki</t>
+          <t>Takashi Watanabe</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>執行役員</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Nitori Co., Ltd.</t>
+          <t>JFE Systems,Inc.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Stefan Zach</t>
+          <t>Robert Watson</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>VP Global IT</t>
+          <t>Sr Account Executive</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Wieland Group</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Beau Zaremski</t>
+          <t>Ashley Waxman</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>VP of Sales</t>
+          <t>Strategic Sales Executive</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Aevitas IT LLC</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Yuan Zhang</t>
+          <t>Christy Weaver</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Senior Project Manager, SAP AI RIG</t>
+          <t>Global Demand Generation Man…</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Vertex, Inc.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Cathy Zhou</t>
+          <t>Mike Weaver</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>IT Director, EBS</t>
+          <t>Senior I…</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>True Commerce Inc. TrueCommerce</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Gustavo Zintak</t>
+          <t>Chris Webster</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>SVP IT Strategy &amp; Architecture</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>SWISS MEDICAL S.A.</t>
+          <t>Ahold Delhaize</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Alina Zuberi</t>
+          <t>Matt Webster</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Global Content Strategist</t>
+          <t>Director of…</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>Gardner White Furniture Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Yoshiaki Agata 縣</t>
+          <t>Patrick Weil</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>AJS株式会社</t>
+          <t>Metrie Canada Ltd</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>裕紀 阿保</t>
+          <t>Sarah Weiler</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Manager, Busine…</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FORTIENCE CONSULTING INC.</t>
+          <t>Ball Horticultural Company</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
+          <t>Adam Werner</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>VP, Corporate Technology</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Crocs, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Maddie Werner</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Director of Delivery Solutions</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Robra IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Katherine West</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>CX Account Executive</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Anja Wettling</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>anuwo GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Charleen Wetzstein</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SAP Principal Architect</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>PROSPECTOR, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Peter Wheatley</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Enterprise Architect…</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>SAP America (Houston)</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Robb White</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Peter Widmer</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Chief of Staff to the Global Head of S…</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Chad Wiech</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Director of Solution…</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Pittsburgh, SAP America</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Chamnida Wijetilleke</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>The Ducats Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Pete Wilkins</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>NA Partner Manager</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>SAP America(Bellevue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Mark Willey</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Vice…</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Ed Williamson</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Client Services Lead</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>XMATERIA LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Monica Willis</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>HR Strategy and Value A…</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Plano- Legacy West</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Charlotte Wilson</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Senior Manager Strategic Cha…</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Direct Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Emily Wisemiller</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Molex</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Julia Wolfe</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Analyst Relations Manager</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Jennifer Workman</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Techn…</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Universal Destinations &amp; Experiences</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Steven Wright Wright</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>VP Sales</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Acuiti Labs Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Monty Wurth</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>VP of Operations</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Optima Consulting L.L.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Brad Wylie</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>KAORI YASHIKI</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Business Resear…</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Hitachi Digital Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>YOUNGHO YOO</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Team Leader</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>LG CNS Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Mohamed YUSUF</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Head of Integrated Toolchain</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Hikaru Yafuso</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Senior Alliance Director</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Sonoko Yamamoto</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Partner Business Manager</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Osamu Yamazaki</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Co…</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Kenji Yanagi</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Group Leader</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>ASAHI GROUP JAPAN, LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>EJ Yang</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>IT Deputy Director</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>MediaTek Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Kiran Yarlagadda Yarlagadda</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Managing…</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Adroix Corp DBA CodeForce 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Takayuki Yasuda</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>JFE Systems, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Tomoki Yasuda</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>AssistantMana…</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>NTT DATA Japan Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Kazuhiro Yonekawa</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Chief/Proj…</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>CANON MARKETING JAPAN INC.,</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Sungeui Yoon</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Senior Specialist</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Christopher Yope</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>SAP Supply C…</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>DXC Technology Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Kohei Yoshimatsu</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>アズビル株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>taichi yoshida</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Senior Ma…</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>BENIC SOLUTION CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>nakajima yuki</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Nitori Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Stefan Zach</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>VP Global IT</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Wieland Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Beau Zaremski</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Yuan Zhang</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Senior Project Manager, SAP AI RIG</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Cathy Zhou</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>IT Director, EBS</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Ecolab Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Gustavo Zintak</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Manager/Head of Dept</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>SWISS MEDICAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Alina Zuberi</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Global Content Strategist</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Yoshiaki Agata 縣</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>AJS株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>裕紀 阿保</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>FORTIENCE CONSULTING INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
           <t>謙介 青木</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
+      <c r="B426" t="inlineStr">
         <is>
           <t>Manager, Uvance Market Developme…</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
+      <c r="C426" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C426"/>
+  <dimension ref="A1:C437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4285,493 +4285,497 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Sukhbir Singh</t>
+          <t>Olga Shumikhina</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>S…</t>
+          <t>Umoja HCM Team Lead</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>The School Board of Duval County Florida</t>
+          <t>The United Nations</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Vikrant Sisodia</t>
+          <t>Andrew Sigler</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Sr. Product Manager</t>
+          <t>Account Director</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>Syntax Systems USA LP</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>David Smith</t>
+          <t>Mikolaj Sikorski</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>VP, Chief Enterprise Ar…</t>
+          <t>Strategic Partner Initiatives</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SAP America (Reston)</t>
+          <t>SAP Ireland Ltd.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Rachel Smith</t>
+          <t>Jonathan Silva</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Partner Sales Manager</t>
+          <t>Instituição de Pagament…</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Docusign Inc</t>
+          <t>Nu Pagamentos S.A</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Mark Smysor</t>
+          <t>Renato Silva</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Business Systems Analyst in Enterpri…</t>
+          <t>Solutions Sa…</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Globant Brasil Consultoria Ltda</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Delaiah Snowden</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>IT Ana…</t>
-        </is>
-      </c>
+          <t>Sergei Silva</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
-          <t>South Florida Water Management Dist</t>
+          <t>Vistex</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Jairo Soares De Matos</t>
+          <t>Felix Silvagnoli</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Analyst - SAP Busi…</t>
+          <t>SAP Platform Owner</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Canadian Blood Services</t>
+          <t>BP International Limited</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Michael Somerville</t>
+          <t>Gianluca Simeone</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Sales Executive</t>
+          <t>Global SAP CTIO &amp; AI Leader</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Checkout.com</t>
+          <t>Capgemini</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>YoonWon Song</t>
+          <t>Cintia Simonelli</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Managing Part…</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>i-SENS, Inc.</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Dag Terje Sorlie</t>
+          <t>Eric Simonson</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Director - Product Marke…</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Thiago Souza</t>
+          <t>Natalie Singh</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>IT CO…</t>
+          <t>Global Strategic Scale L…</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>MINERACAO SERRAS DO OESTE LTDA</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Meik Spanowsky</t>
+          <t>Sukhbir Singh</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>S…</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>The School Board of Duval County Florida</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Thorsten Spihlmann</t>
+          <t>Vikrant Sisodia</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Head of Business Development for T…</t>
+          <t>Sr. Product Manager</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TD Srinivasan</t>
+          <t>David Smith</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Industry…</t>
+          <t>VP, Chief Enterprise Ar…</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SAP Public Services, Inc. (Hudson Y</t>
+          <t>SAP America (Reston)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Mike Stafford</t>
+          <t>Rachel Smith</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Senior ABAP Developer</t>
+          <t>Partner Sales Manager</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Titan Ventures LLC</t>
+          <t>Docusign Inc</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Jennifer Stapleton</t>
+          <t>Mark Smysor</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>VP of Accounting Strategy &amp;…</t>
+          <t>Business Systems Analyst in Enterpri…</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>American Equity</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>John Stark</t>
+          <t>Delaiah Snowden</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Global Head of SAP Alliance</t>
+          <t>IT Ana…</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Loftware</t>
+          <t>South Florida Water Management Dist</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Denis Staudt</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr"/>
+          <t>Jairo Soares De Matos</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Analyst - SAP Busi…</t>
+        </is>
+      </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
+          <t>Canadian Blood Services</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Maximilian Stein</t>
+          <t>Michael Somerville</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SAP Product Owner - Treasury CPIT</t>
+          <t>Sales Executive</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Checkout.com</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Amanda Steiner</t>
+          <t>YoonWon Song</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Business Process Architect</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>i-SENS, Inc.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Dieter Steinmann</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr"/>
+          <t>Dag Terje Sorlie</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Jorrit Steinz</t>
+          <t>Thiago Souza</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>IT CO…</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ChannelEngine.com</t>
+          <t>MINERACAO SERRAS DO OESTE LTDA</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Robert Stemmler</t>
+          <t>Meik Spanowsky</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Global Alliances &amp; Ec…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Yonathan Stephanos</t>
+          <t>Thorsten Spihlmann</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SAP Data &amp; AI Business Group Le…</t>
+          <t>Head of Business Development for T…</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Patrick Stewart</t>
+          <t>TD Srinivasan</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Industry…</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>SAP Public Services, Inc. (Hudson Y</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Jochen Stiebe</t>
+          <t>Mike Stafford</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Head of Sales Treas…</t>
+          <t>Senior ABAP Developer</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Target-Networks GmbH</t>
+          <t>Titan Ventures LLC</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Leslie Stoffel</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr"/>
+          <t>Jennifer Stapleton</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>VP of Accounting Strategy &amp;…</t>
+        </is>
+      </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
+          <t>American Equity</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Miodrag Stojanov</t>
+          <t>John Stark</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Lead Engineer</t>
+          <t>Global Head of SAP Alliance</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>SEMOS SOFTWARE LLC</t>
+          <t>Loftware</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Bojana Stojanovich</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>VP, NA Strategic Partnerships</t>
-        </is>
-      </c>
+          <t>Denis Staudt</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Tricentis</t>
+          <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Seda Strate</t>
+          <t>Maximilian Stein</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Partner Innovation Lead</t>
+          <t>SAP Product Owner - Treasury CPIT</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -4783,454 +4787,446 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Divya Struebing</t>
+          <t>Amanda Steiner</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Supply Chain Customer…</t>
+          <t>Business Process Architect</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>McKesson</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Kevin Stupp</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Director S4 Platform</t>
-        </is>
-      </c>
+          <t>Dieter Steinmann</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Harish Subramanian</t>
+          <t>Jorrit Steinz</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Principal Enterprise Arch…</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>ChannelEngine.com</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Marc Sudjian</t>
+          <t>Robert Stemmler</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Enterprise Architect, SAP So…</t>
+          <t>Global Alliances &amp; Ec…</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bombardier Inc.</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Hirofumi Sugimoto</t>
+          <t>Yonathan Stephanos</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>SAP Data &amp; AI Business Group Le…</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ABeam Systems Ltd.</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Michael Sukachev</t>
+          <t>Patrick Stewart</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Sr. EA</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Teranet Inc</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Som Suresh</t>
+          <t>Jochen Stiebe</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Man…</t>
+          <t>Head of Sales Treas…</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>Target-Networks GmbH</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Jain Sushant</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Chief Revenue Officer, F&amp;S…</t>
-        </is>
-      </c>
+          <t>Leslie Stoffel</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Scott Sutker</t>
+          <t>Miodrag Stojanov</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Vice President Customer Success…</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Alpharetta</t>
+          <t>SEMOS SOFTWARE LLC</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Mergenthaler Sven</t>
+          <t>Bojana Stojanovich</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Global Head of Strategic Central Ser…</t>
+          <t>VP, NA Strategic Partnerships</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Tricentis</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Jereme Swoboda</t>
+          <t>Seda Strate</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Segment Director</t>
+          <t>Partner Innovation Lead</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Avvale, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Debra Syring</t>
+          <t>Divya Struebing</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Senior IT Manager</t>
+          <t>Supply Chain Customer…</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Entegris, Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Kai Szatkowski</t>
+          <t>Kevin Stupp</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Head of Product Sales</t>
+          <t>Director S4 Platform</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Natuvion GmbH</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MARCO TOMBOLINI</t>
+          <t>Harish Subramanian</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Global He…</t>
+          <t>Principal Enterprise Arch…</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>DOLCE &amp; GABBANA BEAUTY SRL</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>KAZUSHI TOYOMASU</t>
+          <t>Marc Sudjian</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Global Direct…</t>
+          <t>Enterprise Architect, SAP So…</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>MOL Chemical Tankers Pte Ltd</t>
+          <t>Bombardier Inc.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Stacey Taborelli</t>
+          <t>Hirofumi Sugimoto</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Executive Business Partn…</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>ABeam Systems Ltd.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Ahmed Taher</t>
+          <t>Michael Sukachev</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Sr. EA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Al Daajan Trading</t>
+          <t>Teranet Inc</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Chieko Takahata</t>
+          <t>Som Suresh</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Chief</t>
+          <t>Man…</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>BROTHER INDUSTRIES,LTD.</t>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Arai Takahiro</t>
+          <t>Jain Sushant</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Services Delivery Manag…</t>
+          <t>Chief Revenue Officer, F&amp;S…</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Eiji Takashina</t>
+          <t>Scott Sutker</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Associate Director</t>
+          <t>Vice President Customer Success…</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Kyndryl Japan KK</t>
+          <t>Alpharetta</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Tetsushi Takino</t>
+          <t>Mergenthaler Sven</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Global Head of Strategic Central Ser…</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>大和ハウス工業株式会社</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Makoto Tamura</t>
+          <t>Jereme Swoboda</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Alliance Group Director</t>
+          <t>Segment Director</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>FUJITSU LIMITED</t>
+          <t>Avvale, Inc.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Chiyuki Tanaka</t>
+          <t>Debra Syring</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Team leader</t>
+          <t>Senior IT Manager</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Recruit Co., Ltd.</t>
+          <t>Entegris, Inc.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Steve Tanaka</t>
+          <t>Kai Szatkowski</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Sr Vice Presid…</t>
+          <t>Head of Product Sales</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Blommer Chocolate Company</t>
+          <t>Natuvion GmbH</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Yasuhiro Tanaka</t>
+          <t>MARCO TOMBOLINI</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Global He…</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Recuruit Co.,Ltd.</t>
+          <t>DOLCE &amp; GABBANA BEAUTY SRL</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Kristin Taner</t>
+          <t>KAZUSHI TOYOMASU</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Chief Marke…</t>
+          <t>Global Direct…</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Vortex Software Consulting, LLC</t>
+          <t>MOL Chemical Tankers Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Mitchell Tauer</t>
+          <t>Stacey Taborelli</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Services Account Execut…</t>
+          <t>Executive Business Partn…</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -5242,2379 +5238,2566 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Roxanna Tavares</t>
+          <t>Ahmed Taher</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Director, Gl…</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>The Nielsen Company (US), LLC.</t>
+          <t>Al Daajan Trading</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Theo Tavrides</t>
+          <t>Chieko Takahata</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Vice Presi…</t>
+          <t>Chief</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>NTT Data Business Solutions, Inc.</t>
+          <t>BROTHER INDUSTRIES,LTD.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Jamie Taylor</t>
+          <t>Arai Takahiro</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Global VP, Strategic Partnerships</t>
+          <t>Services Delivery Manag…</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Meghan Taylor</t>
+          <t>Eiji Takashina</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Industry Account Ex…</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>Kyndryl Japan KK</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Samantha Taylor</t>
+          <t>Tetsushi Takino</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Senior Solutions Account Exec…</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>大和ハウス工業株式会社</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Sarah Taylor</t>
+          <t>Makoto Tamura</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Solution Advisor</t>
+          <t>Alliance Group Director</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>FUJITSU LIMITED</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Jorge Tercero</t>
+          <t>Chiyuki Tanaka</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Manager/H…</t>
+          <t>Team leader</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Asociacion Mutual Sancor Salud</t>
+          <t>Recruit Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Michael Teti</t>
+          <t>Steve Tanaka</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Sr Vice Presid…</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Carlisle Construction Materials</t>
+          <t>Blommer Chocolate Company</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Suji Thampi</t>
+          <t>Yasuhiro Tanaka</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>MINDSPRINT PTE. LTD.</t>
+          <t>Recuruit Co.,Ltd.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Le Thanh Phong</t>
+          <t>Kristin Taner</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Managing Direc…</t>
+          <t>Chief Marke…</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>FPT Japan Holdings Co., Ltd.</t>
+          <t>Vortex Software Consulting, LLC</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Michael Theis</t>
+          <t>Mitchell Tauer</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Senior Director, Healthcare Life Scien…</t>
+          <t>Services Account Execut…</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Icertis</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Rene Theriault</t>
+          <t>Roxanna Tavares</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>IT Program Director</t>
+          <t>Director, Gl…</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>BRP INC</t>
+          <t>The Nielsen Company (US), LLC.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Barbara Thrasher</t>
+          <t>Theo Tavrides</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>SR STAFF ARCHITECT</t>
+          <t>Vice Presi…</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Tyson Foods, Inc.</t>
+          <t>NTT Data Business Solutions, Inc.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Nissim Titan</t>
+          <t>Jamie Taylor</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Global VP, Strategic Partnerships</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>4CAST SYSTEMS LTD</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>James Tiwari</t>
+          <t>Meghan Taylor</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Industry Account Ex…</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Intellioz LLC</t>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Shuhei Toba</t>
+          <t>Samantha Taylor</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Senior Solutions Account Exec…</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Business Engineering Corporation</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>John Tocci</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr"/>
+          <t>Sarah Taylor</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Solution Advisor</t>
+        </is>
+      </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Cbs Corporate Business Solutions America In…</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Oliver Toloui</t>
+          <t>Jorge Tercero</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Director - AI…</t>
+          <t>Manager/H…</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Ibase Operations Corp Qualitest</t>
+          <t>Asociacion Mutual Sancor Salud</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ray Toma</t>
+          <t>Michael Teti</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Senior Principal — Global Strategic Initia…</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Carlisle Construction Materials</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Yuko Tominaga</t>
+          <t>Suji Thampi</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Research Writer</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>MINDSPRINT PTE. LTD.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Laura Tozzo</t>
+          <t>Le Thanh Phong</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>AI Product Lead SAP IBP</t>
+          <t>Managing Direc…</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>FPT Japan Holdings Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Eero Traagel</t>
+          <t>Michael Theis</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Senior Director, Healthcare Life Scien…</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>IBM Canada Limited</t>
+          <t>Icertis</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Adam Trahan</t>
+          <t>Rene Theriault</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>IT Program Director</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>BRP INC</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Evgeny Treskin</t>
+          <t>Barbara Thrasher</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>SAP Alliances Director</t>
+          <t>SR STAFF ARCHITECT</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Chetan Tripathi</t>
+          <t>Nissim Titan</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>oCFO Adoption expert</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>4CAST SYSTEMS LTD</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Seshagiri Tripurana</t>
+          <t>James Tiwari</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Senior Director</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Intellioz LLC</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Masaru Tsukahira</t>
+          <t>Shuhei Toba</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>TOKYO ELECTRON LIMITED.</t>
+          <t>Business Engineering Corporation</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Lindsay Tucker</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Solution Consultant</t>
-        </is>
-      </c>
+          <t>John Tocci</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Docusign</t>
+          <t>Cbs Corporate Business Solutions America In…</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Paul Turbes</t>
+          <t>Oliver Toloui</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Director - AI…</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>KPMG LLP</t>
+          <t>Ibase Operations Corp Qualitest</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Treaver Tyler</t>
+          <t>Ray Toma</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Tech…</t>
+          <t>Senior Principal — Global Strategic Initia…</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Meijer Great Lakes Limited Partnership</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Kotaro Ueda</t>
+          <t>Yuko Tominaga</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Research Writer</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>JSUG</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Rajkishore Una</t>
+          <t>Laura Tozzo</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>President/CEO</t>
+          <t>AI Product Lead SAP IBP</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>GyanSys, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Bala Parameswara Rao Upadhyay…</t>
+          <t>Eero Traagel</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Associate Director</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Stefanini, Inc.</t>
+          <t>IBM Canada Limited</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Oscar Uribe</t>
+          <t>Adam Trahan</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>EDUARDONO S A S</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>SACHIN VAIDYA</t>
+          <t>Evgeny Treskin</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Director - Enterprise Commercial…</t>
+          <t>SAP Alliances Director</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Pfizer, Inc.</t>
+          <t>Argano</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Jonathan VON RUEDEN</t>
+          <t>Chetan Tripathi</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Chief AI Officer</t>
+          <t>oCFO Adoption expert</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Wagner Valentin</t>
+          <t>Seshagiri Tripurana</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Director of Regulated Indust…</t>
+          <t>Senior Director</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>SAP Brasil Ltda.</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Jorge Valles Velásquez</t>
+          <t>Masaru Tsukahira</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>KMMP…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
+          <t>TOKYO ELECTRON LIMITED.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Henri Vallet</t>
+          <t>Lindsay Tucker</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>VP Sales, Americas B2B</t>
+          <t>Solution Consultant</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Mirakl</t>
+          <t>Docusign</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Jeff Van Pelt</t>
+          <t>Paul Turbes</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Founder / Managing Dire…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Javelin Consulting</t>
+          <t>KPMG LLP</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Meredith Van Wyk</t>
+          <t>Treaver Tyler</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Americas Field Partner…</t>
+          <t>Tech…</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Meijer Great Lakes Limited Partnership</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Joris Van der Donck</t>
+          <t>Kotaro Ueda</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Sr Manag…</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Commscope Connectivity Belgium</t>
+          <t>JSUG</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Vijay Varee</t>
+          <t>Rajkishore Una</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>President/CEO</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Petsmart LLC</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Suman Varma</t>
+          <t>Bala Parameswara Rao Upadhyay…</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Stefanini, Inc.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Chris Vassalotti</t>
+          <t>Oscar Uribe</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Opentext</t>
+          <t>EDUARDONO S A S</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Raju Vedala</t>
+          <t>SACHIN VAIDYA</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Director - Enterprise Commercial…</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>CES Business Technologies, LLC</t>
+          <t>Pfizer, Inc.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Asier Vega Sanchez</t>
+          <t>Jonathan VON RUEDEN</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Chief AI Officer</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Arkyn</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Jennifer Veillon</t>
+          <t>Wagner Valentin</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Dir Project Controls</t>
+          <t>Director of Regulated Indust…</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Fluor Corporation</t>
+          <t>SAP Brasil Ltda.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Ajay Reddy Velampudi</t>
+          <t>Jorge Valles Velásquez</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Senior VP - Sa…</t>
+          <t>KMMP…</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Miracle Software Systems Inc.</t>
+          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>William Velastegui</t>
+          <t>Henri Vallet</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>JEFE DE TI Y PR…</t>
+          <t>VP Sales, Americas B2B</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Plasticaucho Industrial S.A.</t>
+          <t>Mirakl</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Rajiv Vemula</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr"/>
+          <t>Jeff Van Pelt</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Founder / Managing Dire…</t>
+        </is>
+      </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions U.S. Corporat…</t>
+          <t>Javelin Consulting</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Sundu Venkataramani</t>
+          <t>Meredith Van Wyk</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Industry Val…</t>
+          <t>Americas Field Partner…</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>SAP Industries (Washington DC)</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Venkat Venkataramani</t>
+          <t>Joris Van der Donck</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>Sr Manag…</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Commscope Connectivity Belgium</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Tom Venner-Crysell</t>
+          <t>Vijay Varee</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>ERPeople Solutions Ltd</t>
+          <t>Petsmart LLC</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Eduardo Vergara</t>
+          <t>Suman Varma</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Agrosuper S.A.</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Amit Verma</t>
+          <t>Chris Vassalotti</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>RVP, Head of CFO Advisory…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>Opentext</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Kumar Vidit</t>
+          <t>Raju Vedala</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Product Marketing M…</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>CES Business Technologies, LLC</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Lakshmi Vidyashankar</t>
+          <t>Asier Vega Sanchez</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>VP of IT</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Marvin Engineering Co., Inc.</t>
+          <t>Arkyn</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Jayant Vikram</t>
+          <t>Jennifer Veillon</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Cloud Delivery Lead</t>
+          <t>Dir Project Controls</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Accenture LLP</t>
+          <t>Fluor Corporation</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Yeni Villanueva</t>
+          <t>Ajay Reddy Velampudi</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Supervisora…</t>
+          <t>Senior VP - Sa…</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Compañia Minera Antamina S.A.</t>
+          <t>Miracle Software Systems Inc.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Robert Vinyard</t>
+          <t>William Velastegui</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>VP and Senior Partner</t>
+          <t>JEFE DE TI Y PR…</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Plasticaucho Industrial S.A.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Thomas Vioux</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
+          <t>Rajiv Vemula</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Anil Visal</t>
+          <t>Sundu Venkataramani</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Industry Val…</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Clara Viscido</t>
+          <t>Venkat Venkataramani</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Consulting Services Director</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>GEONOSIS</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Paulo Vita Vita</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr"/>
+          <t>Tom Venner-Crysell</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
+          <t>ERPeople Solutions Ltd</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Ranjan Vitt</t>
+          <t>Eduardo Vergara</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>AI Compliance Governance Program…</t>
+          <t>Manager/Head of Dept</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Agrosuper S.A.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Jose Voisin</t>
+          <t>Amit Verma</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Global CIO</t>
+          <t>RVP, Head of CFO Advisory…</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Christina Volk</t>
+          <t>Kumar Vidit</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Head of Strate…</t>
+          <t>Product Marketing M…</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Jessica Voyles</t>
+          <t>Lakshmi Vidyashankar</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Account Executive, South</t>
+          <t>VP of IT</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Marvin Engineering Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Sandeep Vyas</t>
+          <t>Jayant Vikram</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Solutio…</t>
+          <t>Cloud Delivery Lead</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Incture Technologies Private Limited</t>
+          <t>Accenture LLP</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Thomas von Alm</t>
+          <t>Yeni Villanueva</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>SVP Cross-Solution Services</t>
+          <t>Supervisora…</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Compañia Minera Antamina S.A.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Markus von Quast</t>
+          <t>Robert Vinyard</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Global Head Industry Ecosystem</t>
+          <t>VP and Senior Partner</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>TATSUO WATANABE</t>
+          <t>Thomas Vioux</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Principal Cons…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>D I SQUARE CORPORATION.</t>
+          <t>PwC</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Masayuki Wada</t>
+          <t>Anil Visal</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SVP, Head of Corporate Digit…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Fujitsu Limited</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Stephen Wagenheim</t>
+          <t>Clara Viscido</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Senior Sales Executive - Suppl…</t>
+          <t>Consulting Services Director</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Dallas (Allen)</t>
+          <t>GEONOSIS</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Neha Wahi</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Global Alliance Lead</t>
-        </is>
-      </c>
+          <t>Paulo Vita Vita</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr">
         <is>
-          <t>A.T. Kearney, Inc.</t>
+          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Waka Wakabayashi</t>
+          <t>Ranjan Vitt</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Associate Partner</t>
+          <t>AI Compliance Governance Program…</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>KPMG Consulting Co., Ltd.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Gustavo Waldfogiel</t>
+          <t>Jose Voisin</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>LAC HCM Head</t>
+          <t>Global CIO</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>SAP Argentina - Buenos Aires</t>
+          <t>Carmeuse</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Shashikant Walimbe</t>
+          <t>Christina Volk</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Vice President &amp; Global Head -…</t>
+          <t>Head of Strate…</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>LTM LIMITED</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Julie Walker</t>
+          <t>Jessica Voyles</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Sr. Director, Enterprise Applicatio…</t>
+          <t>Account Executive, South</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Armstrong</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Rob Wallace</t>
+          <t>Sandeep Vyas</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Senior Manager Digital &amp; In…</t>
+          <t>Solutio…</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Jaguarlandrover</t>
+          <t>Incture Technologies Private Limited</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Enzhou Wang</t>
+          <t>Thomas von Alm</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Chief Technology Officer</t>
+          <t>SVP Cross-Solution Services</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>City of Tacoma</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>May Wang</t>
+          <t>Markus von Quast</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Direc…</t>
+          <t>Global Head Industry Ecosystem</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Adam Warner</t>
+          <t>TATSUO WATANABE</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Cost Analyst</t>
+          <t>Principal Cons…</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Marathon Cheese Corporation</t>
+          <t>D I SQUARE CORPORATION.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Kosuke Watanabe</t>
+          <t>Masayuki Wada</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>SVP, Head of Corporate Digit…</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>Fujitsu Limited</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Takashi Watanabe</t>
+          <t>Stephen Wagenheim</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>執行役員</t>
+          <t>Senior Sales Executive - Suppl…</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>JFE Systems,Inc.</t>
+          <t>Dallas (Allen)</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Robert Watson</t>
+          <t>Neha Wahi</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Sr Account Executive</t>
+          <t>Global Alliance Lead</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>A.T. Kearney, Inc.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Ashley Waxman</t>
+          <t>Waka Wakabayashi</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Strategic Sales Executive</t>
+          <t>Associate Partner</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Aevitas IT LLC</t>
+          <t>KPMG Consulting Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Christy Weaver</t>
+          <t>Gustavo Waldfogiel</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Global Demand Generation Man…</t>
+          <t>LAC HCM Head</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Vertex, Inc.</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Mike Weaver</t>
+          <t>Shashikant Walimbe</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Senior I…</t>
+          <t>Vice President &amp; Global Head -…</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>True Commerce Inc. TrueCommerce</t>
+          <t>LTM LIMITED</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Chris Webster</t>
+          <t>Julie Walker</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>SVP IT Strategy &amp; Architecture</t>
+          <t>Sr. Director, Enterprise Applicatio…</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Ahold Delhaize</t>
+          <t>Armstrong</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Matt Webster</t>
+          <t>Rob Wallace</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Director of…</t>
+          <t>Senior Manager Digital &amp; In…</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Gardner White Furniture Co., Inc.</t>
+          <t>Jaguarlandrover</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Patrick Weil</t>
+          <t>Enzhou Wang</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Chief Technology Officer</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Metrie Canada Ltd</t>
+          <t>City of Tacoma</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Sarah Weiler</t>
+          <t>May Wang</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Manager, Busine…</t>
+          <t>Direc…</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Ball Horticultural Company</t>
+          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Adam Werner</t>
+          <t>Adam Warner</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>VP, Corporate Technology</t>
+          <t>Cost Analyst</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Crocs, Inc.</t>
+          <t>Marathon Cheese Corporation</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Maddie Werner</t>
+          <t>Kosuke Watanabe</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Director of Delivery Solutions</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Robra IT</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Katherine West</t>
+          <t>Takashi Watanabe</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>CX Account Executive</t>
+          <t>執行役員</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>JFE Systems,Inc.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Anja Wettling</t>
+          <t>Robert Watson</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Sr Account Executive</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>anuwo GmbH</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Charleen Wetzstein</t>
+          <t>Ashley Waxman</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>SAP Principal Architect</t>
+          <t>Strategic Sales Executive</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>PROSPECTOR, LLC</t>
+          <t>Aevitas IT LLC</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Peter Wheatley</t>
+          <t>Christy Weaver</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Enterprise Architect…</t>
+          <t>Global Demand Generation Man…</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>SAP America (Houston)</t>
+          <t>Vertex, Inc.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Robb White</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr"/>
+          <t>Mike Weaver</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Senior I…</t>
+        </is>
+      </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+          <t>True Commerce Inc. TrueCommerce</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Peter Widmer</t>
+          <t>Chris Webster</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Chief of Staff to the Global Head of S…</t>
+          <t>SVP IT Strategy &amp; Architecture</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Ahold Delhaize</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Chad Wiech</t>
+          <t>Matt Webster</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Director of Solution…</t>
+          <t>Director of…</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>Gardner White Furniture Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Chamnida Wijetilleke</t>
+          <t>Patrick Weil</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>The Ducats Group LLC</t>
+          <t>Metrie Canada Ltd</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Pete Wilkins</t>
+          <t>Sarah Weiler</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>NA Partner Manager</t>
+          <t>Manager, Busine…</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>Ball Horticultural Company</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Mark Willey</t>
+          <t>Adam Werner</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Vice…</t>
+          <t>VP, Corporate Technology</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>Crocs, Inc.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Ed Williamson</t>
+          <t>Maddie Werner</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Client Services Lead</t>
+          <t>Director of Delivery Solutions</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>XMATERIA LTD</t>
+          <t>Robra IT</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Monica Willis</t>
+          <t>Katherine West</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>HR Strategy and Value A…</t>
+          <t>CX Account Executive</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Plano- Legacy West</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Charlotte Wilson</t>
+          <t>Anja Wettling</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Senior Manager Strategic Cha…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Direct Energy</t>
+          <t>anuwo GmbH</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Emily Wisemiller</t>
+          <t>Charleen Wetzstein</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>SAP Principal Architect</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>PROSPECTOR, LLC</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Julia Wolfe</t>
+          <t>Peter Wheatley</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Analyst Relations Manager</t>
+          <t>Enterprise Architect…</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SAP America (Houston)</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Jennifer Workman</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>Techn…</t>
-        </is>
-      </c>
+          <t>Robb White</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Universal Destinations &amp; Experiences</t>
+          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Steven Wright Wright</t>
+          <t>Peter Widmer</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>VP Sales</t>
+          <t>Chief of Staff to the Global Head of S…</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Acuiti Labs Limited</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Monty Wurth</t>
+          <t>Chad Wiech</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>VP of Operations</t>
+          <t>Director of Solution…</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Optima Consulting L.L.C.</t>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Brad Wylie</t>
+          <t>Chamnida Wijetilleke</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>The Ducats Group LLC</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>KAORI YASHIKI</t>
+          <t>Pete Wilkins</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Business Resear…</t>
+          <t>NA Partner Manager</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services LLC</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>YOUNGHO YOO</t>
+          <t>Mark Willey</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Team Leader</t>
+          <t>Vice…</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>LG CNS Co., Ltd.</t>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Mohamed YUSUF</t>
+          <t>Ed Williamson</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Head of Integrated Toolchain</t>
+          <t>Client Services Lead</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>XMATERIA LTD</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Hikaru Yafuso</t>
+          <t>Monica Willis</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Senior Alliance Director</t>
+          <t>HR Strategy and Value A…</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Plano- Legacy West</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Sonoko Yamamoto</t>
+          <t>Charlotte Wilson</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Partner Business Manager</t>
+          <t>Senior Manager Strategic Cha…</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>Direct Energy</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Osamu Yamazaki</t>
+          <t>Emily Wisemiller</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Co…</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+          <t>Molex</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Kenji Yanagi</t>
+          <t>Julia Wolfe</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Group Leader</t>
+          <t>Analyst Relations Manager</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>ASAHI GROUP JAPAN, LTD.</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>EJ Yang</t>
+          <t>Jennifer Workman</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>IT Deputy Director</t>
+          <t>Techn…</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>MediaTek Inc.</t>
+          <t>Universal Destinations &amp; Experiences</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Kiran Yarlagadda Yarlagadda</t>
+          <t>Steven Wright Wright</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Managing…</t>
+          <t>VP Sales</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Adroix Corp DBA CodeForce 360</t>
+          <t>Acuiti Labs Limited</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Takayuki Yasuda</t>
+          <t>Monty Wurth</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>VP of Operations</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>JFE Systems, Inc.</t>
+          <t>Optima Consulting L.L.C.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Tomoki Yasuda</t>
+          <t>Brad Wylie</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>AssistantMana…</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>NTT DATA Japan Corporation</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Kazuhiro Yonekawa</t>
+          <t>KAORI YASHIKI</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Chief/Proj…</t>
+          <t>Business Resear…</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>CANON MARKETING JAPAN INC.,</t>
+          <t>Hitachi Digital Services LLC</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Sungeui Yoon</t>
+          <t>YOUNGHO YOO</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Senior Specialist</t>
+          <t>Team Leader</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>LG CNS Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Christopher Yope</t>
+          <t>Mohamed YUSUF</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>SAP Supply C…</t>
+          <t>Head of Integrated Toolchain</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>DXC Technology Services LLC</t>
+          <t>SAP MENA LLC</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Kohei Yoshimatsu</t>
+          <t>Hikaru Yafuso</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Senior Alliance Director</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>アズビル株式会社</t>
+          <t>Databricks</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>taichi yoshida</t>
+          <t>Sonoko Yamamoto</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Senior Ma…</t>
+          <t>Partner Business Manager</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>BENIC SOLUTION CORPORATION</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>nakajima yuki</t>
+          <t>Osamu Yamazaki</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Co…</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Nitori Co., Ltd.</t>
+          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Stefan Zach</t>
+          <t>Kenji Yanagi</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>VP Global IT</t>
+          <t>Group Leader</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Wieland Group</t>
+          <t>ASAHI GROUP JAPAN, LTD.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Beau Zaremski</t>
+          <t>EJ Yang</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>VP of Sales</t>
+          <t>IT Deputy Director</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>MediaTek Inc.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Yuan Zhang</t>
+          <t>Kiran Yarlagadda Yarlagadda</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Senior Project Manager, SAP AI RIG</t>
+          <t>Managing…</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Adroix Corp DBA CodeForce 360</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Cathy Zhou</t>
+          <t>Takayuki Yasuda</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>IT Director, EBS</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>JFE Systems, Inc.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Gustavo Zintak</t>
+          <t>Tomoki Yasuda</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>AssistantMana…</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>SWISS MEDICAL S.A.</t>
+          <t>NTT DATA Japan Corporation</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Alina Zuberi</t>
+          <t>Kazuhiro Yonekawa</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Global Content Strategist</t>
+          <t>Chief/Proj…</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>CANON MARKETING JAPAN INC.,</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Yoshiaki Agata 縣</t>
+          <t>Sungeui Yoon</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>Senior Specialist</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>AJS株式会社</t>
+          <t>Microsoft</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>裕紀 阿保</t>
+          <t>Christopher Yope</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>SAP Supply C…</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>FORTIENCE CONSULTING INC.</t>
+          <t>DXC Technology Services LLC</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
+          <t>Kohei Yoshimatsu</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>アズビル株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>taichi yoshida</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Senior Ma…</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>BENIC SOLUTION CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>nakajima yuki</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Nitori Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Stefan Zach</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>VP Global IT</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Wieland Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Beau Zaremski</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Yuan Zhang</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Senior Project Manager, SAP AI RIG</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Cathy Zhou</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>IT Director, EBS</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Ecolab Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Gustavo Zintak</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Manager/Head of Dept</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>SWISS MEDICAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Alina Zuberi</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Global Content Strategist</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Yoshiaki Agata 縣</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>AJS株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>裕紀 阿保</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>FORTIENCE CONSULTING INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
           <t>謙介 青木</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
+      <c r="B437" t="inlineStr">
         <is>
           <t>Manager, Uvance Market Developme…</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr">
+      <c r="C437" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C437"/>
+  <dimension ref="A1:C493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4285,178 +4285,174 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Olga Shumikhina</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Umoja HCM Team Lead</t>
-        </is>
-      </c>
+          <t>Marco Sanna</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
-          <t>The United Nations</t>
+          <t>cbs Corporate Business Solutions Unternehm…</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Andrew Sigler</t>
+          <t>Rajesh Sarin</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Account Director</t>
+          <t>Global Head - ERP Platf…</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Syntax Systems USA LP</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Mikolaj Sikorski</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Strategic Partner Initiatives</t>
-        </is>
-      </c>
+          <t>Subhayu Sarkar</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SAP Ireland Ltd.</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Jonathan Silva</t>
+          <t>Michael Sass</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Instituição de Pagament…</t>
+          <t>VP, IT</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Nu Pagamentos S.A</t>
+          <t>Alphatec Holdings, Inc.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Renato Silva</t>
+          <t>Yuki Sato</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Solutions Sa…</t>
+          <t>Business Consulting…</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Globant Brasil Consultoria Ltda</t>
+          <t>EY Global Services Ltd</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Sergei Silva</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr"/>
+          <t>Naoya Satomi</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Senior Manager</t>
+        </is>
+      </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Vistex</t>
+          <t>NTT DATA Japan Corporation</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Felix Silvagnoli</t>
+          <t>Klaus-Peter Sauer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SAP Platform Owner</t>
+          <t>Product Manager SAP Business Data…</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>BP International Limited</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Gianluca Simeone</t>
+          <t>Vivek Saurabh</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Global SAP CTIO &amp; AI Leader</t>
+          <t>Director of Business Developm…</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Cintia Simonelli</t>
+          <t>Tom Savoie</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Managing Part…</t>
+          <t>Customer Solution Director</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>SAP Argentina - Buenos Aires</t>
+          <t>EverBlue Partners</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Eric Simonson</t>
+          <t>Andreas Schaefer</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Director - Product Marke…</t>
+          <t>CRO SCM MEE</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Natalie Singh</t>
+          <t>James Scheel</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Global Strategic Scale L…</t>
+          <t>Solution Sales Executive…</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -4468,3336 +4464,4276 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Sukhbir Singh</t>
+          <t>Ralf Scherer</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>S…</t>
+          <t>Global Transfo…</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>The School Board of Duval County Florida</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Vikrant Sisodia</t>
+          <t>Kathrin Schmalzing</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Sr. Product Manager</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>David Smith</t>
+          <t>Brian Schmidt</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>VP, Chief Enterprise Ar…</t>
+          <t>Principal I.T. Architect</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SAP America (Reston)</t>
+          <t>Mckesson</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Rachel Smith</t>
+          <t>Jan Schneider</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Partner Sales Manager</t>
+          <t>GVP Head of AI Partner Ecosystem</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Docusign Inc</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Mark Smysor</t>
+          <t>Rebecca Schneider</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Business Systems Analyst in Enterpri…</t>
+          <t>Project Consultant</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Delaiah Snowden</t>
+          <t>Tonia Schneider</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>IT Ana…</t>
+          <t>Principal Accoun…</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>South Florida Water Management Dist</t>
+          <t>Amazon Web Services, Inc.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Jairo Soares De Matos</t>
+          <t>Pete Scholtens</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Analyst - SAP Busi…</t>
+          <t>Managing Direc…</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Canadian Blood Services</t>
+          <t>Delaware North America LLC</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Michael Somerville</t>
+          <t>Axel Schroeder</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Sales Executive</t>
+          <t>Chief Architect</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Checkout.com</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>YoonWon Song</t>
+          <t>Christoph Schroeder</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Global Head, Industry Business Unit…</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>i-SENS, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Dag Terje Sorlie</t>
+          <t>Carsten Schuetz</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>VP, Global He…</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>SAP Deutschland SE &amp; Co.KG</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Thiago Souza</t>
+          <t>Michael Schultz</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>IT CO…</t>
+          <t>Value Advisor</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>MINERACAO SERRAS DO OESTE LTDA</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Meik Spanowsky</t>
+          <t>Floyd Scott</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Customer Success Ma…</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>LG CNS America, Inc.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Thorsten Spihlmann</t>
+          <t>Cindy Seaburn</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Head of Business Development for T…</t>
+          <t>S…</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>The School Board of Duval County Florida</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TD Srinivasan</t>
+          <t>Kress Sebastian</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Industry…</t>
+          <t>Head of AI, Platforms &amp; Data</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>SAP Public Services, Inc. (Hudson Y</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Mike Stafford</t>
+          <t>Sandeep Sehgal</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Senior ABAP Developer</t>
+          <t>Vice-President, SAP Services</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Titan Ventures LLC</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Jennifer Stapleton</t>
+          <t>Aparna Seksaria</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>VP of Accounting Strategy &amp;…</t>
+          <t>Global Director, Life Sciences IBU</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>American Equity</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>John Stark</t>
+          <t>Sam Seth</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Global Head of SAP Alliance</t>
+          <t>GM Retail, Co…</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Loftware</t>
+          <t>On Demand Technologies, Inc.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Denis Staudt</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr"/>
+          <t>Rahul Sethi</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Sr. Client Advocate</t>
+        </is>
+      </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
+          <t>Corevist Inc</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Maximilian Stein</t>
+          <t>Kanan Sethi Jawa</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SAP Product Owner - Treasury CPIT</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Bombardier Inc.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Amanda Steiner</t>
+          <t>JUAN IGNACIO Sevilla</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Business Process Architect</t>
+          <t>GERENTE DE PRODUCCIÓN</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>plasticaucho</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Dieter Steinmann</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr"/>
+          <t>Harshal Shah</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
+          <t>Elsner Technologies pvt ltd</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Jorrit Steinz</t>
+          <t>Vinay Shah</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Value Advisor</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ChannelEngine.com</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Robert Stemmler</t>
+          <t>Dawn Shakeshaft</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Global Alliances &amp; Ec…</t>
+          <t>Controller</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Associated Feed &amp; Supply Co.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Yonathan Stephanos</t>
+          <t>Aditya Shankar</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SAP Data &amp; AI Business Group Le…</t>
+          <t>Co-fou…</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Sookti AI Innovations Private Limited</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Patrick Stewart</t>
+          <t>Hari Shankar</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Associate Vice Presi…</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Jochen Stiebe</t>
+          <t>Murali Shanmugam</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Head of Sales Treas…</t>
+          <t>Business AI Strategy A…</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Target-Networks GmbH</t>
+          <t>SAP Australia Pty Ltd</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Leslie Stoffel</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr"/>
+          <t>Chris Shano</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Marketing Head,…</t>
+        </is>
+      </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
+          <t>ATOS INTERNATIONAL SAS</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Miodrag Stojanov</t>
+          <t>Ashuka Sharma</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Lead Engineer</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>SEMOS SOFTWARE LLC</t>
+          <t>SAP America Inc. (Hudson Yards)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Bojana Stojanovich</t>
+          <t>Dhruv Sharma</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>VP, NA Strategic Partnerships</t>
+          <t>Assistant Vice Preside…</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Tricentis</t>
+          <t>Celebal Technologies</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Seda Strate</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Partner Innovation Lead</t>
+          <t>Glo…</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SNP TRANSFORMATIONS SEA PTE. LTD.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Divya Struebing</t>
+          <t>Shantanu Sharma</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Supply Chain Customer…</t>
+          <t>Architecture Advisor</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>SAP America (Reston)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Kevin Stupp</t>
+          <t>Suchit Sharma</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Director S4 Platform</t>
+          <t>Assistan…</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Celebal Technologies Americas Inc.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Harish Subramanian</t>
+          <t>Heidi Sheehan</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Principal Enterprise Arch…</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>SAP AMERICA, INC.</t>
-        </is>
-      </c>
+          <t>Vice President, Information Technol…</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Marc Sudjian</t>
+          <t>Anastasiya Shemanskaya</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Enterprise Architect, SAP So…</t>
+          <t>CFO Customer Office</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bombardier Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Hirofumi Sugimoto</t>
+          <t>Sameer Shepal</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Global Lead - SAP…</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ABeam Systems Ltd.</t>
+          <t>Tata Technologies Limited</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Michael Sukachev</t>
+          <t>Colby Sheridan</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Sr. EA</t>
+          <t>Industry Executive Advis…</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Teranet Inc</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Som Suresh</t>
+          <t>Scott Sherman</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Man…</t>
+          <t>SVP Information Te…</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>The Pittsburgh Paints Co.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Jain Sushant</t>
+          <t>Yasuhiro Shibata</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer, F&amp;S…</t>
+          <t>Department Manager</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>JSOL Corporation</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Scott Sutker</t>
+          <t>Allon Shiff Shiff</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Vice President Customer Success…</t>
+          <t>Value Advis…</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Alpharetta</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Mergenthaler Sven</t>
+          <t>Dong Moon Shin</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Global Head of Strategic Central Ser…</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Pan Ocean Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Jereme Swoboda</t>
+          <t>Mary Shinn</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Segment Director</t>
+          <t>Managing Director, SAP K…</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Avvale, Inc.</t>
+          <t>SAP Korea Limited</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Debra Syring</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Senior IT Manager</t>
-        </is>
-      </c>
+          <t>Tomoya Shinozaki</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Entegris, Inc.</t>
+          <t>フォーティエンスコンサルティング株式会社…</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Kai Szatkowski</t>
+          <t>Nobunori Shiono</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Head of Product Sales</t>
+          <t>IT…</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Natuvion GmbH</t>
+          <t>株式会社ベイカレントコンサルティング</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MARCO TOMBOLINI</t>
+          <t>Krista Shirley</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Global He…</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>DOLCE &amp; GABBANA BEAUTY SRL</t>
+          <t>Expand Energy Corporation</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>KAZUSHI TOYOMASU</t>
+          <t>Lisa Shober</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Global Direct…</t>
+          <t>Mana…</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>MOL Chemical Tankers Pte Ltd</t>
+          <t>Air Products and Chemicals, Inc</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Stacey Taborelli</t>
+          <t>Olga Shumikhina</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Executive Business Partn…</t>
+          <t>Umoja HCM Team Lead</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>The United Nations</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ahmed Taher</t>
+          <t>Andrew Sigler</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Account Director</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Al Daajan Trading</t>
+          <t>Syntax Systems USA LP</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Chieko Takahata</t>
+          <t>Mikolaj Sikorski</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Chief</t>
+          <t>Strategic Partner Initiatives</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>BROTHER INDUSTRIES,LTD.</t>
+          <t>SAP Ireland Ltd.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Arai Takahiro</t>
+          <t>Jonathan Silva</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Services Delivery Manag…</t>
+          <t>Instituição de Pagament…</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>Nu Pagamentos S.A</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Eiji Takashina</t>
+          <t>Renato Silva</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Associate Director</t>
+          <t>Solutions Sa…</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Kyndryl Japan KK</t>
+          <t>Globant Brasil Consultoria Ltda</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Tetsushi Takino</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
+          <t>Sergei Silva</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>大和ハウス工業株式会社</t>
+          <t>Vistex</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Makoto Tamura</t>
+          <t>Felix Silvagnoli</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Alliance Group Director</t>
+          <t>SAP Platform Owner</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>FUJITSU LIMITED</t>
+          <t>BP International Limited</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Chiyuki Tanaka</t>
+          <t>Gianluca Simeone</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Team leader</t>
+          <t>Global SAP CTIO &amp; AI Leader</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Recruit Co., Ltd.</t>
+          <t>Capgemini</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Steve Tanaka</t>
+          <t>Cintia Simonelli</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Sr Vice Presid…</t>
+          <t>Managing Part…</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Blommer Chocolate Company</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Yasuhiro Tanaka</t>
+          <t>Eric Simonson</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Director - Product Marke…</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Recuruit Co.,Ltd.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Kristin Taner</t>
+          <t>Natalie Singh</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Chief Marke…</t>
+          <t>Global Strategic Scale L…</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Vortex Software Consulting, LLC</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Mitchell Tauer</t>
+          <t>Sukhbir Singh</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Services Account Execut…</t>
+          <t>S…</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>The School Board of Duval County Florida</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Roxanna Tavares</t>
+          <t>Vikrant Sisodia</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Director, Gl…</t>
+          <t>Sr. Product Manager</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>The Nielsen Company (US), LLC.</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Theo Tavrides</t>
+          <t>David Smith</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Vice Presi…</t>
+          <t>VP, Chief Enterprise Ar…</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>NTT Data Business Solutions, Inc.</t>
+          <t>SAP America (Reston)</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Jamie Taylor</t>
+          <t>Rachel Smith</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Global VP, Strategic Partnerships</t>
+          <t>Partner Sales Manager</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Docusign Inc</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Meghan Taylor</t>
+          <t>Mark Smysor</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Industry Account Ex…</t>
+          <t>Business Systems Analyst in Enterpri…</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Samantha Taylor</t>
+          <t>Delaiah Snowden</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Senior Solutions Account Exec…</t>
+          <t>IT Ana…</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>South Florida Water Management Dist</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Sarah Taylor</t>
+          <t>Jairo Soares De Matos</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Solution Advisor</t>
+          <t>Analyst - SAP Busi…</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Canadian Blood Services</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Jorge Tercero</t>
+          <t>Michael Somerville</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Manager/H…</t>
+          <t>Sales Executive</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Asociacion Mutual Sancor Salud</t>
+          <t>Checkout.com</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Michael Teti</t>
+          <t>YoonWon Song</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Carlisle Construction Materials</t>
+          <t>i-SENS, Inc.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Suji Thampi</t>
+          <t>Dag Terje Sorlie</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>MINDSPRINT PTE. LTD.</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Le Thanh Phong</t>
+          <t>Thiago Souza</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Managing Direc…</t>
+          <t>IT CO…</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>FPT Japan Holdings Co., Ltd.</t>
+          <t>MINERACAO SERRAS DO OESTE LTDA</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Michael Theis</t>
+          <t>Meik Spanowsky</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Senior Director, Healthcare Life Scien…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Icertis</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Rene Theriault</t>
+          <t>Thorsten Spihlmann</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>IT Program Director</t>
+          <t>Head of Business Development for T…</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>BRP INC</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Barbara Thrasher</t>
+          <t>TD Srinivasan</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>SR STAFF ARCHITECT</t>
+          <t>Industry…</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Tyson Foods, Inc.</t>
+          <t>SAP Public Services, Inc. (Hudson Y</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Nissim Titan</t>
+          <t>Mike Stafford</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Senior ABAP Developer</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4CAST SYSTEMS LTD</t>
+          <t>Titan Ventures LLC</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>James Tiwari</t>
+          <t>Jennifer Stapleton</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>VP of Accounting Strategy &amp;…</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Intellioz LLC</t>
+          <t>American Equity</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Shuhei Toba</t>
+          <t>John Stark</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Global Head of SAP Alliance</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Business Engineering Corporation</t>
+          <t>Loftware</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>John Tocci</t>
+          <t>Denis Staudt</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Cbs Corporate Business Solutions America In…</t>
+          <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Oliver Toloui</t>
+          <t>Maximilian Stein</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Director - AI…</t>
+          <t>SAP Product Owner - Treasury CPIT</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Ibase Operations Corp Qualitest</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Ray Toma</t>
+          <t>Amanda Steiner</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Senior Principal — Global Strategic Initia…</t>
+          <t>Business Process Architect</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>McKesson</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Yuko Tominaga</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Research Writer</t>
-        </is>
-      </c>
+          <t>Dieter Steinmann</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Laura Tozzo</t>
+          <t>Jorrit Steinz</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>AI Product Lead SAP IBP</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>ChannelEngine.com</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Eero Traagel</t>
+          <t>Robert Stemmler</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Global Alliances &amp; Ec…</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>IBM Canada Limited</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Adam Trahan</t>
+          <t>Yonathan Stephanos</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>SAP Data &amp; AI Business Group Le…</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Evgeny Treskin</t>
+          <t>Patrick Stewart</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>SAP Alliances Director</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Chetan Tripathi</t>
+          <t>Jochen Stiebe</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>oCFO Adoption expert</t>
+          <t>Head of Sales Treas…</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Target-Networks GmbH</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Seshagiri Tripurana</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Senior Director</t>
-        </is>
-      </c>
+          <t>Leslie Stoffel</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Masaru Tsukahira</t>
+          <t>Miodrag Stojanov</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>TOKYO ELECTRON LIMITED.</t>
+          <t>SEMOS SOFTWARE LLC</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Lindsay Tucker</t>
+          <t>Bojana Stojanovich</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Solution Consultant</t>
+          <t>VP, NA Strategic Partnerships</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Docusign</t>
+          <t>Tricentis</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Paul Turbes</t>
+          <t>Seda Strate</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Partner Innovation Lead</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>KPMG LLP</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Treaver Tyler</t>
+          <t>Divya Struebing</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Tech…</t>
+          <t>Supply Chain Customer…</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Meijer Great Lakes Limited Partnership</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Kotaro Ueda</t>
+          <t>Kevin Stupp</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Director S4 Platform</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>JSUG</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Rajkishore Una</t>
+          <t>Harish Subramanian</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>President/CEO</t>
+          <t>Principal Enterprise Arch…</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>GyanSys, Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Bala Parameswara Rao Upadhyay…</t>
+          <t>Marc Sudjian</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Associate Director</t>
+          <t>Enterprise Architect, SAP So…</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Stefanini, Inc.</t>
+          <t>Bombardier Inc.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Oscar Uribe</t>
+          <t>Hirofumi Sugimoto</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>EDUARDONO S A S</t>
+          <t>ABeam Systems Ltd.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>SACHIN VAIDYA</t>
+          <t>Michael Sukachev</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Director - Enterprise Commercial…</t>
+          <t>Sr. EA</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Pfizer, Inc.</t>
+          <t>Teranet Inc</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Jonathan VON RUEDEN</t>
+          <t>Som Suresh</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Chief AI Officer</t>
+          <t>Man…</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Wagner Valentin</t>
+          <t>Jain Sushant</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Director of Regulated Indust…</t>
+          <t>Chief Revenue Officer, F&amp;S…</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>SAP Brasil Ltda.</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Jorge Valles Velásquez</t>
+          <t>Scott Sutker</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>KMMP…</t>
+          <t>Vice President Customer Success…</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
+          <t>Alpharetta</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Henri Vallet</t>
+          <t>Mergenthaler Sven</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>VP Sales, Americas B2B</t>
+          <t>Global Head of Strategic Central Ser…</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mirakl</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Jeff Van Pelt</t>
+          <t>Jereme Swoboda</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Founder / Managing Dire…</t>
+          <t>Segment Director</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Javelin Consulting</t>
+          <t>Avvale, Inc.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Meredith Van Wyk</t>
+          <t>Debra Syring</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Americas Field Partner…</t>
+          <t>Senior IT Manager</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Entegris, Inc.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Joris Van der Donck</t>
+          <t>Kai Szatkowski</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Sr Manag…</t>
+          <t>Head of Product Sales</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Commscope Connectivity Belgium</t>
+          <t>Natuvion GmbH</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Vijay Varee</t>
+          <t>MARCO TOMBOLINI</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Global He…</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Petsmart LLC</t>
+          <t>DOLCE &amp; GABBANA BEAUTY SRL</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Suman Varma</t>
+          <t>KAZUSHI TOYOMASU</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Global Direct…</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>MOL Chemical Tankers Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Chris Vassalotti</t>
+          <t>Stacey Taborelli</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Executive Business Partn…</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Opentext</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Raju Vedala</t>
+          <t>Ahmed Taher</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>CES Business Technologies, LLC</t>
+          <t>Al Daajan Trading</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Asier Vega Sanchez</t>
+          <t>Chieko Takahata</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Chief</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Arkyn</t>
+          <t>BROTHER INDUSTRIES,LTD.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Jennifer Veillon</t>
+          <t>Arai Takahiro</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Dir Project Controls</t>
+          <t>Services Delivery Manag…</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Fluor Corporation</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Ajay Reddy Velampudi</t>
+          <t>Eiji Takashina</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Senior VP - Sa…</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Miracle Software Systems Inc.</t>
+          <t>Kyndryl Japan KK</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>William Velastegui</t>
+          <t>Tetsushi Takino</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>JEFE DE TI Y PR…</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Plasticaucho Industrial S.A.</t>
+          <t>大和ハウス工業株式会社</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Rajiv Vemula</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr"/>
+          <t>Makoto Tamura</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Alliance Group Director</t>
+        </is>
+      </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions U.S. Corporat…</t>
+          <t>FUJITSU LIMITED</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Sundu Venkataramani</t>
+          <t>Chiyuki Tanaka</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Industry Val…</t>
+          <t>Team leader</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>SAP Industries (Washington DC)</t>
+          <t>Recruit Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Venkat Venkataramani</t>
+          <t>Steve Tanaka</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>Sr Vice Presid…</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Blommer Chocolate Company</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Tom Venner-Crysell</t>
+          <t>Yasuhiro Tanaka</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>ERPeople Solutions Ltd</t>
+          <t>Recuruit Co.,Ltd.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Eduardo Vergara</t>
+          <t>Kristin Taner</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>Chief Marke…</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Agrosuper S.A.</t>
+          <t>Vortex Software Consulting, LLC</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Amit Verma</t>
+          <t>Mitchell Tauer</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>RVP, Head of CFO Advisory…</t>
+          <t>Services Account Execut…</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Kumar Vidit</t>
+          <t>Roxanna Tavares</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Product Marketing M…</t>
+          <t>Director, Gl…</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>The Nielsen Company (US), LLC.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Lakshmi Vidyashankar</t>
+          <t>Theo Tavrides</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>VP of IT</t>
+          <t>Vice Presi…</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Marvin Engineering Co., Inc.</t>
+          <t>NTT Data Business Solutions, Inc.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Jayant Vikram</t>
+          <t>Jamie Taylor</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Cloud Delivery Lead</t>
+          <t>Global VP, Strategic Partnerships</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Accenture LLP</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Yeni Villanueva</t>
+          <t>Meghan Taylor</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Supervisora…</t>
+          <t>Industry Account Ex…</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Compañia Minera Antamina S.A.</t>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Robert Vinyard</t>
+          <t>Samantha Taylor</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>VP and Senior Partner</t>
+          <t>Senior Solutions Account Exec…</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Thomas Vioux</t>
+          <t>Sarah Taylor</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Solution Advisor</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Anil Visal</t>
+          <t>Jorge Tercero</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Manager/H…</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>Asociacion Mutual Sancor Salud</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Clara Viscido</t>
+          <t>Michael Teti</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Consulting Services Director</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>GEONOSIS</t>
+          <t>Carlisle Construction Materials</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Paulo Vita Vita</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr"/>
+          <t>Suji Thampi</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Vice President</t>
+        </is>
+      </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
+          <t>MINDSPRINT PTE. LTD.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ranjan Vitt</t>
+          <t>Le Thanh Phong</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>AI Compliance Governance Program…</t>
+          <t>Managing Direc…</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>FPT Japan Holdings Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Jose Voisin</t>
+          <t>Michael Theis</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Global CIO</t>
+          <t>Senior Director, Healthcare Life Scien…</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>Icertis</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Christina Volk</t>
+          <t>Rene Theriault</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Head of Strate…</t>
+          <t>IT Program Director</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>BRP INC</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Jessica Voyles</t>
+          <t>Barbara Thrasher</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Account Executive, South</t>
+          <t>SR STAFF ARCHITECT</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Sandeep Vyas</t>
+          <t>Nissim Titan</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Solutio…</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Incture Technologies Private Limited</t>
+          <t>4CAST SYSTEMS LTD</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Thomas von Alm</t>
+          <t>James Tiwari</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>SVP Cross-Solution Services</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Intellioz LLC</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Markus von Quast</t>
+          <t>Shuhei Toba</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Global Head Industry Ecosystem</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Business Engineering Corporation</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>TATSUO WATANABE</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Principal Cons…</t>
-        </is>
-      </c>
+          <t>John Tocci</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
       <c r="C369" t="inlineStr">
         <is>
-          <t>D I SQUARE CORPORATION.</t>
+          <t>Cbs Corporate Business Solutions America In…</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Masayuki Wada</t>
+          <t>Oliver Toloui</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>SVP, Head of Corporate Digit…</t>
+          <t>Director - AI…</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Fujitsu Limited</t>
+          <t>Ibase Operations Corp Qualitest</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Stephen Wagenheim</t>
+          <t>Ray Toma</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Senior Sales Executive - Suppl…</t>
+          <t>Senior Principal — Global Strategic Initia…</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Dallas (Allen)</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Neha Wahi</t>
+          <t>Yuko Tominaga</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Global Alliance Lead</t>
+          <t>Research Writer</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>A.T. Kearney, Inc.</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Waka Wakabayashi</t>
+          <t>Laura Tozzo</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Associate Partner</t>
+          <t>AI Product Lead SAP IBP</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>KPMG Consulting Co., Ltd.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Gustavo Waldfogiel</t>
+          <t>Eero Traagel</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>LAC HCM Head</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>SAP Argentina - Buenos Aires</t>
+          <t>IBM Canada Limited</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Shashikant Walimbe</t>
+          <t>Adam Trahan</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Vice President &amp; Global Head -…</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>LTM LIMITED</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Julie Walker</t>
+          <t>Evgeny Treskin</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Sr. Director, Enterprise Applicatio…</t>
+          <t>SAP Alliances Director</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Armstrong</t>
+          <t>Argano</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Rob Wallace</t>
+          <t>Chetan Tripathi</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Senior Manager Digital &amp; In…</t>
+          <t>oCFO Adoption expert</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Jaguarlandrover</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Enzhou Wang</t>
+          <t>Seshagiri Tripurana</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Chief Technology Officer</t>
+          <t>Senior Director</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>City of Tacoma</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>May Wang</t>
+          <t>Masaru Tsukahira</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Direc…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
+          <t>TOKYO ELECTRON LIMITED.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Adam Warner</t>
+          <t>Lindsay Tucker</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Cost Analyst</t>
+          <t>Solution Consultant</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Marathon Cheese Corporation</t>
+          <t>Docusign</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Kosuke Watanabe</t>
+          <t>Paul Turbes</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>KPMG LLP</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Takashi Watanabe</t>
+          <t>Treaver Tyler</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>執行役員</t>
+          <t>Tech…</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>JFE Systems,Inc.</t>
+          <t>Meijer Great Lakes Limited Partnership</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Robert Watson</t>
+          <t>Kotaro Ueda</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Sr Account Executive</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>JSUG</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Ashley Waxman</t>
+          <t>Rajkishore Una</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Strategic Sales Executive</t>
+          <t>President/CEO</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Aevitas IT LLC</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Christy Weaver</t>
+          <t>Bala Parameswara Rao Upadhyay…</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Global Demand Generation Man…</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Vertex, Inc.</t>
+          <t>Stefanini, Inc.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Mike Weaver</t>
+          <t>Oscar Uribe</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Senior I…</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>True Commerce Inc. TrueCommerce</t>
+          <t>EDUARDONO S A S</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Chris Webster</t>
+          <t>SACHIN VAIDYA</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>SVP IT Strategy &amp; Architecture</t>
+          <t>Director - Enterprise Commercial…</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Ahold Delhaize</t>
+          <t>Pfizer, Inc.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Matt Webster</t>
+          <t>Jonathan VON RUEDEN</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Director of…</t>
+          <t>Chief AI Officer</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Gardner White Furniture Co., Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Patrick Weil</t>
+          <t>Wagner Valentin</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Director of Regulated Indust…</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Metrie Canada Ltd</t>
+          <t>SAP Brasil Ltda.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Sarah Weiler</t>
+          <t>Jorge Valles Velásquez</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Manager, Busine…</t>
+          <t>KMMP…</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Ball Horticultural Company</t>
+          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Adam Werner</t>
+          <t>Henri Vallet</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>VP, Corporate Technology</t>
+          <t>VP Sales, Americas B2B</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Crocs, Inc.</t>
+          <t>Mirakl</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Maddie Werner</t>
+          <t>Jeff Van Pelt</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Director of Delivery Solutions</t>
+          <t>Founder / Managing Dire…</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Robra IT</t>
+          <t>Javelin Consulting</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Katherine West</t>
+          <t>Meredith Van Wyk</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>CX Account Executive</t>
+          <t>Americas Field Partner…</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Anja Wettling</t>
+          <t>Joris Van der Donck</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Sr Manag…</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>anuwo GmbH</t>
+          <t>Commscope Connectivity Belgium</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Charleen Wetzstein</t>
+          <t>Vijay Varee</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>SAP Principal Architect</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>PROSPECTOR, LLC</t>
+          <t>Petsmart LLC</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Peter Wheatley</t>
+          <t>Suman Varma</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Enterprise Architect…</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>SAP America (Houston)</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Robb White</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr"/>
+          <t>Chris Vassalotti</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+          <t>Opentext</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Peter Widmer</t>
+          <t>Raju Vedala</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Chief of Staff to the Global Head of S…</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>CES Business Technologies, LLC</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Chad Wiech</t>
+          <t>Asier Vega Sanchez</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Director of Solution…</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>Arkyn</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Chamnida Wijetilleke</t>
+          <t>Jennifer Veillon</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Dir Project Controls</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>The Ducats Group LLC</t>
+          <t>Fluor Corporation</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Pete Wilkins</t>
+          <t>Ajay Reddy Velampudi</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>NA Partner Manager</t>
+          <t>Senior VP - Sa…</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>Miracle Software Systems Inc.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Mark Willey</t>
+          <t>William Velastegui</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Vice…</t>
+          <t>JEFE DE TI Y PR…</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>Plasticaucho Industrial S.A.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ed Williamson</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Client Services Lead</t>
-        </is>
-      </c>
+          <t>Rajiv Vemula</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr">
         <is>
-          <t>XMATERIA LTD</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Monica Willis</t>
+          <t>Sundu Venkataramani</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>HR Strategy and Value A…</t>
+          <t>Industry Val…</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Plano- Legacy West</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Charlotte Wilson</t>
+          <t>Venkat Venkataramani</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Senior Manager Strategic Cha…</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Direct Energy</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Emily Wisemiller</t>
+          <t>Tom Venner-Crysell</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>ERPeople Solutions Ltd</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Julia Wolfe</t>
+          <t>Eduardo Vergara</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Analyst Relations Manager</t>
+          <t>Manager/Head of Dept</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Agrosuper S.A.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Jennifer Workman</t>
+          <t>Amit Verma</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Techn…</t>
+          <t>RVP, Head of CFO Advisory…</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Universal Destinations &amp; Experiences</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Steven Wright Wright</t>
+          <t>Kumar Vidit</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>VP Sales</t>
+          <t>Product Marketing M…</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Acuiti Labs Limited</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Monty Wurth</t>
+          <t>Lakshmi Vidyashankar</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>VP of Operations</t>
+          <t>VP of IT</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Optima Consulting L.L.C.</t>
+          <t>Marvin Engineering Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Brad Wylie</t>
+          <t>Jayant Vikram</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Cloud Delivery Lead</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Accenture LLP</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>KAORI YASHIKI</t>
+          <t>Yeni Villanueva</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Business Resear…</t>
+          <t>Supervisora…</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services LLC</t>
+          <t>Compañia Minera Antamina S.A.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>YOUNGHO YOO</t>
+          <t>Robert Vinyard</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Team Leader</t>
+          <t>VP and Senior Partner</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>LG CNS Co., Ltd.</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Mohamed YUSUF</t>
+          <t>Thomas Vioux</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Head of Integrated Toolchain</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>PwC</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Hikaru Yafuso</t>
+          <t>Anil Visal</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Senior Alliance Director</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Sonoko Yamamoto</t>
+          <t>Clara Viscido</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Partner Business Manager</t>
+          <t>Consulting Services Director</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>GEONOSIS</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Osamu Yamazaki</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Co…</t>
-        </is>
-      </c>
+          <t>Paulo Vita Vita</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Kenji Yanagi</t>
+          <t>Ranjan Vitt</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Group Leader</t>
+          <t>AI Compliance Governance Program…</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>ASAHI GROUP JAPAN, LTD.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>EJ Yang</t>
+          <t>Jose Voisin</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>IT Deputy Director</t>
+          <t>Global CIO</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>MediaTek Inc.</t>
+          <t>Carmeuse</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Kiran Yarlagadda Yarlagadda</t>
+          <t>Christina Volk</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Managing…</t>
+          <t>Head of Strate…</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Adroix Corp DBA CodeForce 360</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Takayuki Yasuda</t>
+          <t>Jessica Voyles</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>Account Executive, South</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>JFE Systems, Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Tomoki Yasuda</t>
+          <t>Sandeep Vyas</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>AssistantMana…</t>
+          <t>Solutio…</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>NTT DATA Japan Corporation</t>
+          <t>Incture Technologies Private Limited</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Kazuhiro Yonekawa</t>
+          <t>Thomas von Alm</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Chief/Proj…</t>
+          <t>SVP Cross-Solution Services</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>CANON MARKETING JAPAN INC.,</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Sungeui Yoon</t>
+          <t>Markus von Quast</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Senior Specialist</t>
+          <t>Global Head Industry Ecosystem</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Christopher Yope</t>
+          <t>TATSUO WATANABE</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>SAP Supply C…</t>
+          <t>Principal Cons…</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>DXC Technology Services LLC</t>
+          <t>D I SQUARE CORPORATION.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Kohei Yoshimatsu</t>
+          <t>Masayuki Wada</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>SVP, Head of Corporate Digit…</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>アズビル株式会社</t>
+          <t>Fujitsu Limited</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>taichi yoshida</t>
+          <t>Stephen Wagenheim</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Senior Ma…</t>
+          <t>Senior Sales Executive - Suppl…</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>BENIC SOLUTION CORPORATION</t>
+          <t>Dallas (Allen)</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>nakajima yuki</t>
+          <t>Neha Wahi</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Global Alliance Lead</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Nitori Co., Ltd.</t>
+          <t>A.T. Kearney, Inc.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Stefan Zach</t>
+          <t>Waka Wakabayashi</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>VP Global IT</t>
+          <t>Associate Partner</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Wieland Group</t>
+          <t>KPMG Consulting Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Beau Zaremski</t>
+          <t>Gustavo Waldfogiel</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>VP of Sales</t>
+          <t>LAC HCM Head</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Yuan Zhang</t>
+          <t>Shashikant Walimbe</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Senior Project Manager, SAP AI RIG</t>
+          <t>Vice President &amp; Global Head -…</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>LTM LIMITED</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Cathy Zhou</t>
+          <t>Julie Walker</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>IT Director, EBS</t>
+          <t>Sr. Director, Enterprise Applicatio…</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>Armstrong</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Gustavo Zintak</t>
+          <t>Rob Wallace</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>Senior Manager Digital &amp; In…</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>SWISS MEDICAL S.A.</t>
+          <t>Jaguarlandrover</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Alina Zuberi</t>
+          <t>Enzhou Wang</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Global Content Strategist</t>
+          <t>Chief Technology Officer</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>City of Tacoma</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Yoshiaki Agata 縣</t>
+          <t>May Wang</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>Direc…</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>AJS株式会社</t>
+          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>裕紀 阿保</t>
+          <t>Adam Warner</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cost Analyst</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>FORTIENCE CONSULTING INC.</t>
+          <t>Marathon Cheese Corporation</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
+          <t>Kosuke Watanabe</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Senior Account Executive</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Takashi Watanabe</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>執行役員</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>JFE Systems,Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Robert Watson</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Sr Account Executive</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Ashley Waxman</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Strategic Sales Executive</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Aevitas IT LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Christy Weaver</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Global Demand Generation Man…</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Vertex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Mike Weaver</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Senior I…</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>True Commerce Inc. TrueCommerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Chris Webster</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>SVP IT Strategy &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Ahold Delhaize</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Matt Webster</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Director of…</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Gardner White Furniture Co., Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Patrick Weil</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Metrie Canada Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Sarah Weiler</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Manager, Busine…</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Ball Horticultural Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Adam Werner</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>VP, Corporate Technology</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Crocs, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Maddie Werner</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Director of Delivery Solutions</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Robra IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Katherine West</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>CX Account Executive</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Anja Wettling</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>anuwo GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Charleen Wetzstein</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>SAP Principal Architect</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>PROSPECTOR, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Peter Wheatley</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Enterprise Architect…</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>SAP America (Houston)</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Robb White</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Peter Widmer</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Chief of Staff to the Global Head of S…</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Chad Wiech</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Director of Solution…</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Pittsburgh, SAP America</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Chamnida Wijetilleke</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>The Ducats Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Pete Wilkins</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>NA Partner Manager</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>SAP America(Bellevue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Mark Willey</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Vice…</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Ed Williamson</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Client Services Lead</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>XMATERIA LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Monica Willis</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>HR Strategy and Value A…</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Plano- Legacy West</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Charlotte Wilson</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Senior Manager Strategic Cha…</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Direct Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Emily Wisemiller</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Molex</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Julia Wolfe</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Analyst Relations Manager</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Jennifer Workman</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Techn…</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Universal Destinations &amp; Experiences</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Steven Wright Wright</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>VP Sales</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Acuiti Labs Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Monty Wurth</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>VP of Operations</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Optima Consulting L.L.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Brad Wylie</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>KAORI YASHIKI</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Business Resear…</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Hitachi Digital Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>YOUNGHO YOO</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Team Leader</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>LG CNS Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Mohamed YUSUF</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Head of Integrated Toolchain</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Hikaru Yafuso</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Senior Alliance Director</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Sonoko Yamamoto</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Partner Business Manager</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Osamu Yamazaki</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Co…</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Kenji Yanagi</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Group Leader</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>ASAHI GROUP JAPAN, LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>EJ Yang</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>IT Deputy Director</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>MediaTek Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Kiran Yarlagadda Yarlagadda</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Managing…</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Adroix Corp DBA CodeForce 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Takayuki Yasuda</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>JFE Systems, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Tomoki Yasuda</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>AssistantMana…</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>NTT DATA Japan Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Kazuhiro Yonekawa</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Chief/Proj…</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>CANON MARKETING JAPAN INC.,</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Sungeui Yoon</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Senior Specialist</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Christopher Yope</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>SAP Supply C…</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>DXC Technology Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Kohei Yoshimatsu</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>アズビル株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>taichi yoshida</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Senior Ma…</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>BENIC SOLUTION CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>nakajima yuki</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Nitori Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Stefan Zach</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>VP Global IT</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Wieland Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Beau Zaremski</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Yuan Zhang</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Senior Project Manager, SAP AI RIG</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Cathy Zhou</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>IT Director, EBS</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Ecolab Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Gustavo Zintak</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Manager/Head of Dept</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>SWISS MEDICAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Alina Zuberi</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Global Content Strategist</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Yoshiaki Agata 縣</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>AJS株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>裕紀 阿保</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>FORTIENCE CONSULTING INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
           <t>謙介 青木</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
+      <c r="B493" t="inlineStr">
         <is>
           <t>Manager, Uvance Market Developme…</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
+      <c r="C493" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C493"/>
+  <dimension ref="A1:C549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1307,7 +1307,6 @@
           <t>Andreas Axer</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>WIRTGEN GROUP Branch of John Deere Gmb…</t>
@@ -1796,7 +1795,6 @@
           <t>Dan Berard</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>International Business Machines Corporation…</t>
@@ -2370,7 +2368,6 @@
           <t>Adam Breiterman</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
           <t>Maryland &amp; Virginia Milk Producers Cooperati…</t>
@@ -2502,7 +2499,6 @@
           <t>Jay Brown</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>ConsultingNetwork Business Solutions, LLC</t>
@@ -2753,7 +2749,6 @@
           <t>Erin Buss</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
           <t>Globalsource Information Technology III, Inc.</t>
@@ -3480,7 +3475,6 @@
           <t>Taiseer Chirakkal</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
           <t>International Business Machines Corporation…</t>
@@ -3714,7 +3708,6 @@
           <t>Zach Clement</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
           <t>American Equity Investment Li fe Insurance C…</t>
@@ -4288,7 +4281,6 @@
           <t>Marco Sanna</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
           <t>cbs Corporate Business Solutions Unternehm…</t>
@@ -4318,7 +4310,6 @@
           <t>Subhayu Sarkar</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr">
         <is>
           <t>Cognizant Technology Solutions U.S. Corporat…</t>
@@ -5016,7 +5007,6 @@
           <t>Vice President, Information Technol…</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5160,7 +5150,6 @@
           <t>Tomoya Shinozaki</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
           <t>フォーティエンスコンサルティング株式会社…</t>
@@ -5309,7 +5298,6 @@
           <t>Sergei Silva</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
           <t>Vistex</t>
@@ -5696,7 +5684,6 @@
           <t>Denis Staudt</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
         <is>
           <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
@@ -5743,7 +5730,6 @@
           <t>Dieter Steinmann</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
         <is>
           <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
@@ -5841,7 +5827,6 @@
           <t>Leslie Stoffel</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr">
         <is>
           <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
@@ -6636,7 +6621,6 @@
           <t>John Tocci</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr"/>
       <c r="C369" t="inlineStr">
         <is>
           <t>Cbs Corporate Business Solutions America In…</t>
@@ -7210,7 +7194,6 @@
           <t>Rajiv Vemula</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr">
         <is>
           <t>Cognizant Technology Solutions U.S. Corporat…</t>
@@ -7444,7 +7427,6 @@
           <t>Paulo Vita Vita</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr">
         <is>
           <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
@@ -8052,7 +8034,6 @@
           <t>Robb White</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr">
         <is>
           <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
@@ -8736,6 +8717,938 @@
       <c r="C493" t="inlineStr">
         <is>
           <t>Fujitsu</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>James Rasque</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>IT Business Analyst Supervisor</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Kwik Trip Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Abhishek Rastogi</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Lead Specialist, Business Cont...</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>National Grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Jeannine Rau</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>SCSM</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Koushika Ravikumar</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>KATBOTZ LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Prachi Ray</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Marketing - SAP</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Vasee Rayan</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Senior Vic...</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>SAP Labs, LLC. (Newtown Square)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Carlos Recio</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Vice President Testing Practice</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Innovise IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Araja Reddy</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Deloitte Consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Sasi Reddy</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Sr. SAP Applicati...</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Sun Chemical Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Nico Reichen</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>PricewaterhouseCoopers GmbH Wirtschaftsp...</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Caitlin Reidy</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Icertis Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Kristen Reinken</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Journey &amp; Change Management L...</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Efrain Reyes</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>SAP Function...</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Aecon Construction Group Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Luis Reyes</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Regional Sales Director SSLATAM</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Vistex Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Dan Rhoadhouse</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Process Ar...</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>The Scotts Miracle-Gro Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Fernando Riccardi</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Exed Consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Devin Rich</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Chief Info. Off.</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Lansing Building Products, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Trey Riley</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Senior Director</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Leprino Foods Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Lisa Rinaldi</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Finance Lead, ED...</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>General Electric Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Angela Rios</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>CIO</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Centro de Sistemas y Negocios S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Jerome Robertson</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Director, AI Driven Business Insights</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Pfizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Lauren Robinson</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr"/>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Sparks</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Devin Robnick</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Head of NA Field Market...</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Virginia Roda</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Chief Technology Off</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Southbay S.R.L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Alexander Rodde</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Head of Corporate Portfolio</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Sebastian Rode</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Global ERP Delivery Lead</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Roche</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Hernan Rodriguez</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Practice Manager</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Nearshore Argentina S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Josiane Roger</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>CGI Information Systems and Management C...</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Laurie Rogosheske</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Director E...</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer United States Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Rachel Romanoski</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Director - SAP SCM...</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>SAP America (Houston)</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Diana Romaya</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>SAP...</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>John Rooney</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Regional Partner Director</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Stonebranch</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Susanne Ross</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Senior Partner Marketin...</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Coveo Solutions Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Cori Rothgery</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Data &amp; A...</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>DURACELL U.S. OPERATIONS, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Sylvain Roy</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>It Director</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Heroux-Devtek</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Renee Rubino</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Senior Manager of Alliance Partnershi...</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>SMC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Felix Rubio</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Industry Advisor Latin America</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>SAP Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Frank Ruetten</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Client Partner</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>IBM Deutschland GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Frank Ruland</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr"/>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>PricewaterhouseCoopers GmbH Wirtschaftsp...</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Roxanne Ryan</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Director, Executive Progr...</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Scott Ryerson</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Partner Executive</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Capgemini America, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Royce Ryu</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Head of Services Deliver...</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Natalie Röthel</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Executive Assistant</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>mariano rivarola</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Gerente Industrial Regional</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>HZ GROUP S.R.L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Hanumantha Rao Sabbireddy</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Tech Mahindra</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Andrew Sackett</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Director of Partnerships</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Collibra Belgium BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Rinchen Sahni</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>KATBOTZ LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>KG Saito</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Vice President</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>MACNICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Makoto Saito</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>IT Development Dept</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Tokyo Electron Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Tito Salazar</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Partner Growth Manager</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>OneRail</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Sarah Salzman</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Regional VP of Sales</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Basware, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Julissa Samuels</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Gerente de aplica...</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>American Sportswear, S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Brent Sandberg</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Project Manager, Business Transf...</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Carmeuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Sachin Sangle</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>ImpactQA</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>KATSUYUKI SHINZEKI</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Assistant Manager</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Marubeni Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>JASBIR SINGH</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Associate Partner, Global...</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>IBM India Pvt Ltd</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C549"/>
+  <dimension ref="A1:C604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8879,7 +8879,6 @@
           <t>Nico Reichen</t>
         </is>
       </c>
-      <c r="B503" t="inlineStr"/>
       <c r="C503" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers GmbH Wirtschaftsp...</t>
@@ -8892,7 +8891,6 @@
           <t>Caitlin Reidy</t>
         </is>
       </c>
-      <c r="B504" t="inlineStr"/>
       <c r="C504" t="inlineStr">
         <is>
           <t>Icertis Inc.</t>
@@ -9075,7 +9073,6 @@
           <t>Lauren Robinson</t>
         </is>
       </c>
-      <c r="B515" t="inlineStr"/>
       <c r="C515" t="inlineStr">
         <is>
           <t>Sparks</t>
@@ -9173,7 +9170,6 @@
           <t>Josiane Roger</t>
         </is>
       </c>
-      <c r="B521" t="inlineStr"/>
       <c r="C521" t="inlineStr">
         <is>
           <t>CGI Information Systems and Management C...</t>
@@ -9356,7 +9352,6 @@
           <t>Frank Ruland</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr"/>
       <c r="C532" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers GmbH Wirtschaftsp...</t>
@@ -9649,6 +9644,937 @@
       <c r="C549" t="inlineStr">
         <is>
           <t>IBM India Pvt Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Mayur Patel</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Director IT COE</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Axalta Coating Systems, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Subhajit Paul</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>IT Technical Lead - SAP CoE</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Jabil Circuit, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Dan Pavlick</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Director of Strategic Partnerships</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>OneRail</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Matt Pegoraro</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Field Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Paul Pelletier</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Logistics Operatio...</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Defense Logistics Agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Leila Penteado</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Value Advisor Head Brazil</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>SAP Brasil Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Rogério Peres</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>CIO</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>JBS USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Eddie Perez</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Master Producti...</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Marvin Engineering Co., Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Fernanda Perez</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>General Manag...</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>SAP Argentina - Buenos Aires</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>April Perkins</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Sr. Mgr. SAP...</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>thyssenkrupp Materials NA, Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Ernie Perno</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>St Account...</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>The Hackett Group- Answerthink</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Teresa Perrius</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Director, Payroll Operations</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Catherine Perry-Robertson</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Partner, Natio...</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>PricewaterhouseCoopers LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Hari S. Peruri</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>CIO</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>AGCO Corp</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>George Peter</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Sr Mgmt Business Sys</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Pure Storage Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Mark Petersen</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Sr...</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Advanced Workforce Inc DBA TotalTek Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Sladjana Petrovic</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>IGM Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Jim Phelan</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>EVP, US Country M...</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>msg global solutions, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Matt Phillips</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Sr. Director</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Woodward Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Alex Pierroutsakos</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Industry Exec Advisor -...</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>SAP America (Miami)</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Dave Pinet</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Finance AE</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>SAP Canada - Ottawa</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>James Pinto</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr"/>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>International Business Machines Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Peter Pluim</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>President, Global Cloud Op...</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>SAP UK Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Tomas Pluma</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>SCM Solution Advisory LAC</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>SAP Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Chris Podeszwa</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Principal Accoun...</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Alokai (ex - Vue Storefront)</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Franck Poisson</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>PWC US Group LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Eric Pokriefka</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Manager, Customer IT</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>DTE Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Michael Polaha</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>SR VP Record to Report</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Paula Popity</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Celco -...</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Celulosa Arauco y Constitucion S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Simone Porcu</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Karin Porwoll</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Global Strategic Partner Marketing SAP</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Raja Pothapragada</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Customer/Partner Success Man...</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Panaya, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Joel Pousinho</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Maxfield Group Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Andrea Powers</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Global Account Director</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Mediafly</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Stacy Price</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>IT Manager</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>American Airlines, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Whitney Price</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Director Supply Chain C...</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Brenda Prinzing</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Senior Co...</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>SAP America Inc. (Hudson Yards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Pascal Proulx</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>STI Maintenance inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Mark Pryor</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>VP Digital, M&amp;A+ERP</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>bp</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Manoj Purohit</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>SVP and Head of APAC Cor...</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>SAP ASIA Pte Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Joyce Purtell</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Vice President, Tax Tech...</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Angie Pyles</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>HCM Account Executive</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Plano- Legacy West</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Ashley Quinn</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Gentex Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Huzefa Qutbuddin</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Executive Vice President</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Royal Cyber Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR RAMALINGAM</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Senior Manager</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>CSL BEHRING LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>AMIT RANJAN</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Sr. Director IT Enterprise Applicat...</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Saputo Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Budi Rachman</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Predictive...</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Hamilton Prime International LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Arun Rajakani</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Architect - SAP Cloud</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>A.O. Smith Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Vishal Rajpal</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>VP Client Inn...</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Sutherland Global Services Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Kannan Ramanathan</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Director of Sales</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>SoftServe, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Rajesh Ramegowda Shankarappa</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Claudia Ramos</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Sales representative</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>724 BC Consulting SAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Warren Rampersaud</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Enterprise Account E...</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Liam Ranik</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Industry Account Executi...</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Paul Rascoe</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Janitor</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Beam Therapeutics</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C604"/>
+  <dimension ref="A1:C660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10010,7 +10010,6 @@
           <t>James Pinto</t>
         </is>
       </c>
-      <c r="B571" t="inlineStr"/>
       <c r="C571" t="inlineStr">
         <is>
           <t>International Business Machines Corporation</t>
@@ -10575,6 +10574,954 @@
       <c r="C604" t="inlineStr">
         <is>
           <t>Beam Therapeutics</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Kazuto Nakada</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Territory Ecosystem Man...</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Yoshihiro Nakamura</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Chief Info. Off.</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>MAFTEC Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>KiWoong Nam</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Blueward inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Balachander Nandagopal</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Senior Director</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Icertis, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Travis Nault</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>AscendN, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>DEBS Nayak</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Director — SAP...</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>INNOVAPTE CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Madhur Nayak</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Miracle Software Systems Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Sunny Neely</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Industry Advisor, Consu...</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Daniel Nersveen</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>PFERD-W...</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>August Rüggeberg GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>MJ Nevarez</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Planner/Scheduler</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Pantexas Deterrence LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Pamela Newberry</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Manager S4 Systems</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Collins Aerospace</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Albert Nguyen</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>VP Strategic Growth</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Qualitest</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Tom Nierlich</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>VP, Strategic Alliances</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Sovos</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Youssef Nifaoui</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Customer Success Mana...</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Jim Nissen</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Senior Program Manager</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Steve Noffke</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>American National Insurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Dongjin Noh</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Senior Professional</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Pavel Nouel</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Vice President,...</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Carlos Nunez</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>MDR</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Vendelux</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>matthew nasta</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>IT OTC Manager</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>S.C. Johnson &amp; Son, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Liz O'Neill</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Director, Business Deve...</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>DIBELL GROUP, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Conor O'Rourke</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>SAP Account Manager</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>ALKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Atilola Odeyemi Odeyemi</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Associate VP</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Africa Finance Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Halil Oezcelik</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Customer Officer</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Masayoshi Okita</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Hitachi, Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Testuo Okuma</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Executive Partner</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>BAYCURRENT, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Hiroshi Okura</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>SAP Japan CFO</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Yuta Okuyama</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>IT person</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>NTTデータグループ</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Matt Olive</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Vice President of Sales</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>T S P</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Aleksandro Oliveira</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Grupo Edson Queiroz</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Cristian Olsen</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Chief Info. Off.</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Grupo Herman Zupan</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Andre Ory</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>OTS ERP Director</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>State of Louisiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Rauf Osho</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Senior SAP System E...</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>MIT Lincoln Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Catherine Ouellet</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Team Leader SAP Busine...</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Foliot Furniture Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Tatsuya Owada</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr"/>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>NIPPON STEEL Hitachi Systems Solutions, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Chad Owen</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Principal, Customer Success</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>msg Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Christine Owens</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Sr PM/ S/4HANA lead</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>e.l.f. Cosmetics, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Megha Oza</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Strategi...</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Splisys IT Consulting Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>HyunMo PARK</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>BizTech i Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Carlos Mauricio Pacheco Campan...</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Regional BRM</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Softtek</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Sachin Pai</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>SVP &amp; Global Head —...</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Celebal Technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Shieun Paik</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Director IT</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Cardinal Health 200, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Ganesh Palanievelu</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Vice President</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Tech Mahindra</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Augusto Palma</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Executive Manager CoE SAP</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>HYPERA S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Rodolfo Pampin</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>BAITCON S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Joyce Pan</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Finance Manager</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>SAP (China) Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Debasis Panda</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Delivery Director</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Defense Logistics Agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Carolina Paolini</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Business Readiness...</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Jaguar Land Rover Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Ravikiran Papthimar Papthimar</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Sr. Dire...</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Incture Technologies Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Keshav Parameshwara</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Senior Customer...</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>SAP LABS INDIA PVT. LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Fernando Pariani</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Chief In...</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>CENTRO MEDICO AMENABAR S.R.L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Adarsh Parikh</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Silver Touch Technologies Canada Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Edward Park</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Agent 008</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>National Amusements, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Sang-Yull Park</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Team Leader</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Woongjin Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Anfernee Parker</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Senior Account Executive</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Brian Partlow</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Assis...</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Medical College of Virginia Foundation</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C660"/>
+  <dimension ref="A1:C717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -11161,7 +11161,6 @@
           <t>Tatsuya Owada</t>
         </is>
       </c>
-      <c r="B639" t="inlineStr"/>
       <c r="C639" t="inlineStr">
         <is>
           <t>NIPPON STEEL Hitachi Systems Solutions, Inc.</t>
@@ -11522,6 +11521,967 @@
       <c r="C660" t="inlineStr">
         <is>
           <t>Medical College of Virginia Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Jenny McLean</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Partner, Retail Industry...</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Clarkston Consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Kathryn McLean McLean</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>BONFIRE CONSULTING LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Tommy McMullen</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>SAP Practice Lead</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Fidelis Companies LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>John McNally</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Senior Account Executive</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Tom McSorley</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>General Ma...</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>The Gill Corporation --Maryland</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Mark Meanwell</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Senior Manager Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Sylvamo</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Michael Meany</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Enterprise Account Exec...</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Shane Meehan</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Sr. Director</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>BioMarin Pharmaceutical, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Thomas Mehlkopf</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Head of Treasury and Working Capit...</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Nilay Mehta</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Principal Solution Archit...</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Mariana Melbardis</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr"/>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Price Waterhouse &amp; Co Asesores de Empresa...</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Emily Meltzer</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Developme...</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Accenture Federal Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Ritesh Menon</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Senior Vice President &amp; Business...</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Incture LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Janet Mercado</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Power &amp; Cloud Client Leader</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Katherine Merrick</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Supv IT Program M...</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Puget Sound Energy, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Monica Alejandra Mesa</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Team Lead SAP Projec</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Cementos Argos S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Ryan Mezzanotte</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>SAP Account Manager</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Alku, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Maya Midmore</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Industry Account Executive</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Lynn Mikoshi</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Joe Miles</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Life Sciences Industry Director</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>UI Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Patrick Miller</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Director - Enterprise Applicat...</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Cerapedics Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Rebecca Miller</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Acc. Operations Mgr.</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Purdue University</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Piyush Mistry</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Rich Mitton</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Mathis Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>S Mohanavelu Mohanavelu</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>ERP solu...</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Gulfstream Aerospace Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Sanjeev Monga</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Kraft Heinz Foods Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Matt Monroe</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Sr. Services Account...</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>SAP America (Houston)</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Hyunsook Moon</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>DIRECTOR</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>BSG partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Brian Moore</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>SVP &amp; General Manager, Servic...</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Stephine Morbach</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr"/>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>American Equity Investment Life Insurance C...</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Dodjie Morelos</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Carlisle Construction Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Abby Morgan</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Customer Engagement Manag...</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Visionsoft Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Lori Morgan</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>VP, Sales</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Ritsuo Moriya</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>SAP AMO</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Kobelco Systems Corp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Alex Moronta</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Gerente Soluciones...</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Pasteurizadora Rica S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Meir Morozov</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Enterprise Account Specialist</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Panaya, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Craig Moskowitz</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>SAP Program Director</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Empower</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Michael Moukeiber</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Senior Director</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Molex, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Basant Mudgal</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Consultant, Business...</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Celebal Technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Krish Mujje</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>SVP, Digital &amp; AI S...</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Tachyon Technologies LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Maximilian Mundel</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>VP Platform Sales</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Hanane Murakami</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>IBM Japan, Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Kentaro Murata</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Empl...</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>パナソニックインダストリー株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Wataru Murayama</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Sales Manager(Retail /...)</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Kylie Murphy</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Mar...</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>SAP Global Marketing(Newtown Square)</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Craig Murray</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Business Transformation...</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Piramanayagam Muthusamy</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Global Head, SAP Te...</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Kishore Muthyala</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Miracle Software Systems Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Jay Myers</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Value Advisor</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Ariba Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Suzi Myers</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Director, Application Dev</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Cardinal Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Florian Müller</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Head of Security Product Manageme...</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>PRAKASH NARAYANAN</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Enterprise Account Executive</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Bristlecone, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Suresh NG</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>SAP Sales Specialist</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Wanda NI LAIGHIN</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Vice President, Global Marketing...</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>SAP France</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Kota Nagashio</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Man...</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>パナソニック インダストリー株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Masaki Nagata</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Consulting Divisi...</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>DI SQUARE CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Sahiba Nagpaul</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>AVP, SolEx &amp; Partner Success at I...</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Icertis, Inc.</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C717"/>
+  <dimension ref="A1:C772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -11700,7 +11700,6 @@
           <t>Mariana Melbardis</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr"/>
       <c r="C671" t="inlineStr">
         <is>
           <t>Price Waterhouse &amp; Co Asesores de Empresa...</t>
@@ -12019,7 +12018,6 @@
           <t>Stephine Morbach</t>
         </is>
       </c>
-      <c r="B690" t="inlineStr"/>
       <c r="C690" t="inlineStr">
         <is>
           <t>American Equity Investment Life Insurance C...</t>
@@ -12482,6 +12480,933 @@
       <c r="C717" t="inlineStr">
         <is>
           <t>Icertis, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Anand Lokineni</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>IT Architect</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Jabil Circuit, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Sergio Lopez</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>CFO</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>WINES AND SPIRITS S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Diego Loria</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Gerente de sistemas</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>MAINCAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Nathalie Lotra</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr"/>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company Lilly Technology Center...</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Tammy Louie</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Senior Financial Systems Analyst</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>AutoZone</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Wepoint Louis</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Vice-President</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>ONEPOINT</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Lydia Lousky</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Supply Ch...</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>SAP America Inc. (Hudson Yards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Diego Lozano</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Seidor Consulting SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Jeroen Luijrink</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>SAP Nederland BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Michael Lukac</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Enterprise AE</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Pittsburgh, SAP America</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Adam Benjamin Lustig</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>VP, Solution Advisory</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Basware</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Bill Lynch</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Sr Director IT</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Sharp</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Thomas Lynch</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>VP, Value Advisory</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Nicolas Löwe</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>BearingPoint GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Ravish M</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Expert, Advanced Success Pl...</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>YOSHIHIRO MISAWA</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Managing Director General...</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>JFE Systems,Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>TIZIANA MOROSINI</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Corporate Marketing Events</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>SAP Italia S.p.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Santipriya Madabushi</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Sapta Global Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Sanjay Madala</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>SAP Competency...</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>ShimentoX Technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Janet Maddern</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>ERP Program Manager</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>UT-Battelle LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Aaron Maestas</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Sr Director, Health Systems Natio...</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Sergo Maglakelidze</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Director, Privat...</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Evan Magouirk</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Manager, Pricing &amp; A...</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>McKesson Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Souvik Majumdar</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Acuiti Labs Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Naresh Makhijani Makhijani</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Glo...</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Bob Marchand</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>COO</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Innovise-IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Melissa Marchetti</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>SAP...</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>John Marcine</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Industry Account Executive</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Alan Martin</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Senior Solutions Sales E...</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Lawrence Martin</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Chief Product Officer an...</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Sascha Martin</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>SVP, Global H...</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>SAP Deutschland SE &amp; Co.KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Martine Martine</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Portefeuille Soucy Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Raphael Martins</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Sol...</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Seidor - Tecnologia da Informação LTDA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Fernando Martins Salles</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>I...</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>AMBAR SERVICOS DE INFORMATICA LTDA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Takahiro Marufuji</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Dire...</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>MITSUBISHI CHEMICAL CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Shiho Maruta</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Team leader</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>（株）リクルート</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Adriana Masson</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Chicken Farmers of Ontario</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Tsuyoshi Masuda</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>VP and Head of RISE Ja...</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Monika Matel-Sousa</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Deputy Chief Technology Offi...</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>City of Toronto</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Deepak Mathur</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Medline Industries, LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Nikhil Mathur</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Senior Director</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Celebal Technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Doug Maulbetsch</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Director SAP applications</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Lucid Motors</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Jared Mayers</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Acquisition Suppo...</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Pantexas Deterrence LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Lia Mazmanian</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Marketing Execution Specialist</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Nelia Mazula</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Supply Chain Sales Exec...</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Gerard McCann</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Strategic Allianc...</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Opentext Ot Addison Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Kevin McCollom</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Global VP, General Mgr.</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Archlynk, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Gerry McCool</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Value Advisor</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Michaelene McCormick</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Senior Services Account...</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Lauren McCullin</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Senior Sales Executive-...</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>John McDonnell</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Industry Advisor, Wholes...</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Teresa McGivern</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Global Workforce Tranf...</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>PROFINDA LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Ben McGrail</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Managing director</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>XMATERIA LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Denise McGuigan</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Part...</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Patricia McKinley</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr"/>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>CARMEUSE RESEARCH AND TECHNOLOGY S...</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C772"/>
+  <dimension ref="A1:C829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -12540,7 +12540,6 @@
           <t>Nathalie Lotra</t>
         </is>
       </c>
-      <c r="B721" t="inlineStr"/>
       <c r="C721" t="inlineStr">
         <is>
           <t>Eli Lilly and Company Lilly Technology Center...</t>
@@ -13403,10 +13402,974 @@
           <t>Patricia McKinley</t>
         </is>
       </c>
-      <c r="B772" t="inlineStr"/>
       <c r="C772" t="inlineStr">
         <is>
           <t>CARMEUSE RESEARCH AND TECHNOLOGY S...</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Jan Krueger</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Technical Account Director</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Mike Krug</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>SAP Technical...</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Pennsylvania State University</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Siddhi Kshatriya</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Organizational Change Managem...</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>AutoZone</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Greg Kull</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Leader, SAP Partner Sales</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Vertex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>SAP Pro...</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Molex Electronic Technologies, LLC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Sandeep Kumar</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Partner [Data, Analytics &amp; AI]</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>SCMXpert</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Jazz Kundra</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Amgen Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Sabrina Kunze</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Consulting Sen...</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Trent Kurbis</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Manager, IT Service M...</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>The Mosaic Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Makoto Kurimoto</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr"/>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>キヤノンマーケティングジャパン株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Dennis Kurlandski</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Kohei Kuroda</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Senior Consultant</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Fortience Consulting Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Amir Kviatkovsky Kviatkovsky</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>CFO</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Panaya Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Changhyeok Kwon</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Senior Professional</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Christina Kyriasoglou</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Tech Reporter</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Bloomberg LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Martin Kögel</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>VOQUZ Labs</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Arvind LAKSHMAN</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>BioMerieux Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>JUNG HYUN LIM</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Group leader</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Blueward INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Kun-Yi LIM</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Principal Tax Product...</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Autodesk Asia Pte Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>ROBSON LUIS DA CUNHA</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Product Director</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Invent Software Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Jonathan La Blunda</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Gerente Comercial Interpac...</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>INTERPACK S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Marc Laberge</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>SCM Solution Director</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>DBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Rosemary Lafferty</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Business Excellence...</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Americas Styrenics LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Brian Laird</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Exec...</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>SAP America Public Sec.(Newtown Sq)</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Nick Lake</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Digital and Innovation Manager - Logistics</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>JLR</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Vijay Lakhanpal</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>AVP - CLOUD I...</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Celebal Technologies Pvt Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Jose Luis Lanchas</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Global Events</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Nicholas Landolfi</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Customer Success Partner</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Ariba Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Mark Landrosh</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Industry Executive Advis...</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Joanne Lang</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Natuvion Americas, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Marcus Lange</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Global Partner Manager for S...</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Dynatrace LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Juan Carlos Lara</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>KMMP...</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Joseph Lattanzi</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Logistics Business Analyst</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Lincoln Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Sean Laughlin</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Product Marketing Direct...</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>George Lawrie</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Senior Dir...</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>SAP Industries (Newtown Square)</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Julian Lebowitz</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Director SAP and Busines...</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Centerra Gold Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Austin Ledesma</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Account Director</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Solace</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>DaeWon Lee</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Blueward inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Hye Jin Lee</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Woongjin Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Jang Moo Lee</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>System Engineer</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>LG CNS America Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Juhong Lee</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>SAP Korea Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Steven Leighton</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Head Digital &amp; Inn...</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Dan Lemashov</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Sr. Finance SSE</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Bobbi Lemoshov</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>IMS Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Dave Leong</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Principle - High Tech Strategic Ac...</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Bristlecone</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>David Leslie</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Software Engineer in Test</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>FlightSafety</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Brent Lewis</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Sr. Mgr. Data...</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Armstrong World Industries, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Kelly Lewis</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Director SAP Ap...</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Brown-Forman Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Verena Leymann</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Vice President and Head of Corporat...</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Al Limaye</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>LSInextGen</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Mara Lincoln</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Sr Sponsorship Engagement Direct...</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Freeman</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Robert Lindberg</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Director of Ent. Sys</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>CHS Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Angela Lipscomb</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>IT Manager</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>DTE Electric Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Andrew Little</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Canadian Blood Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Noelia Llobera</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Sasami</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Gwyneth Lloyd-Jones</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Accenture Japan Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Kirk Logan</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>VP Supply Chain, C...</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C829"/>
+  <dimension ref="A1:C884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -13567,7 +13567,6 @@
           <t>Makoto Kurimoto</t>
         </is>
       </c>
-      <c r="B782" t="inlineStr"/>
       <c r="C782" t="inlineStr">
         <is>
           <t>キヤノンマーケティングジャパン株式会社</t>
@@ -14370,6 +14369,933 @@
       <c r="C829" t="inlineStr">
         <is>
           <t>Pittsburgh, SAP America</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Maruti Kampli</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Director - API Digital Integrations</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Miraclesoft</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Hideaki Kanamori</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Principal Project Manager</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Masaya Kanatani</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Project M...</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>BENIC SOLUTION CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Sandeep Kandirelli</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Tachyon Technologies LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Nadine Kanja</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Global Head Industry Business Unit...</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Saumya Kapoor</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Global Head of Sales, Planni...</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>SAP UK Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Kiran Kumar Karanam</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>IT SAP</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>FlightSafety International Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Eswar Karnam</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>ERP Associate Director</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Stefanini</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Srinivas Karnati</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Director, Digital Tr...</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Tachyon Technologies LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Srinu Karuturi</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>SCSM-Procurement</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>New York - Hudson Yards</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Mariusz Karwowski</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>SAP Architect</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>SLAVIA CONSULTING LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Vivek Kasera</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Associate Vice President</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Birlasoft</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Sean Kask</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Chief AI Strategy Officer</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>SAP (Schweiz) AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Sasi Kathirasen Mani</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>SENIOR VICE PRESIDE...</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>SAP Australia Pty Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Chaz Kattamuri</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Client Partner</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>TSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Tony Kavadas</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Chief Sales Officer</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Mediafly</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>JR Kavanagh</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Sr Account Exec - SCM</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Masayoshi Kawase</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>AssistantMana...</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>NTT DATA Japan Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Kentaro Kazama</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>SectionManager</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>JSOL Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Cristina Kazda</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Director of IT, Commercial</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Ecolab Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Steve Kelchen</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Sr Account Executive</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>TotalTek</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Sean Kelly</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>BlackJet Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Sarah Kennedy</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>VP, SAP Services</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Aisling Keogh</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Coveo Solutions Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Shigeki Keumi</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>BU Head, General Manager</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Hitachi Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>George Kezhakekuttiyil</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>SBU Leader</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Darshana Khadke</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>SAP Business Analyst</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>KNPC Holdco, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Junghyun Kim</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Senior Director</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Samsung Electronics Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Ron King</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>VP, Sales Executive</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Deloitte Consulting LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Kaede Kitabatake</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Kyndryl Japan KK</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Hiroshi Kitano</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>EY Strategy and Consulting Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Adam Kiwon</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>whitepaper.id GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Jason Klimas</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Functional An...</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Hellermanntyton Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Jonathon Kline</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>EBS Deputy Portfo...</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Defense Logistics Agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Edward Kloczkowski</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Director of Information Te...</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Paul's Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Candice Knauss</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr"/>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>American Equity Investment Life Insurance C...</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Motoki Kobashi</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Director, PFC sales3</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Faith Koch</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>HR Coordi...</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Basin Electric Power Cooperative</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Gerard Koelmeyer</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Customer References</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Christian Koestler</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Global Director, Client...</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Hiroki Komine</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>営業</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>JFE Systems,Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Hiroki Komiyama</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Gen...</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>NTT DATA Global Solutions Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Srikanth Kondagunta</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Information Systems Offi...</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>The United Nations</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Brian Kooistra</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Facilities Syste...</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Exact Sciences Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Chris Kornely</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Aflac, Incorporated</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Chris Kosrow</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Donna</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Mykola Kosyak</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>SAP Techn...</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>System Design Analysis (SDA) inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Kotani Kotani</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>BROTHER INDUSTRIES,LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Matt Kramer</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>VP, Supply Chain Manag...</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Filip Kransfeld</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Practice Director</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Avvale Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Stephan Kreipl</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Head of Product Management SAP I...</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Joel Kremke</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>SVP, WW Partner Alliances &amp; Progr...</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>OpenText</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Jens Kreuter</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Executive Communic...</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>zeit:raum digital GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>Libby Krider</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>TrueCommerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>Gopal Krishnan</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr"/>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>INK IT Solutions and Consulting Private Limite...</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C884"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -14973,7 +14973,6 @@
           <t>Candice Knauss</t>
         </is>
       </c>
-      <c r="B865" t="inlineStr"/>
       <c r="C865" t="inlineStr">
         <is>
           <t>American Equity Investment Life Insurance C...</t>
@@ -15292,10 +15291,375 @@
           <t>Gopal Krishnan</t>
         </is>
       </c>
-      <c r="B884" t="inlineStr"/>
       <c r="C884" t="inlineStr">
         <is>
           <t>INK IT Solutions and Consulting Private Limite...</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>Pam Jeffries</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr"/>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Cognizant Technology Solutions U.S. Corporat...</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Sergey Jermakov</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Senior Partner</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>SIA Clarity Labs</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Jessica Jestis</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Technology Manager</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Southwest Airlines Co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Rajat Jetly</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>VP - Sales and BD</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>INNOVISE IT LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Mithlesh Jha</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Managing p...</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Noshtek Consulting Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Jim Thomas Jim</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr"/>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Wietersdorfer Finanz und Beteiligungs GmbH...</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Jurema Johnson</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Business Development</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>ReleaseOwl</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Vijay Johnwesley</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Sr Mgr SAP Delivery</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Leprino Foods Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Brian Jones</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Services Partner Manager</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Darius Jones</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Senior Value Advisor</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Sony Jose</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>FlightSafety International Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Sunny Joshi</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Regional Sales Leader</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Veritas Prime, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Aaron Joy Joy</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Business Consultant</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Travis County, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Kenneth Juengling</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Manager...</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Pennsylvania Turnpike Commission</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Christian Jäkel</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Schwarz Digits</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>GYOYEON KIM</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Team Manager</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Blueward INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Kimikazu Kabata</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Solution Advisor Expert</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Jeremy Kahl</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Procureme...</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Los Alamos National Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Yogi Kalra</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>INNOVAPTE CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Armin Kaltenmeier</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Partner, Global Chief...</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Ernst &amp; Young U.S. LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Dishank Kamath</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Program Manager</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>Ravi Kishore Kamma</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Principal Produc...</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>ReleaseOwl Private Limited</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -15303,7 +15303,6 @@
           <t>Pam Jeffries</t>
         </is>
       </c>
-      <c r="B885" t="inlineStr"/>
       <c r="C885" t="inlineStr">
         <is>
           <t>Cognizant Technology Solutions U.S. Corporat...</t>
@@ -15384,7 +15383,6 @@
           <t>Jim Thomas Jim</t>
         </is>
       </c>
-      <c r="B890" t="inlineStr"/>
       <c r="C890" t="inlineStr">
         <is>
           <t>Wietersdorfer Finanz und Beteiligungs GmbH...</t>
@@ -15660,6 +15658,23 @@
       <c r="C906" t="inlineStr">
         <is>
           <t>ReleaseOwl Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Susan Cunningham</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Senior Programmer / An...</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Unisys Corporation</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C907"/>
+  <dimension ref="A1:C958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -15678,6 +15678,869 @@
         </is>
       </c>
     </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Anindya Gaine</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Program Director SAP Imp...</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Fluor Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Suresh Gali</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>IT Solutions Architect</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>NRG Energy, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Francisco Galindo</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Sr Director IT finance</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>George Galindo</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Account Director</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>SAP Industries, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Glenn Gammon</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Director of S...</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>TLP Management Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Joanne Gammon</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Ariba US Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Suman Gandhe</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>FICO Consultant</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Gary Gang</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Client Engagement Manag...</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Veritas Prime, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Javier Garcia</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Commercial Dir...</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Smartshift Technologies, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Jose Garcia</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Sr. Director, SAP Practice Lead</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Nsight, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Amit Garussi</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>VP Product</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Panaya Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Patti Gary</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Senior Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Tyson Foods, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Dino Gattola</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Senior Account Executive, Sup...</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>SAP CANADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Boris Gebhardt</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Manager...</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>STARTEAM Global Germany GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Frank Genevieve</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>SAP Sales Executive</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>NTT DATA Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Brent George</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>SAP Advisor</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Tricentis GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Jacob George</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Raytheon</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Mark George</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Program Direct...</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Delaware North America LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Eliza Georgescu</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Senior Manager, Partner...</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Collibra Belgium BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Kimberly Gershenzon</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Finance Account Executi...</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Deana Gervais</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Strategic Sales Support Specialist</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Pferd Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Stefanie Geßler</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>SAP EWM Expert</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>4flow SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Keya Gholap</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>KATBOTZ LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Benedikt Gieger</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Strategic Projects, SAP SCM</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Richard Gilbert</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Head of B2B Partner...</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Worldpay (UK) Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Stacey Gilbert</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Merck</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Don Gillespie</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Senior Director Strategic Alliances</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>ADP, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Joe Golemba</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Global Head, Strategic Alliances...</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Vistex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Raul Gomez</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>VP of IT</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Hexagon AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Santiago Julian Gomez</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Supply Chain Regional Man...</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>INTERPACK S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Moises Gonzalez</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Client Engagement Manag...</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Veritas Prime, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Oziel Gonzalez</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>VA Head Mexico</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>SAP Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Nelson González</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Subgerente e Operaciones...</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Grupo Kaufmann</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Senthil Gopalan</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>D-1 (SVP)</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>The United Nations</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Pooven Govender</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>APAC CLOUD ARCHITE...</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>SAP Australia Pty Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Christine Graham</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Lakeview Farms, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Geoff Gray</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Head of Product</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>The Config Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Andrew Greaves</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Sen...</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>SAPOCOM Technologies Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Samuel Grenade</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr"/>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Coveo Solutions Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Betsy Griffin</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Senior Account Executive</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Paula Griffin</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Seni...</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Medical College of Virginia Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Nicole Griffith</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Sr. Director, SAP Alliance</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Protera</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Tim Grochowski</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Senior Cloud Executive</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Anette Grossmueller</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Head of Cross Product Management,...</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Scott Groth</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Directir, ERP Architect</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Pfizer, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>John Grzybek</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Senior SAP Projec...</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Fujitsu North America, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Rodolfo Guerrero</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>GBM Dominicana</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Alex Guglielmetti</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>VP - IT Advisor</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Pantexan Deterrence</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Patricia Guillermo</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>It Lead</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Kellanova/Mars</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Dmitri Guinzbourg</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Team Lead/Supervisor</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Air Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Timothy Guizon</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Finance Manager</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Henry Company LLC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C958"/>
+  <dimension ref="A1:C1012"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -16330,7 +16330,6 @@
           <t>Samuel Grenade</t>
         </is>
       </c>
-      <c r="B946" t="inlineStr"/>
       <c r="C946" t="inlineStr">
         <is>
           <t>Coveo Solutions Inc</t>
@@ -16538,6 +16537,916 @@
       <c r="C958" t="inlineStr">
         <is>
           <t>Henry Company LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Sriram Hariharasubramanian</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Partner, Tech Consult...</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>EY Global Services Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Lori Harner</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Global Vice President, Pr...</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Melissa Harris</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>IT Program Manager</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Masco Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Paul Harris</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Senior Director, SAP Basi...</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Varsity Brands, LLC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Joe Hartnett</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>OpenText</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Richard Hatton</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>VP Platform Engin...</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>NBCUniversal Media, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Kishie Hattori</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Chief Partner Officer</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Chelsea Hebb</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Director, Cons...</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Collective Insights Consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Heiko Hecht</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>IBIS America Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Tess Heiligers</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Business Advisor to SVP ERP Tranfo...</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>BP P.L.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Christian Heinrich</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Chief Solutions Officer &amp; Membe...</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>sovanta AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Isabel Heinz</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Sales Consultant</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>anuwo GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>David Heitz</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Account Director</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Nicolas Helmstaetter</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Treasury Expert</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Frauke Hering</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Sovereign Cloud Portfolio Manager</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Adriana Hernandez</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Head Architecture</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Bachoco, S.A. de C.V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Sergio Hernandez</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Head of IT Solutions Ma...</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Valarie Hernandez</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Business Analyst</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Travis County, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Juan Manuel Hernandez Bello</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>GERENTE SERVICI...</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Organizacion Terpel S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Ralph Hess</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Executive...</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Navigator Business Solutions, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Chris Hilko</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Industry Account Executi...</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Scott Hillhouse</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Industry Account Executi...</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Brandon Hilton</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Enterprise Syst...</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Eastman Chemical Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Kent Hinkemeyer</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr"/>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer Global Business Services B.V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Gary Hinton</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Managing Partner - Shell</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>SAP Nederland BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>David Hoag</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Sr. Manager IT SAP</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Builders Firstsource, Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Stefan Hoffmann</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Vice President Strategy &amp; Soluti...</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Argano LLC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Robert Holland</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Chief Re...</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Wellesley Information Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Michael Hom</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Global Head of Digit...</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Jpmorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Ricardo Honda</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Head of BTM Brazil</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>SAP Brasil Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Keith Hontz</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Global Head of SAP Alliance</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Zscaler, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Stuart Hooker</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr"/>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Shell Information Technology International B.V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Norma Hopkins</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>SLED Field Marketin...</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>SAP Canada - Waterloo</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Jeffrey Hornibrook</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Erin Houston Houston</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>IT Solution Manager</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>MSA the Safety Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Aaron Hovick</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Asst. Director</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Hy-Vee, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Mike Howard</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Thinklogicx</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Hector Hoz</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>VP Solution Advisory Spend...</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>SAP Brasil Ltda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Haibo Huang</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Senior Director</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Holina Huang</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Head of CE&amp;A of CS&amp;D...</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>SAP Taiwan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Yvania Huertas Vargas</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Manager/Head o...</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Banco de Crédito del Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Josh Hulme</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>INSPYR Solutions, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Jens Hungershausen</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Chairman of the Board</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>DSAG eV</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Ryan Hurney</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Sr. Manager</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>DXC Technology Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Farheen Hussain</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Solution - Customer Suc...</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Omar Hussein Olmedo</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Poject Manager</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Bachoco, S.A. de C.V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Jared Hyde</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>VP / Assistant GM, Project Phoenix</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>CRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>KAZUSHI INA</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>JFE Systems,Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>Manabu Ichinogo</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Senior Principal</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Open Text K.K.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>TOSHIKATSU Ikeuchi</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>General...</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>NEC Networks &amp; System Integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Masakazu Imanaga</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Head of Process Industr...</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Vincent Immordino</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Director, Private Equity &amp; Canada Sales</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Esker</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Akari Inada</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>ABeam Systems Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Tatsuya Inagaki</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Sony Global Solutions Inc.</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1012"/>
+  <dimension ref="A1:C1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -16937,7 +16937,6 @@
           <t>Kent Hinkemeyer</t>
         </is>
       </c>
-      <c r="B982" t="inlineStr"/>
       <c r="C982" t="inlineStr">
         <is>
           <t>Wolters Kluwer Global Business Services B.V.</t>
@@ -17069,7 +17068,6 @@
           <t>Stuart Hooker</t>
         </is>
       </c>
-      <c r="B990" t="inlineStr"/>
       <c r="C990" t="inlineStr">
         <is>
           <t>Shell Information Technology International B.V.</t>
@@ -17447,6 +17445,397 @@
       <c r="C1012" t="inlineStr">
         <is>
           <t>Sony Global Solutions Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Al Ingallinera Jr</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>VP, Product Management...</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Baton Simulations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Babu Inti</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>CIO</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>CommScope, Inc. of North Carolina</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Rick Isom</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Ken Ito</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Division Manager</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>TIS Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Morgan Jacob</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Director Enterprise</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>L B Foster Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Amith Kumar Jada</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>SAP Progr...</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Mahi Jadhav</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>QTC Transformation Man...</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Acuiti Labs Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Chung JaePhil</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>SAP Korea Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Andrew Jaehnig</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>SAP Manager</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>ALKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Alon Jaffe</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>VP Fe...</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>SAP America Public Sec.(Washington)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Anand Jain Jain</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>MD - Enterprise Technolo...</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Eisner and Amper</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Mehga Jain</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Enterprise Architect - M...</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>SAP INDIA PVT. LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Naren Jain</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Managing Dire...</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>PricewaterhouseCoopers LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Prateek Jain</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Lead Consultant</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Celebal Technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Soumyaa Jain</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Content Specialist</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Cognitus Consulting LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Raj Jakhete</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Vice President, I...</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Oliver Healthcare Packaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>William Jan</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Senior Value Advisor</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Nathan Janardhana</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Information Systems Offi...</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>The United Nations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Lars Janitz</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Senior Exe...</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>NTT DATA Business Solutions AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Brian Janzen</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>SVP, Continuous Impr...</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Graham Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Jose Antonio Jaramillo</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Pyramid Consulting SAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Pawel Jaroszewicz</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Senior Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Onapsis Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>Suneth Jayawardhane</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Senior Principal, Valu...</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>SAP America (Reston)</t>
         </is>
       </c>
     </row>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C493"/>
+  <dimension ref="A1:C516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4285,748 +4285,752 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Marco Sanna</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr"/>
+          <t>Daniel Ibarra</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SAP Solution Architect</t>
+        </is>
+      </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>cbs Corporate Business Solutions Unternehm…</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Rajesh Sarin</t>
+          <t>Kenji Ichikawa</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Global Head - ERP Platf…</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Hitachi, Ltd.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Subhayu Sarkar</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr"/>
+          <t>Carolyn Ingram</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>VP, Finance Transformation</t>
+        </is>
+      </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions U.S. Corporat…</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Michael Sass</t>
+          <t>Marco Innocenti</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>VP, IT</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Alphatec Holdings, Inc.</t>
+          <t>SAP Italia S.p.A.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Yuki Sato</t>
+          <t>Hiroshi Inoue</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Business Consulting…</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>EY Global Services Ltd</t>
+          <t>NTT DATA Japan Corporation</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Naoya Satomi</t>
+          <t>Marc Isenberg</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>VP, Solution Sales</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>NTT DATA Japan Corporation</t>
+          <t>Tricentis</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Klaus-Peter Sauer</t>
+          <t>Anjali Israni</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Product Manager SAP Business Data…</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Deloitte</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Vivek Saurabh</t>
+          <t>Sandra Iverson</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Director of Business Developm…</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>GyanSys, Inc.</t>
+          <t>3M Company</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Tom Savoie</t>
+          <t>Pradeep Iyengar</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Customer Solution Director</t>
+          <t>VP Solution Engineering</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>EverBlue Partners</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Andreas Schaefer</t>
+          <t>Lakshmi Iyer</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CRO SCM MEE</t>
+          <t>Director, Cloud Practice</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>James Scheel</t>
+          <t>Rajesh Iyer</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Solution Sales Executive…</t>
+          <t>Principal Consultant</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Capgemini</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Ralf Scherer</t>
+          <t>Sunil Kapoor</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Global Transfo…</t>
+          <t>Head of Digital Transformation</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>Wipro Limited</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Kathrin Schmalzing</t>
+          <t>Yuki Kato</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Brian Schmidt</t>
+          <t>Megan Keller</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Principal I.T. Architect</t>
+          <t>Director, Strategic Partnerships</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Mckesson</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Jan Schneider</t>
+          <t>Aarti Khanna</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>GVP Head of AI Partner Ecosystem</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>HCL Technologies</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Rebecca Schneider</t>
+          <t>Daniel Kim</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Project Consultant</t>
+          <t>VP Engineering</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Samsung SDS America</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Tonia Schneider</t>
+          <t>Soo-Jin Kim</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Principal Accoun…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Amazon Web Services, Inc.</t>
+          <t>LG CNS Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Pete Scholtens</t>
+          <t>Heinrich Klein</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Managing Direc…</t>
+          <t>Head of CFO Advisory</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Delaware North America LLC</t>
+          <t>SAP Deutschland SE &amp; Co.KG</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Axel Schroeder</t>
+          <t>Rebecca Knight</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Chief Architect</t>
+          <t>Senior Solution Sales Executive</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Christoph Schroeder</t>
+          <t>Andrei Kovac</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Global Head, Industry Business Unit…</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Carsten Schuetz</t>
+          <t>Maria Kowalski</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>VP, Global He…</t>
+          <t>Product Manager</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp; Co.KG</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Michael Schultz</t>
+          <t>Stefan Krause</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Value Advisor</t>
+          <t>VP, Cloud Operations</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Floyd Scott</t>
+          <t>Nikhil Krishnan</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Customer Success Ma…</t>
+          <t>Director, Industry Solutions</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>LG CNS America, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Cindy Seaburn</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>S…</t>
-        </is>
-      </c>
+          <t>Marco Sanna</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
         <is>
-          <t>The School Board of Duval County Florida</t>
+          <t>cbs Corporate Business Solutions Unternehm…</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Kress Sebastian</t>
+          <t>Rajesh Sarin</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Head of AI, Platforms &amp; Data</t>
+          <t>Global Head - ERP Platf…</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Sandeep Sehgal</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Vice-President, SAP Services</t>
-        </is>
-      </c>
+          <t>Subhayu Sarkar</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Aparna Seksaria</t>
+          <t>Michael Sass</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Global Director, Life Sciences IBU</t>
+          <t>VP, IT</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Alphatec Holdings, Inc.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Sam Seth</t>
+          <t>Yuki Sato</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>GM Retail, Co…</t>
+          <t>Business Consulting…</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>On Demand Technologies, Inc.</t>
+          <t>EY Global Services Ltd</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Rahul Sethi</t>
+          <t>Naoya Satomi</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Sr. Client Advocate</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Corevist Inc</t>
+          <t>NTT DATA Japan Corporation</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Kanan Sethi Jawa</t>
+          <t>Klaus-Peter Sauer</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Product Manager SAP Business Data…</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bombardier Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>JUAN IGNACIO Sevilla</t>
+          <t>Vivek Saurabh</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>GERENTE DE PRODUCCIÓN</t>
+          <t>Director of Business Developm…</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>plasticaucho</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Harshal Shah</t>
+          <t>Tom Savoie</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Customer Solution Director</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Elsner Technologies pvt ltd</t>
+          <t>EverBlue Partners</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Vinay Shah</t>
+          <t>Andreas Schaefer</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Value Advisor</t>
+          <t>CRO SCM MEE</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Dawn Shakeshaft</t>
+          <t>James Scheel</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Solution Sales Executive…</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Associated Feed &amp; Supply Co.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Aditya Shankar</t>
+          <t>Ralf Scherer</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Co-fou…</t>
+          <t>Global Transfo…</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Sookti AI Innovations Private Limited</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Hari Shankar</t>
+          <t>Kathrin Schmalzing</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Associate Vice Presi…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Murali Shanmugam</t>
+          <t>Brian Schmidt</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Business AI Strategy A…</t>
+          <t>Principal I.T. Architect</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>SAP Australia Pty Ltd</t>
+          <t>Mckesson</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Chris Shano</t>
+          <t>Jan Schneider</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Marketing Head,…</t>
+          <t>GVP Head of AI Partner Ecosystem</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>ATOS INTERNATIONAL SAS</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Ashuka Sharma</t>
+          <t>Rebecca Schneider</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>Project Consultant</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>SAP America Inc. (Hudson Yards)</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Dhruv Sharma</t>
+          <t>Tonia Schneider</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Assistant Vice Preside…</t>
+          <t>Principal Accoun…</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Celebal Technologies</t>
+          <t>Amazon Web Services, Inc.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Priya Sharma</t>
+          <t>Pete Scholtens</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Glo…</t>
+          <t>Managing Direc…</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>SNP TRANSFORMATIONS SEA PTE. LTD.</t>
+          <t>Delaware North America LLC</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Shantanu Sharma</t>
+          <t>Axel Schroeder</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Architecture Advisor</t>
+          <t>Chief Architect</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SAP America (Reston)</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Suchit Sharma</t>
+          <t>Christoph Schroeder</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Assistan…</t>
+          <t>Global Head, Industry Business Unit…</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Celebal Technologies Americas Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Heidi Sheehan</t>
+          <t>Carsten Schuetz</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Vice President, Information Technol…</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr"/>
+          <t>VP, Global He…</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SAP Deutschland SE &amp; Co.KG</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Anastasiya Shemanskaya</t>
+          <t>Michael Schultz</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>CFO Customer Office</t>
+          <t>Value Advisor</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5038,1705 +5042,1705 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Sameer Shepal</t>
+          <t>Floyd Scott</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Global Lead - SAP…</t>
+          <t>Customer Success Ma…</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Tata Technologies Limited</t>
+          <t>LG CNS America, Inc.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Colby Sheridan</t>
+          <t>Cindy Seaburn</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Industry Executive Advis…</t>
+          <t>S…</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>The School Board of Duval County Florida</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Scott Sherman</t>
+          <t>Kress Sebastian</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SVP Information Te…</t>
+          <t>Head of AI, Platforms &amp; Data</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>The Pittsburgh Paints Co.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Yasuhiro Shibata</t>
+          <t>Sandeep Sehgal</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Department Manager</t>
+          <t>Vice-President, SAP Services</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>JSOL Corporation</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Allon Shiff Shiff</t>
+          <t>Aparna Seksaria</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Value Advis…</t>
+          <t>Global Director, Life Sciences IBU</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>SAP Industries (Washington DC)</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Dong Moon Shin</t>
+          <t>Sam Seth</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>GM Retail, Co…</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Pan Ocean Co., Ltd.</t>
+          <t>On Demand Technologies, Inc.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Mary Shinn</t>
+          <t>Rahul Sethi</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Managing Director, SAP K…</t>
+          <t>Sr. Client Advocate</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>SAP Korea Limited</t>
+          <t>Corevist Inc</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Tomoya Shinozaki</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr"/>
+          <t>Kanan Sethi Jawa</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>フォーティエンスコンサルティング株式会社…</t>
+          <t>Bombardier Inc.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Nobunori Shiono</t>
+          <t>JUAN IGNACIO Sevilla</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>IT…</t>
+          <t>GERENTE DE PRODUCCIÓN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>株式会社ベイカレントコンサルティング</t>
+          <t>plasticaucho</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Krista Shirley</t>
+          <t>Harshal Shah</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Expand Energy Corporation</t>
+          <t>Elsner Technologies pvt ltd</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Lisa Shober</t>
+          <t>Vinay Shah</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Mana…</t>
+          <t>Value Advisor</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Air Products and Chemicals, Inc</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Olga Shumikhina</t>
+          <t>Dawn Shakeshaft</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Umoja HCM Team Lead</t>
+          <t>Controller</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>The United Nations</t>
+          <t>Associated Feed &amp; Supply Co.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Andrew Sigler</t>
+          <t>Aditya Shankar</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Account Director</t>
+          <t>Co-fou…</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Syntax Systems USA LP</t>
+          <t>Sookti AI Innovations Private Limited</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Mikolaj Sikorski</t>
+          <t>Hari Shankar</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Strategic Partner Initiatives</t>
+          <t>Associate Vice Presi…</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>SAP Ireland Ltd.</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Jonathan Silva</t>
+          <t>Murali Shanmugam</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Instituição de Pagament…</t>
+          <t>Business AI Strategy A…</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Nu Pagamentos S.A</t>
+          <t>SAP Australia Pty Ltd</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Renato Silva</t>
+          <t>Chris Shano</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Solutions Sa…</t>
+          <t>Marketing Head,…</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Globant Brasil Consultoria Ltda</t>
+          <t>ATOS INTERNATIONAL SAS</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Sergei Silva</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr"/>
+          <t>Ashuka Sharma</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Vistex</t>
+          <t>SAP America Inc. (Hudson Yards)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Felix Silvagnoli</t>
+          <t>Dhruv Sharma</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SAP Platform Owner</t>
+          <t>Assistant Vice Preside…</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>BP International Limited</t>
+          <t>Celebal Technologies</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Gianluca Simeone</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Global SAP CTIO &amp; AI Leader</t>
+          <t>Glo…</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SNP TRANSFORMATIONS SEA PTE. LTD.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Cintia Simonelli</t>
+          <t>Shantanu Sharma</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Managing Part…</t>
+          <t>Architecture Advisor</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>SAP Argentina - Buenos Aires</t>
+          <t>SAP America (Reston)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Eric Simonson</t>
+          <t>Suchit Sharma</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Director - Product Marke…</t>
+          <t>Assistan…</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Celebal Technologies Americas Inc.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Natalie Singh</t>
+          <t>Heidi Sheehan</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Global Strategic Scale L…</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>SAP AMERICA, INC.</t>
-        </is>
-      </c>
+          <t>Vice President, Information Technol…</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Sukhbir Singh</t>
+          <t>Anastasiya Shemanskaya</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>S…</t>
+          <t>CFO Customer Office</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>The School Board of Duval County Florida</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Vikrant Sisodia</t>
+          <t>Sameer Shepal</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Sr. Product Manager</t>
+          <t>Global Lead - SAP…</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>Tata Technologies Limited</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>David Smith</t>
+          <t>Colby Sheridan</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>VP, Chief Enterprise Ar…</t>
+          <t>Industry Executive Advis…</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>SAP America (Reston)</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Rachel Smith</t>
+          <t>Scott Sherman</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Partner Sales Manager</t>
+          <t>SVP Information Te…</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Docusign Inc</t>
+          <t>The Pittsburgh Paints Co.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Mark Smysor</t>
+          <t>Yasuhiro Shibata</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Business Systems Analyst in Enterpri…</t>
+          <t>Department Manager</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>JSOL Corporation</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Delaiah Snowden</t>
+          <t>Allon Shiff Shiff</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>IT Ana…</t>
+          <t>Value Advis…</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>South Florida Water Management Dist</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Jairo Soares De Matos</t>
+          <t>Dong Moon Shin</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Analyst - SAP Busi…</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Canadian Blood Services</t>
+          <t>Pan Ocean Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Michael Somerville</t>
+          <t>Mary Shinn</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Sales Executive</t>
+          <t>Managing Director, SAP K…</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Checkout.com</t>
+          <t>SAP Korea Limited</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>YoonWon Song</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>IT Director</t>
-        </is>
-      </c>
+          <t>Tomoya Shinozaki</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>i-SENS, Inc.</t>
+          <t>フォーティエンスコンサルティング株式会社…</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Dag Terje Sorlie</t>
+          <t>Nobunori Shiono</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>IT…</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>株式会社ベイカレントコンサルティング</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Thiago Souza</t>
+          <t>Krista Shirley</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>IT CO…</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>MINERACAO SERRAS DO OESTE LTDA</t>
+          <t>Expand Energy Corporation</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Meik Spanowsky</t>
+          <t>Lisa Shober</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Mana…</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>Air Products and Chemicals, Inc</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Thorsten Spihlmann</t>
+          <t>Olga Shumikhina</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Head of Business Development for T…</t>
+          <t>Umoja HCM Team Lead</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>The United Nations</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>TD Srinivasan</t>
+          <t>Andrew Sigler</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Industry…</t>
+          <t>Account Director</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>SAP Public Services, Inc. (Hudson Y</t>
+          <t>Syntax Systems USA LP</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Mike Stafford</t>
+          <t>Mikolaj Sikorski</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Senior ABAP Developer</t>
+          <t>Strategic Partner Initiatives</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Titan Ventures LLC</t>
+          <t>SAP Ireland Ltd.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Jennifer Stapleton</t>
+          <t>Jonathan Silva</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>VP of Accounting Strategy &amp;…</t>
+          <t>Instituição de Pagament…</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>American Equity</t>
+          <t>Nu Pagamentos S.A</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>John Stark</t>
+          <t>Renato Silva</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Global Head of SAP Alliance</t>
+          <t>Solutions Sa…</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Loftware</t>
+          <t>Globant Brasil Consultoria Ltda</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Denis Staudt</t>
+          <t>Sergei Silva</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
         <is>
-          <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
+          <t>Vistex</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Maximilian Stein</t>
+          <t>Felix Silvagnoli</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>SAP Product Owner - Treasury CPIT</t>
+          <t>SAP Platform Owner</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>BP International Limited</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Amanda Steiner</t>
+          <t>Gianluca Simeone</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Business Process Architect</t>
+          <t>Global SAP CTIO &amp; AI Leader</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Capgemini</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Dieter Steinmann</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr"/>
+          <t>Cintia Simonelli</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Managing Part…</t>
+        </is>
+      </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Jorrit Steinz</t>
+          <t>Eric Simonson</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Director - Product Marke…</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ChannelEngine.com</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Robert Stemmler</t>
+          <t>Natalie Singh</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Global Alliances &amp; Ec…</t>
+          <t>Global Strategic Scale L…</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Yonathan Stephanos</t>
+          <t>Sukhbir Singh</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>SAP Data &amp; AI Business Group Le…</t>
+          <t>S…</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>The School Board of Duval County Florida</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Patrick Stewart</t>
+          <t>Vikrant Sisodia</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Sr. Product Manager</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Jochen Stiebe</t>
+          <t>David Smith</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Head of Sales Treas…</t>
+          <t>VP, Chief Enterprise Ar…</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Target-Networks GmbH</t>
+          <t>SAP America (Reston)</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Leslie Stoffel</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr"/>
+          <t>Rachel Smith</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Partner Sales Manager</t>
+        </is>
+      </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
+          <t>Docusign Inc</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Miodrag Stojanov</t>
+          <t>Mark Smysor</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Lead Engineer</t>
+          <t>Business Systems Analyst in Enterpri…</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>SEMOS SOFTWARE LLC</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Bojana Stojanovich</t>
+          <t>Delaiah Snowden</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>VP, NA Strategic Partnerships</t>
+          <t>IT Ana…</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Tricentis</t>
+          <t>South Florida Water Management Dist</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Seda Strate</t>
+          <t>Jairo Soares De Matos</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Partner Innovation Lead</t>
+          <t>Analyst - SAP Busi…</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Canadian Blood Services</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Divya Struebing</t>
+          <t>Michael Somerville</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Supply Chain Customer…</t>
+          <t>Sales Executive</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Checkout.com</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Kevin Stupp</t>
+          <t>YoonWon Song</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Director S4 Platform</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>i-SENS, Inc.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Harish Subramanian</t>
+          <t>Dag Terje Sorlie</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Principal Enterprise Arch…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Marc Sudjian</t>
+          <t>Thiago Souza</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Enterprise Architect, SAP So…</t>
+          <t>IT CO…</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Bombardier Inc.</t>
+          <t>MINERACAO SERRAS DO OESTE LTDA</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Hirofumi Sugimoto</t>
+          <t>Meik Spanowsky</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>ABeam Systems Ltd.</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Michael Sukachev</t>
+          <t>Thorsten Spihlmann</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Sr. EA</t>
+          <t>Head of Business Development for T…</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Teranet Inc</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Som Suresh</t>
+          <t>TD Srinivasan</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Man…</t>
+          <t>Industry…</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>SAP Public Services, Inc. (Hudson Y</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Jain Sushant</t>
+          <t>Mike Stafford</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer, F&amp;S…</t>
+          <t>Senior ABAP Developer</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>Titan Ventures LLC</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Scott Sutker</t>
+          <t>Jennifer Stapleton</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Vice President Customer Success…</t>
+          <t>VP of Accounting Strategy &amp;…</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Alpharetta</t>
+          <t>American Equity</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Mergenthaler Sven</t>
+          <t>John Stark</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Global Head of Strategic Central Ser…</t>
+          <t>Global Head of SAP Alliance</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Loftware</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Jereme Swoboda</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Segment Director</t>
-        </is>
-      </c>
+          <t>Denis Staudt</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Avvale, Inc.</t>
+          <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Debra Syring</t>
+          <t>Maximilian Stein</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Senior IT Manager</t>
+          <t>SAP Product Owner - Treasury CPIT</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Entegris, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Kai Szatkowski</t>
+          <t>Amanda Steiner</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Head of Product Sales</t>
+          <t>Business Process Architect</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Natuvion GmbH</t>
+          <t>McKesson</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>MARCO TOMBOLINI</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Global He…</t>
-        </is>
-      </c>
+          <t>Dieter Steinmann</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
       <c r="C339" t="inlineStr">
         <is>
-          <t>DOLCE &amp; GABBANA BEAUTY SRL</t>
+          <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>KAZUSHI TOYOMASU</t>
+          <t>Jorrit Steinz</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Global Direct…</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>MOL Chemical Tankers Pte Ltd</t>
+          <t>ChannelEngine.com</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Stacey Taborelli</t>
+          <t>Robert Stemmler</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Executive Business Partn…</t>
+          <t>Global Alliances &amp; Ec…</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ahmed Taher</t>
+          <t>Yonathan Stephanos</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>SAP Data &amp; AI Business Group Le…</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Al Daajan Trading</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Chieko Takahata</t>
+          <t>Patrick Stewart</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Chief</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>BROTHER INDUSTRIES,LTD.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Arai Takahiro</t>
+          <t>Jochen Stiebe</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Services Delivery Manag…</t>
+          <t>Head of Sales Treas…</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>Target-Networks GmbH</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Eiji Takashina</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Associate Director</t>
-        </is>
-      </c>
+          <t>Leslie Stoffel</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Kyndryl Japan KK</t>
+          <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Tetsushi Takino</t>
+          <t>Miodrag Stojanov</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>大和ハウス工業株式会社</t>
+          <t>SEMOS SOFTWARE LLC</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Makoto Tamura</t>
+          <t>Bojana Stojanovich</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Alliance Group Director</t>
+          <t>VP, NA Strategic Partnerships</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>FUJITSU LIMITED</t>
+          <t>Tricentis</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Chiyuki Tanaka</t>
+          <t>Seda Strate</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Team leader</t>
+          <t>Partner Innovation Lead</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Recruit Co., Ltd.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Steve Tanaka</t>
+          <t>Divya Struebing</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Sr Vice Presid…</t>
+          <t>Supply Chain Customer…</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Blommer Chocolate Company</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Yasuhiro Tanaka</t>
+          <t>Kevin Stupp</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Director S4 Platform</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Recuruit Co.,Ltd.</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Kristin Taner</t>
+          <t>Harish Subramanian</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Chief Marke…</t>
+          <t>Principal Enterprise Arch…</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Vortex Software Consulting, LLC</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Mitchell Tauer</t>
+          <t>Marc Sudjian</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Services Account Execut…</t>
+          <t>Enterprise Architect, SAP So…</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Bombardier Inc.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Roxanna Tavares</t>
+          <t>Hirofumi Sugimoto</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Director, Gl…</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>The Nielsen Company (US), LLC.</t>
+          <t>ABeam Systems Ltd.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Theo Tavrides</t>
+          <t>Michael Sukachev</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Vice Presi…</t>
+          <t>Sr. EA</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>NTT Data Business Solutions, Inc.</t>
+          <t>Teranet Inc</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Jamie Taylor</t>
+          <t>Som Suresh</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Global VP, Strategic Partnerships</t>
+          <t>Man…</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Meghan Taylor</t>
+          <t>Jain Sushant</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Industry Account Ex…</t>
+          <t>Chief Revenue Officer, F&amp;S…</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Samantha Taylor</t>
+          <t>Scott Sutker</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Senior Solutions Account Exec…</t>
+          <t>Vice President Customer Success…</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Alpharetta</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Sarah Taylor</t>
+          <t>Mergenthaler Sven</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Solution Advisor</t>
+          <t>Global Head of Strategic Central Ser…</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Jorge Tercero</t>
+          <t>Jereme Swoboda</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Manager/H…</t>
+          <t>Segment Director</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Asociacion Mutual Sancor Salud</t>
+          <t>Avvale, Inc.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Michael Teti</t>
+          <t>Debra Syring</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior IT Manager</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Carlisle Construction Materials</t>
+          <t>Entegris, Inc.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Suji Thampi</t>
+          <t>Kai Szatkowski</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Head of Product Sales</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>MINDSPRINT PTE. LTD.</t>
+          <t>Natuvion GmbH</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Le Thanh Phong</t>
+          <t>MARCO TOMBOLINI</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Managing Direc…</t>
+          <t>Global He…</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>FPT Japan Holdings Co., Ltd.</t>
+          <t>DOLCE &amp; GABBANA BEAUTY SRL</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Michael Theis</t>
+          <t>KAZUSHI TOYOMASU</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Senior Director, Healthcare Life Scien…</t>
+          <t>Global Direct…</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Icertis</t>
+          <t>MOL Chemical Tankers Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Rene Theriault</t>
+          <t>Stacey Taborelli</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>IT Program Director</t>
+          <t>Executive Business Partn…</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>BRP INC</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Barbara Thrasher</t>
+          <t>Ahmed Taher</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>SR STAFF ARCHITECT</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Tyson Foods, Inc.</t>
+          <t>Al Daajan Trading</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Nissim Titan</t>
+          <t>Chieko Takahata</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Chief</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>4CAST SYSTEMS LTD</t>
+          <t>BROTHER INDUSTRIES,LTD.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>James Tiwari</t>
+          <t>Arai Takahiro</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Services Delivery Manag…</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Intellioz LLC</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Shuhei Toba</t>
+          <t>Eiji Takashina</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Business Engineering Corporation</t>
+          <t>Kyndryl Japan KK</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>John Tocci</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr"/>
+          <t>Tetsushi Takino</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Cbs Corporate Business Solutions America In…</t>
+          <t>大和ハウス工業株式会社</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Oliver Toloui</t>
+          <t>Makoto Tamura</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Director - AI…</t>
+          <t>Alliance Group Director</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Ibase Operations Corp Qualitest</t>
+          <t>FUJITSU LIMITED</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Ray Toma</t>
+          <t>Chiyuki Tanaka</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Senior Principal — Global Strategic Initia…</t>
+          <t>Team leader</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Recruit Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Yuko Tominaga</t>
+          <t>Steve Tanaka</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Research Writer</t>
+          <t>Sr Vice Presid…</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Blommer Chocolate Company</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Laura Tozzo</t>
+          <t>Yasuhiro Tanaka</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>AI Product Lead SAP IBP</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Recuruit Co.,Ltd.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Eero Traagel</t>
+          <t>Kristin Taner</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Chief Marke…</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>IBM Canada Limited</t>
+          <t>Vortex Software Consulting, LLC</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Adam Trahan</t>
+          <t>Mitchell Tauer</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Services Account Execut…</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -6748,1992 +6752,2379 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Evgeny Treskin</t>
+          <t>Roxanna Tavares</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>SAP Alliances Director</t>
+          <t>Director, Gl…</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>The Nielsen Company (US), LLC.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Chetan Tripathi</t>
+          <t>Theo Tavrides</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>oCFO Adoption expert</t>
+          <t>Vice Presi…</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>NTT Data Business Solutions, Inc.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Seshagiri Tripurana</t>
+          <t>Jamie Taylor</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Senior Director</t>
+          <t>Global VP, Strategic Partnerships</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Masaru Tsukahira</t>
+          <t>Meghan Taylor</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Industry Account Ex…</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>TOKYO ELECTRON LIMITED.</t>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Lindsay Tucker</t>
+          <t>Samantha Taylor</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Solution Consultant</t>
+          <t>Senior Solutions Account Exec…</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Docusign</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Paul Turbes</t>
+          <t>Sarah Taylor</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Solution Advisor</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>KPMG LLP</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Treaver Tyler</t>
+          <t>Jorge Tercero</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Tech…</t>
+          <t>Manager/H…</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Meijer Great Lakes Limited Partnership</t>
+          <t>Asociacion Mutual Sancor Salud</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Kotaro Ueda</t>
+          <t>Michael Teti</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>JSUG</t>
+          <t>Carlisle Construction Materials</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Rajkishore Una</t>
+          <t>Suji Thampi</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>President/CEO</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>GyanSys, Inc.</t>
+          <t>MINDSPRINT PTE. LTD.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Bala Parameswara Rao Upadhyay…</t>
+          <t>Le Thanh Phong</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Associate Director</t>
+          <t>Managing Direc…</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Stefanini, Inc.</t>
+          <t>FPT Japan Holdings Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Oscar Uribe</t>
+          <t>Michael Theis</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>Senior Director, Healthcare Life Scien…</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>EDUARDONO S A S</t>
+          <t>Icertis</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>SACHIN VAIDYA</t>
+          <t>Rene Theriault</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Director - Enterprise Commercial…</t>
+          <t>IT Program Director</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Pfizer, Inc.</t>
+          <t>BRP INC</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Jonathan VON RUEDEN</t>
+          <t>Barbara Thrasher</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Chief AI Officer</t>
+          <t>SR STAFF ARCHITECT</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Wagner Valentin</t>
+          <t>Nissim Titan</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Director of Regulated Indust…</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>SAP Brasil Ltda.</t>
+          <t>4CAST SYSTEMS LTD</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Jorge Valles Velásquez</t>
+          <t>James Tiwari</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>KMMP…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
+          <t>Intellioz LLC</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Henri Vallet</t>
+          <t>Shuhei Toba</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>VP Sales, Americas B2B</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mirakl</t>
+          <t>Business Engineering Corporation</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Jeff Van Pelt</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>Founder / Managing Dire…</t>
-        </is>
-      </c>
+          <t>John Tocci</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Javelin Consulting</t>
+          <t>Cbs Corporate Business Solutions America In…</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Meredith Van Wyk</t>
+          <t>Oliver Toloui</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Americas Field Partner…</t>
+          <t>Director - AI…</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Ibase Operations Corp Qualitest</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Joris Van der Donck</t>
+          <t>Ray Toma</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Sr Manag…</t>
+          <t>Senior Principal — Global Strategic Initia…</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Commscope Connectivity Belgium</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Vijay Varee</t>
+          <t>Yuko Tominaga</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Research Writer</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Petsmart LLC</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Suman Varma</t>
+          <t>Laura Tozzo</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>AI Product Lead SAP IBP</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Chris Vassalotti</t>
+          <t>Eero Traagel</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Opentext</t>
+          <t>IBM Canada Limited</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Raju Vedala</t>
+          <t>Adam Trahan</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>CES Business Technologies, LLC</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Asier Vega Sanchez</t>
+          <t>Evgeny Treskin</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>SAP Alliances Director</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Arkyn</t>
+          <t>Argano</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Jennifer Veillon</t>
+          <t>Chetan Tripathi</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Dir Project Controls</t>
+          <t>oCFO Adoption expert</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Fluor Corporation</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Ajay Reddy Velampudi</t>
+          <t>Seshagiri Tripurana</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Senior VP - Sa…</t>
+          <t>Senior Director</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Miracle Software Systems Inc.</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>William Velastegui</t>
+          <t>Masaru Tsukahira</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>JEFE DE TI Y PR…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Plasticaucho Industrial S.A.</t>
+          <t>TOKYO ELECTRON LIMITED.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Rajiv Vemula</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr"/>
+          <t>Lindsay Tucker</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Solution Consultant</t>
+        </is>
+      </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions U.S. Corporat…</t>
+          <t>Docusign</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Sundu Venkataramani</t>
+          <t>Paul Turbes</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Industry Val…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>SAP Industries (Washington DC)</t>
+          <t>KPMG LLP</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Venkat Venkataramani</t>
+          <t>Treaver Tyler</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>Tech…</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Meijer Great Lakes Limited Partnership</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Tom Venner-Crysell</t>
+          <t>Kotaro Ueda</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>ERPeople Solutions Ltd</t>
+          <t>JSUG</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Eduardo Vergara</t>
+          <t>Rajkishore Una</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>President/CEO</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Agrosuper S.A.</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Amit Verma</t>
+          <t>Bala Parameswara Rao Upadhyay…</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>RVP, Head of CFO Advisory…</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>Stefanini, Inc.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Kumar Vidit</t>
+          <t>Oscar Uribe</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Product Marketing M…</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>EDUARDONO S A S</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Lakshmi Vidyashankar</t>
+          <t>SACHIN VAIDYA</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>VP of IT</t>
+          <t>Director - Enterprise Commercial…</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Marvin Engineering Co., Inc.</t>
+          <t>Pfizer, Inc.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Jayant Vikram</t>
+          <t>Jonathan VON RUEDEN</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Cloud Delivery Lead</t>
+          <t>Chief AI Officer</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Accenture LLP</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Yeni Villanueva</t>
+          <t>Wagner Valentin</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Supervisora…</t>
+          <t>Director of Regulated Indust…</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Compañia Minera Antamina S.A.</t>
+          <t>SAP Brasil Ltda.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Robert Vinyard</t>
+          <t>Jorge Valles Velásquez</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>VP and Senior Partner</t>
+          <t>KMMP…</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Thomas Vioux</t>
+          <t>Henri Vallet</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>VP Sales, Americas B2B</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Mirakl</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Anil Visal</t>
+          <t>Jeff Van Pelt</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Founder / Managing Dire…</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>Javelin Consulting</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Clara Viscido</t>
+          <t>Meredith Van Wyk</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Consulting Services Director</t>
+          <t>Americas Field Partner…</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>GEONOSIS</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Paulo Vita Vita</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr"/>
+          <t>Joris Van der Donck</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Sr Manag…</t>
+        </is>
+      </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
+          <t>Commscope Connectivity Belgium</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Ranjan Vitt</t>
+          <t>Vijay Varee</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>AI Compliance Governance Program…</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Petsmart LLC</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Jose Voisin</t>
+          <t>Suman Varma</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Global CIO</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Christina Volk</t>
+          <t>Chris Vassalotti</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Head of Strate…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>Opentext</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Jessica Voyles</t>
+          <t>Raju Vedala</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Account Executive, South</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>CES Business Technologies, LLC</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Sandeep Vyas</t>
+          <t>Asier Vega Sanchez</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Solutio…</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Incture Technologies Private Limited</t>
+          <t>Arkyn</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Thomas von Alm</t>
+          <t>Jennifer Veillon</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>SVP Cross-Solution Services</t>
+          <t>Dir Project Controls</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Fluor Corporation</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Markus von Quast</t>
+          <t>Ajay Reddy Velampudi</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Global Head Industry Ecosystem</t>
+          <t>Senior VP - Sa…</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Miracle Software Systems Inc.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>TATSUO WATANABE</t>
+          <t>William Velastegui</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Principal Cons…</t>
+          <t>JEFE DE TI Y PR…</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>D I SQUARE CORPORATION.</t>
+          <t>Plasticaucho Industrial S.A.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Masayuki Wada</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>SVP, Head of Corporate Digit…</t>
-        </is>
-      </c>
+          <t>Rajiv Vemula</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Fujitsu Limited</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Stephen Wagenheim</t>
+          <t>Sundu Venkataramani</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Senior Sales Executive - Suppl…</t>
+          <t>Industry Val…</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Dallas (Allen)</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Neha Wahi</t>
+          <t>Venkat Venkataramani</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Global Alliance Lead</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>A.T. Kearney, Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Waka Wakabayashi</t>
+          <t>Tom Venner-Crysell</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Associate Partner</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>KPMG Consulting Co., Ltd.</t>
+          <t>ERPeople Solutions Ltd</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Gustavo Waldfogiel</t>
+          <t>Eduardo Vergara</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>LAC HCM Head</t>
+          <t>Manager/Head of Dept</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SAP Argentina - Buenos Aires</t>
+          <t>Agrosuper S.A.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Shashikant Walimbe</t>
+          <t>Amit Verma</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Vice President &amp; Global Head -…</t>
+          <t>RVP, Head of CFO Advisory…</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>LTM LIMITED</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Julie Walker</t>
+          <t>Kumar Vidit</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Sr. Director, Enterprise Applicatio…</t>
+          <t>Product Marketing M…</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Armstrong</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Rob Wallace</t>
+          <t>Lakshmi Vidyashankar</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Senior Manager Digital &amp; In…</t>
+          <t>VP of IT</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Jaguarlandrover</t>
+          <t>Marvin Engineering Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Enzhou Wang</t>
+          <t>Jayant Vikram</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Chief Technology Officer</t>
+          <t>Cloud Delivery Lead</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>City of Tacoma</t>
+          <t>Accenture LLP</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>May Wang</t>
+          <t>Yeni Villanueva</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Direc…</t>
+          <t>Supervisora…</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
+          <t>Compañia Minera Antamina S.A.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Adam Warner</t>
+          <t>Robert Vinyard</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Cost Analyst</t>
+          <t>VP and Senior Partner</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Marathon Cheese Corporation</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Kosuke Watanabe</t>
+          <t>Thomas Vioux</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>PwC</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Takashi Watanabe</t>
+          <t>Anil Visal</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>執行役員</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>JFE Systems,Inc.</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Robert Watson</t>
+          <t>Clara Viscido</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Sr Account Executive</t>
+          <t>Consulting Services Director</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>GEONOSIS</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Ashley Waxman</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Strategic Sales Executive</t>
-        </is>
-      </c>
+          <t>Paulo Vita Vita</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Aevitas IT LLC</t>
+          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Christy Weaver</t>
+          <t>Ranjan Vitt</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Global Demand Generation Man…</t>
+          <t>AI Compliance Governance Program…</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Vertex, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Mike Weaver</t>
+          <t>Jose Voisin</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Senior I…</t>
+          <t>Global CIO</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>True Commerce Inc. TrueCommerce</t>
+          <t>Carmeuse</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Chris Webster</t>
+          <t>Christina Volk</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>SVP IT Strategy &amp; Architecture</t>
+          <t>Head of Strate…</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Ahold Delhaize</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Matt Webster</t>
+          <t>Jessica Voyles</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Director of…</t>
+          <t>Account Executive, South</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Gardner White Furniture Co., Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Patrick Weil</t>
+          <t>Sandeep Vyas</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Solutio…</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Metrie Canada Ltd</t>
+          <t>Incture Technologies Private Limited</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Sarah Weiler</t>
+          <t>Thomas von Alm</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Manager, Busine…</t>
+          <t>SVP Cross-Solution Services</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Ball Horticultural Company</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Adam Werner</t>
+          <t>Markus von Quast</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>VP, Corporate Technology</t>
+          <t>Global Head Industry Ecosystem</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Crocs, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Maddie Werner</t>
+          <t>TATSUO WATANABE</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Director of Delivery Solutions</t>
+          <t>Principal Cons…</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Robra IT</t>
+          <t>D I SQUARE CORPORATION.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Katherine West</t>
+          <t>Masayuki Wada</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>CX Account Executive</t>
+          <t>SVP, Head of Corporate Digit…</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Fujitsu Limited</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Anja Wettling</t>
+          <t>Stephen Wagenheim</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Senior Sales Executive - Suppl…</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>anuwo GmbH</t>
+          <t>Dallas (Allen)</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Charleen Wetzstein</t>
+          <t>Neha Wahi</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>SAP Principal Architect</t>
+          <t>Global Alliance Lead</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>PROSPECTOR, LLC</t>
+          <t>A.T. Kearney, Inc.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Peter Wheatley</t>
+          <t>Waka Wakabayashi</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Enterprise Architect…</t>
+          <t>Associate Partner</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>SAP America (Houston)</t>
+          <t>KPMG Consulting Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Robb White</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr"/>
+          <t>Gustavo Waldfogiel</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>LAC HCM Head</t>
+        </is>
+      </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Peter Widmer</t>
+          <t>Shashikant Walimbe</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Chief of Staff to the Global Head of S…</t>
+          <t>Vice President &amp; Global Head -…</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>LTM LIMITED</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Chad Wiech</t>
+          <t>Julie Walker</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Director of Solution…</t>
+          <t>Sr. Director, Enterprise Applicatio…</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>Armstrong</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Chamnida Wijetilleke</t>
+          <t>Rob Wallace</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Senior Manager Digital &amp; In…</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>The Ducats Group LLC</t>
+          <t>Jaguarlandrover</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Pete Wilkins</t>
+          <t>Enzhou Wang</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>NA Partner Manager</t>
+          <t>Chief Technology Officer</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>City of Tacoma</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Mark Willey</t>
+          <t>May Wang</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Vice…</t>
+          <t>Direc…</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Ed Williamson</t>
+          <t>Adam Warner</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Client Services Lead</t>
+          <t>Cost Analyst</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>XMATERIA LTD</t>
+          <t>Marathon Cheese Corporation</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Monica Willis</t>
+          <t>Kosuke Watanabe</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>HR Strategy and Value A…</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Plano- Legacy West</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Charlotte Wilson</t>
+          <t>Takashi Watanabe</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Senior Manager Strategic Cha…</t>
+          <t>執行役員</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Direct Energy</t>
+          <t>JFE Systems,Inc.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Emily Wisemiller</t>
+          <t>Robert Watson</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Sr Account Executive</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Julia Wolfe</t>
+          <t>Ashley Waxman</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Analyst Relations Manager</t>
+          <t>Strategic Sales Executive</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Aevitas IT LLC</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Jennifer Workman</t>
+          <t>Christy Weaver</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Techn…</t>
+          <t>Global Demand Generation Man…</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Universal Destinations &amp; Experiences</t>
+          <t>Vertex, Inc.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Steven Wright Wright</t>
+          <t>Mike Weaver</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>VP Sales</t>
+          <t>Senior I…</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Acuiti Labs Limited</t>
+          <t>True Commerce Inc. TrueCommerce</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Monty Wurth</t>
+          <t>Chris Webster</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>VP of Operations</t>
+          <t>SVP IT Strategy &amp; Architecture</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Optima Consulting L.L.C.</t>
+          <t>Ahold Delhaize</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Brad Wylie</t>
+          <t>Matt Webster</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Director of…</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Gardner White Furniture Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>KAORI YASHIKI</t>
+          <t>Patrick Weil</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Business Resear…</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services LLC</t>
+          <t>Metrie Canada Ltd</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>YOUNGHO YOO</t>
+          <t>Sarah Weiler</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Team Leader</t>
+          <t>Manager, Busine…</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>LG CNS Co., Ltd.</t>
+          <t>Ball Horticultural Company</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Mohamed YUSUF</t>
+          <t>Adam Werner</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Head of Integrated Toolchain</t>
+          <t>VP, Corporate Technology</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>Crocs, Inc.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Hikaru Yafuso</t>
+          <t>Maddie Werner</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Senior Alliance Director</t>
+          <t>Director of Delivery Solutions</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Robra IT</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Sonoko Yamamoto</t>
+          <t>Katherine West</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Partner Business Manager</t>
+          <t>CX Account Executive</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Osamu Yamazaki</t>
+          <t>Anja Wettling</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Co…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+          <t>anuwo GmbH</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Kenji Yanagi</t>
+          <t>Charleen Wetzstein</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Group Leader</t>
+          <t>SAP Principal Architect</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>ASAHI GROUP JAPAN, LTD.</t>
+          <t>PROSPECTOR, LLC</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>EJ Yang</t>
+          <t>Peter Wheatley</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>IT Deputy Director</t>
+          <t>Enterprise Architect…</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>MediaTek Inc.</t>
+          <t>SAP America (Houston)</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Kiran Yarlagadda Yarlagadda</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Managing…</t>
-        </is>
-      </c>
+          <t>Robb White</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Adroix Corp DBA CodeForce 360</t>
+          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Takayuki Yasuda</t>
+          <t>Peter Widmer</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>Chief of Staff to the Global Head of S…</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>JFE Systems, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Tomoki Yasuda</t>
+          <t>Chad Wiech</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>AssistantMana…</t>
+          <t>Director of Solution…</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>NTT DATA Japan Corporation</t>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Kazuhiro Yonekawa</t>
+          <t>Chamnida Wijetilleke</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Chief/Proj…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>CANON MARKETING JAPAN INC.,</t>
+          <t>The Ducats Group LLC</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Sungeui Yoon</t>
+          <t>Pete Wilkins</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Senior Specialist</t>
+          <t>NA Partner Manager</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Christopher Yope</t>
+          <t>Mark Willey</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>SAP Supply C…</t>
+          <t>Vice…</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>DXC Technology Services LLC</t>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Kohei Yoshimatsu</t>
+          <t>Ed Williamson</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Client Services Lead</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>アズビル株式会社</t>
+          <t>XMATERIA LTD</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>taichi yoshida</t>
+          <t>Monica Willis</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Senior Ma…</t>
+          <t>HR Strategy and Value A…</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>BENIC SOLUTION CORPORATION</t>
+          <t>Plano- Legacy West</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>nakajima yuki</t>
+          <t>Charlotte Wilson</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Senior Manager Strategic Cha…</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Nitori Co., Ltd.</t>
+          <t>Direct Energy</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Stefan Zach</t>
+          <t>Emily Wisemiller</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>VP Global IT</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Wieland Group</t>
+          <t>Molex</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Beau Zaremski</t>
+          <t>Julia Wolfe</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>VP of Sales</t>
+          <t>Analyst Relations Manager</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Yuan Zhang</t>
+          <t>Jennifer Workman</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Senior Project Manager, SAP AI RIG</t>
+          <t>Techn…</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Universal Destinations &amp; Experiences</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Cathy Zhou</t>
+          <t>Steven Wright Wright</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>IT Director, EBS</t>
+          <t>VP Sales</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>Acuiti Labs Limited</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Gustavo Zintak</t>
+          <t>Monty Wurth</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>VP of Operations</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>SWISS MEDICAL S.A.</t>
+          <t>Optima Consulting L.L.C.</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Alina Zuberi</t>
+          <t>Brad Wylie</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Global Content Strategist</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>SAP MENA LLC</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Yoshiaki Agata 縣</t>
+          <t>KAORI YASHIKI</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>Business Resear…</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>AJS株式会社</t>
+          <t>Hitachi Digital Services LLC</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>裕紀 阿保</t>
+          <t>YOUNGHO YOO</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Team Leader</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>FORTIENCE CONSULTING INC.</t>
+          <t>LG CNS Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
+          <t>Mohamed YUSUF</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Head of Integrated Toolchain</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Hikaru Yafuso</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Senior Alliance Director</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Sonoko Yamamoto</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Partner Business Manager</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Osamu Yamazaki</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Co…</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Kenji Yanagi</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Group Leader</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>ASAHI GROUP JAPAN, LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>EJ Yang</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>IT Deputy Director</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>MediaTek Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Kiran Yarlagadda Yarlagadda</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Managing…</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Adroix Corp DBA CodeForce 360</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Takayuki Yasuda</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>JFE Systems, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Tomoki Yasuda</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>AssistantMana…</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>NTT DATA Japan Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Kazuhiro Yonekawa</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Chief/Proj…</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>CANON MARKETING JAPAN INC.,</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Sungeui Yoon</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Senior Specialist</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Christopher Yope</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>SAP Supply C…</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>DXC Technology Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Kohei Yoshimatsu</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>アズビル株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>taichi yoshida</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Senior Ma…</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>BENIC SOLUTION CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>nakajima yuki</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Nitori Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Stefan Zach</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>VP Global IT</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Wieland Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Beau Zaremski</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>VP of Sales</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Yuan Zhang</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Senior Project Manager, SAP AI RIG</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Cathy Zhou</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>IT Director, EBS</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Ecolab Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Gustavo Zintak</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Manager/Head of Dept</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>SWISS MEDICAL S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Alina Zuberi</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Global Content Strategist</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>SAP MENA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Yoshiaki Agata 縣</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>AJS株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>裕紀 阿保</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>FORTIENCE CONSULTING INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
           <t>謙介 青木</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
+      <c r="B516" t="inlineStr">
         <is>
           <t>Manager, Uvance Market Developme…</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
+      <c r="C516" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C516"/>
+  <dimension ref="A1:C493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4285,752 +4285,748 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Daniel Ibarra</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>SAP Solution Architect</t>
-        </is>
-      </c>
+          <t>Marco Sanna</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>cbs Corporate Business Solutions Unternehm…</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Kenji Ichikawa</t>
+          <t>Rajesh Sarin</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Global Head - ERP Platf…</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Hitachi, Ltd.</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Carolyn Ingram</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>VP, Finance Transformation</t>
-        </is>
-      </c>
+          <t>Subhayu Sarkar</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Marco Innocenti</t>
+          <t>Michael Sass</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>VP, IT</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>SAP Italia S.p.A.</t>
+          <t>Alphatec Holdings, Inc.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Hiroshi Inoue</t>
+          <t>Yuki Sato</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Business Consulting…</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>NTT DATA Japan Corporation</t>
+          <t>EY Global Services Ltd</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Marc Isenberg</t>
+          <t>Naoya Satomi</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>VP, Solution Sales</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Tricentis</t>
+          <t>NTT DATA Japan Corporation</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Anjali Israni</t>
+          <t>Klaus-Peter Sauer</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Product Manager SAP Business Data…</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Sandra Iverson</t>
+          <t>Vivek Saurabh</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Director of Business Developm…</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>3M Company</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Pradeep Iyengar</t>
+          <t>Tom Savoie</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>VP Solution Engineering</t>
+          <t>Customer Solution Director</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>EverBlue Partners</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Lakshmi Iyer</t>
+          <t>Andreas Schaefer</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Director, Cloud Practice</t>
+          <t>CRO SCM MEE</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Rajesh Iyer</t>
+          <t>James Scheel</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Principal Consultant</t>
+          <t>Solution Sales Executive…</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Sunil Kapoor</t>
+          <t>Ralf Scherer</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Head of Digital Transformation</t>
+          <t>Global Transfo…</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Wipro Limited</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Yuki Kato</t>
+          <t>Kathrin Schmalzing</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Megan Keller</t>
+          <t>Brian Schmidt</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Director, Strategic Partnerships</t>
+          <t>Principal I.T. Architect</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Mckesson</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Aarti Khanna</t>
+          <t>Jan Schneider</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>GVP Head of AI Partner Ecosystem</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>HCL Technologies</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Daniel Kim</t>
+          <t>Rebecca Schneider</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>VP Engineering</t>
+          <t>Project Consultant</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Samsung SDS America</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Soo-Jin Kim</t>
+          <t>Tonia Schneider</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Principal Accoun…</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>LG CNS Co., Ltd.</t>
+          <t>Amazon Web Services, Inc.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Heinrich Klein</t>
+          <t>Pete Scholtens</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Head of CFO Advisory</t>
+          <t>Managing Direc…</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp; Co.KG</t>
+          <t>Delaware North America LLC</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Rebecca Knight</t>
+          <t>Axel Schroeder</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Senior Solution Sales Executive</t>
+          <t>Chief Architect</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Andrei Kovac</t>
+          <t>Christoph Schroeder</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Global Head, Industry Business Unit…</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Maria Kowalski</t>
+          <t>Carsten Schuetz</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Product Manager</t>
+          <t>VP, Global He…</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SAP Deutschland SE &amp; Co.KG</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Stefan Krause</t>
+          <t>Michael Schultz</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>VP, Cloud Operations</t>
+          <t>Value Advisor</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Nikhil Krishnan</t>
+          <t>Floyd Scott</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Director, Industry Solutions</t>
+          <t>Customer Success Ma…</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LG CNS America, Inc.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Marco Sanna</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
+          <t>Cindy Seaburn</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>S…</t>
+        </is>
+      </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>cbs Corporate Business Solutions Unternehm…</t>
+          <t>The School Board of Duval County Florida</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Rajesh Sarin</t>
+          <t>Kress Sebastian</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Global Head - ERP Platf…</t>
+          <t>Head of AI, Platforms &amp; Data</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Subhayu Sarkar</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr"/>
+          <t>Sandeep Sehgal</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Vice-President, SAP Services</t>
+        </is>
+      </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions U.S. Corporat…</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Michael Sass</t>
+          <t>Aparna Seksaria</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>VP, IT</t>
+          <t>Global Director, Life Sciences IBU</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Alphatec Holdings, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Yuki Sato</t>
+          <t>Sam Seth</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Business Consulting…</t>
+          <t>GM Retail, Co…</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>EY Global Services Ltd</t>
+          <t>On Demand Technologies, Inc.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Naoya Satomi</t>
+          <t>Rahul Sethi</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Sr. Client Advocate</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>NTT DATA Japan Corporation</t>
+          <t>Corevist Inc</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Klaus-Peter Sauer</t>
+          <t>Kanan Sethi Jawa</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Product Manager SAP Business Data…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Bombardier Inc.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Vivek Saurabh</t>
+          <t>JUAN IGNACIO Sevilla</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Director of Business Developm…</t>
+          <t>GERENTE DE PRODUCCIÓN</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>GyanSys, Inc.</t>
+          <t>plasticaucho</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Tom Savoie</t>
+          <t>Harshal Shah</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Customer Solution Director</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>EverBlue Partners</t>
+          <t>Elsner Technologies pvt ltd</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Andreas Schaefer</t>
+          <t>Vinay Shah</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>CRO SCM MEE</t>
+          <t>Value Advisor</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>James Scheel</t>
+          <t>Dawn Shakeshaft</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Solution Sales Executive…</t>
+          <t>Controller</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Associated Feed &amp; Supply Co.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Ralf Scherer</t>
+          <t>Aditya Shankar</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Global Transfo…</t>
+          <t>Co-fou…</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>Sookti AI Innovations Private Limited</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Kathrin Schmalzing</t>
+          <t>Hari Shankar</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Associate Vice Presi…</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Brian Schmidt</t>
+          <t>Murali Shanmugam</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Principal I.T. Architect</t>
+          <t>Business AI Strategy A…</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Mckesson</t>
+          <t>SAP Australia Pty Ltd</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Jan Schneider</t>
+          <t>Chris Shano</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>GVP Head of AI Partner Ecosystem</t>
+          <t>Marketing Head,…</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>ATOS INTERNATIONAL SAS</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Rebecca Schneider</t>
+          <t>Ashuka Sharma</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Project Consultant</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SAP America Inc. (Hudson Yards)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Tonia Schneider</t>
+          <t>Dhruv Sharma</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Principal Accoun…</t>
+          <t>Assistant Vice Preside…</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Amazon Web Services, Inc.</t>
+          <t>Celebal Technologies</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Pete Scholtens</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Managing Direc…</t>
+          <t>Glo…</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Delaware North America LLC</t>
+          <t>SNP TRANSFORMATIONS SEA PTE. LTD.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Axel Schroeder</t>
+          <t>Shantanu Sharma</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Chief Architect</t>
+          <t>Architecture Advisor</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SAP America (Reston)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Christoph Schroeder</t>
+          <t>Suchit Sharma</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Global Head, Industry Business Unit…</t>
+          <t>Assistan…</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Celebal Technologies Americas Inc.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Carsten Schuetz</t>
+          <t>Heidi Sheehan</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>VP, Global He…</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>SAP Deutschland SE &amp; Co.KG</t>
-        </is>
-      </c>
+          <t>Vice President, Information Technol…</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Michael Schultz</t>
+          <t>Anastasiya Shemanskaya</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Value Advisor</t>
+          <t>CFO Customer Office</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5042,1705 +5038,1705 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Floyd Scott</t>
+          <t>Sameer Shepal</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Customer Success Ma…</t>
+          <t>Global Lead - SAP…</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>LG CNS America, Inc.</t>
+          <t>Tata Technologies Limited</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Cindy Seaburn</t>
+          <t>Colby Sheridan</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>S…</t>
+          <t>Industry Executive Advis…</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>The School Board of Duval County Florida</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Kress Sebastian</t>
+          <t>Scott Sherman</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Head of AI, Platforms &amp; Data</t>
+          <t>SVP Information Te…</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>The Pittsburgh Paints Co.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Sandeep Sehgal</t>
+          <t>Yasuhiro Shibata</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Vice-President, SAP Services</t>
+          <t>Department Manager</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>JSOL Corporation</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Aparna Seksaria</t>
+          <t>Allon Shiff Shiff</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Global Director, Life Sciences IBU</t>
+          <t>Value Advis…</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Sam Seth</t>
+          <t>Dong Moon Shin</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>GM Retail, Co…</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>On Demand Technologies, Inc.</t>
+          <t>Pan Ocean Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Rahul Sethi</t>
+          <t>Mary Shinn</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Sr. Client Advocate</t>
+          <t>Managing Director, SAP K…</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Corevist Inc</t>
+          <t>SAP Korea Limited</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Kanan Sethi Jawa</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
+          <t>Tomoya Shinozaki</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bombardier Inc.</t>
+          <t>フォーティエンスコンサルティング株式会社…</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>JUAN IGNACIO Sevilla</t>
+          <t>Nobunori Shiono</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>GERENTE DE PRODUCCIÓN</t>
+          <t>IT…</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>plasticaucho</t>
+          <t>株式会社ベイカレントコンサルティング</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Harshal Shah</t>
+          <t>Krista Shirley</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Elsner Technologies pvt ltd</t>
+          <t>Expand Energy Corporation</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Vinay Shah</t>
+          <t>Lisa Shober</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Value Advisor</t>
+          <t>Mana…</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Air Products and Chemicals, Inc</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Dawn Shakeshaft</t>
+          <t>Olga Shumikhina</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Umoja HCM Team Lead</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Associated Feed &amp; Supply Co.</t>
+          <t>The United Nations</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Aditya Shankar</t>
+          <t>Andrew Sigler</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Co-fou…</t>
+          <t>Account Director</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Sookti AI Innovations Private Limited</t>
+          <t>Syntax Systems USA LP</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Hari Shankar</t>
+          <t>Mikolaj Sikorski</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Associate Vice Presi…</t>
+          <t>Strategic Partner Initiatives</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>SAP Ireland Ltd.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Murali Shanmugam</t>
+          <t>Jonathan Silva</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Business AI Strategy A…</t>
+          <t>Instituição de Pagament…</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>SAP Australia Pty Ltd</t>
+          <t>Nu Pagamentos S.A</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Chris Shano</t>
+          <t>Renato Silva</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Marketing Head,…</t>
+          <t>Solutions Sa…</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ATOS INTERNATIONAL SAS</t>
+          <t>Globant Brasil Consultoria Ltda</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Ashuka Sharma</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
+          <t>Sergei Silva</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>SAP America Inc. (Hudson Yards)</t>
+          <t>Vistex</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Dhruv Sharma</t>
+          <t>Felix Silvagnoli</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Assistant Vice Preside…</t>
+          <t>SAP Platform Owner</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Celebal Technologies</t>
+          <t>BP International Limited</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Priya Sharma</t>
+          <t>Gianluca Simeone</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Glo…</t>
+          <t>Global SAP CTIO &amp; AI Leader</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>SNP TRANSFORMATIONS SEA PTE. LTD.</t>
+          <t>Capgemini</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Shantanu Sharma</t>
+          <t>Cintia Simonelli</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Architecture Advisor</t>
+          <t>Managing Part…</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>SAP America (Reston)</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Suchit Sharma</t>
+          <t>Eric Simonson</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Assistan…</t>
+          <t>Director - Product Marke…</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Celebal Technologies Americas Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Heidi Sheehan</t>
+          <t>Natalie Singh</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Vice President, Information Technol…</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr"/>
+          <t>Global Strategic Scale L…</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Anastasiya Shemanskaya</t>
+          <t>Sukhbir Singh</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>CFO Customer Office</t>
+          <t>S…</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>The School Board of Duval County Florida</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Sameer Shepal</t>
+          <t>Vikrant Sisodia</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Global Lead - SAP…</t>
+          <t>Sr. Product Manager</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Tata Technologies Limited</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Colby Sheridan</t>
+          <t>David Smith</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Industry Executive Advis…</t>
+          <t>VP, Chief Enterprise Ar…</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>SAP America (Reston)</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Scott Sherman</t>
+          <t>Rachel Smith</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>SVP Information Te…</t>
+          <t>Partner Sales Manager</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>The Pittsburgh Paints Co.</t>
+          <t>Docusign Inc</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Yasuhiro Shibata</t>
+          <t>Mark Smysor</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Department Manager</t>
+          <t>Business Systems Analyst in Enterpri…</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>JSOL Corporation</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Allon Shiff Shiff</t>
+          <t>Delaiah Snowden</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Value Advis…</t>
+          <t>IT Ana…</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>SAP Industries (Washington DC)</t>
+          <t>South Florida Water Management Dist</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Dong Moon Shin</t>
+          <t>Jairo Soares De Matos</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Analyst - SAP Busi…</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Pan Ocean Co., Ltd.</t>
+          <t>Canadian Blood Services</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Mary Shinn</t>
+          <t>Michael Somerville</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Managing Director, SAP K…</t>
+          <t>Sales Executive</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>SAP Korea Limited</t>
+          <t>Checkout.com</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Tomoya Shinozaki</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr"/>
+          <t>YoonWon Song</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>フォーティエンスコンサルティング株式会社…</t>
+          <t>i-SENS, Inc.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Nobunori Shiono</t>
+          <t>Dag Terje Sorlie</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>IT…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>株式会社ベイカレントコンサルティング</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Krista Shirley</t>
+          <t>Thiago Souza</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>IT CO…</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Expand Energy Corporation</t>
+          <t>MINERACAO SERRAS DO OESTE LTDA</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Lisa Shober</t>
+          <t>Meik Spanowsky</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Mana…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Air Products and Chemicals, Inc</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Olga Shumikhina</t>
+          <t>Thorsten Spihlmann</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Umoja HCM Team Lead</t>
+          <t>Head of Business Development for T…</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>The United Nations</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Andrew Sigler</t>
+          <t>TD Srinivasan</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Account Director</t>
+          <t>Industry…</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Syntax Systems USA LP</t>
+          <t>SAP Public Services, Inc. (Hudson Y</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Mikolaj Sikorski</t>
+          <t>Mike Stafford</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Strategic Partner Initiatives</t>
+          <t>Senior ABAP Developer</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SAP Ireland Ltd.</t>
+          <t>Titan Ventures LLC</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Jonathan Silva</t>
+          <t>Jennifer Stapleton</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Instituição de Pagament…</t>
+          <t>VP of Accounting Strategy &amp;…</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Nu Pagamentos S.A</t>
+          <t>American Equity</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Renato Silva</t>
+          <t>John Stark</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Solutions Sa…</t>
+          <t>Global Head of SAP Alliance</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Globant Brasil Consultoria Ltda</t>
+          <t>Loftware</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Sergei Silva</t>
+          <t>Denis Staudt</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Vistex</t>
+          <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Felix Silvagnoli</t>
+          <t>Maximilian Stein</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>SAP Platform Owner</t>
+          <t>SAP Product Owner - Treasury CPIT</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>BP International Limited</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Gianluca Simeone</t>
+          <t>Amanda Steiner</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Global SAP CTIO &amp; AI Leader</t>
+          <t>Business Process Architect</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>McKesson</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Cintia Simonelli</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Managing Part…</t>
-        </is>
-      </c>
+          <t>Dieter Steinmann</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="inlineStr">
         <is>
-          <t>SAP Argentina - Buenos Aires</t>
+          <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Eric Simonson</t>
+          <t>Jorrit Steinz</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Director - Product Marke…</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>ChannelEngine.com</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Natalie Singh</t>
+          <t>Robert Stemmler</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Global Strategic Scale L…</t>
+          <t>Global Alliances &amp; Ec…</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Sukhbir Singh</t>
+          <t>Yonathan Stephanos</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>S…</t>
+          <t>SAP Data &amp; AI Business Group Le…</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>The School Board of Duval County Florida</t>
+          <t>Accenture</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Vikrant Sisodia</t>
+          <t>Patrick Stewart</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Sr. Product Manager</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>David Smith</t>
+          <t>Jochen Stiebe</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>VP, Chief Enterprise Ar…</t>
+          <t>Head of Sales Treas…</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>SAP America (Reston)</t>
+          <t>Target-Networks GmbH</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Rachel Smith</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Partner Sales Manager</t>
-        </is>
-      </c>
+          <t>Leslie Stoffel</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Docusign Inc</t>
+          <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Mark Smysor</t>
+          <t>Miodrag Stojanov</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Business Systems Analyst in Enterpri…</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>SEMOS SOFTWARE LLC</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Delaiah Snowden</t>
+          <t>Bojana Stojanovich</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>IT Ana…</t>
+          <t>VP, NA Strategic Partnerships</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>South Florida Water Management Dist</t>
+          <t>Tricentis</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Jairo Soares De Matos</t>
+          <t>Seda Strate</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Analyst - SAP Busi…</t>
+          <t>Partner Innovation Lead</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Canadian Blood Services</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Michael Somerville</t>
+          <t>Divya Struebing</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Sales Executive</t>
+          <t>Supply Chain Customer…</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Checkout.com</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>YoonWon Song</t>
+          <t>Kevin Stupp</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Director S4 Platform</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>i-SENS, Inc.</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Dag Terje Sorlie</t>
+          <t>Harish Subramanian</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Principal Enterprise Arch…</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Thiago Souza</t>
+          <t>Marc Sudjian</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>IT CO…</t>
+          <t>Enterprise Architect, SAP So…</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>MINERACAO SERRAS DO OESTE LTDA</t>
+          <t>Bombardier Inc.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Meik Spanowsky</t>
+          <t>Hirofumi Sugimoto</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>ABeam Systems Ltd.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Thorsten Spihlmann</t>
+          <t>Michael Sukachev</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Head of Business Development for T…</t>
+          <t>Sr. EA</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Teranet Inc</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>TD Srinivasan</t>
+          <t>Som Suresh</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Industry…</t>
+          <t>Man…</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>SAP Public Services, Inc. (Hudson Y</t>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Mike Stafford</t>
+          <t>Jain Sushant</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Senior ABAP Developer</t>
+          <t>Chief Revenue Officer, F&amp;S…</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Titan Ventures LLC</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Jennifer Stapleton</t>
+          <t>Scott Sutker</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>VP of Accounting Strategy &amp;…</t>
+          <t>Vice President Customer Success…</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>American Equity</t>
+          <t>Alpharetta</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>John Stark</t>
+          <t>Mergenthaler Sven</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Global Head of SAP Alliance</t>
+          <t>Global Head of Strategic Central Ser…</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Loftware</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Denis Staudt</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr"/>
+          <t>Jereme Swoboda</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Segment Director</t>
+        </is>
+      </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>GLOBAL DISTRIBUIÇÃO DE BENS DE CONSU…</t>
+          <t>Avvale, Inc.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Maximilian Stein</t>
+          <t>Debra Syring</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>SAP Product Owner - Treasury CPIT</t>
+          <t>Senior IT Manager</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Entegris, Inc.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Amanda Steiner</t>
+          <t>Kai Szatkowski</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Business Process Architect</t>
+          <t>Head of Product Sales</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Natuvion GmbH</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Dieter Steinmann</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr"/>
+          <t>MARCO TOMBOLINI</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Global He…</t>
+        </is>
+      </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Fraport AG Frankfurt Airport Services Worldwi…</t>
+          <t>DOLCE &amp; GABBANA BEAUTY SRL</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Jorrit Steinz</t>
+          <t>KAZUSHI TOYOMASU</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>Global Direct…</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>ChannelEngine.com</t>
+          <t>MOL Chemical Tankers Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Robert Stemmler</t>
+          <t>Stacey Taborelli</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Global Alliances &amp; Ec…</t>
+          <t>Executive Business Partn…</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Yonathan Stephanos</t>
+          <t>Ahmed Taher</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>SAP Data &amp; AI Business Group Le…</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Al Daajan Trading</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Patrick Stewart</t>
+          <t>Chieko Takahata</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Chief</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>BROTHER INDUSTRIES,LTD.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Jochen Stiebe</t>
+          <t>Arai Takahiro</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Head of Sales Treas…</t>
+          <t>Services Delivery Manag…</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Target-Networks GmbH</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Leslie Stoffel</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr"/>
+          <t>Eiji Takashina</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Associate Director</t>
+        </is>
+      </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>CARMEUSE RESEARCH AND TECHNOLOGY S…</t>
+          <t>Kyndryl Japan KK</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Miodrag Stojanov</t>
+          <t>Tetsushi Takino</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Lead Engineer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>SEMOS SOFTWARE LLC</t>
+          <t>大和ハウス工業株式会社</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Bojana Stojanovich</t>
+          <t>Makoto Tamura</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>VP, NA Strategic Partnerships</t>
+          <t>Alliance Group Director</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Tricentis</t>
+          <t>FUJITSU LIMITED</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Seda Strate</t>
+          <t>Chiyuki Tanaka</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Partner Innovation Lead</t>
+          <t>Team leader</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Recruit Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Divya Struebing</t>
+          <t>Steve Tanaka</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Supply Chain Customer…</t>
+          <t>Sr Vice Presid…</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Blommer Chocolate Company</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Kevin Stupp</t>
+          <t>Yasuhiro Tanaka</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Director S4 Platform</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Recuruit Co.,Ltd.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Harish Subramanian</t>
+          <t>Kristin Taner</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Principal Enterprise Arch…</t>
+          <t>Chief Marke…</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Vortex Software Consulting, LLC</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Marc Sudjian</t>
+          <t>Mitchell Tauer</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Enterprise Architect, SAP So…</t>
+          <t>Services Account Execut…</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Bombardier Inc.</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Hirofumi Sugimoto</t>
+          <t>Roxanna Tavares</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Director, Gl…</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>ABeam Systems Ltd.</t>
+          <t>The Nielsen Company (US), LLC.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Michael Sukachev</t>
+          <t>Theo Tavrides</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Sr. EA</t>
+          <t>Vice Presi…</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Teranet Inc</t>
+          <t>NTT Data Business Solutions, Inc.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Som Suresh</t>
+          <t>Jamie Taylor</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Man…</t>
+          <t>Global VP, Strategic Partnerships</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Jain Sushant</t>
+          <t>Meghan Taylor</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer, F&amp;S…</t>
+          <t>Industry Account Ex…</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Scott Sutker</t>
+          <t>Samantha Taylor</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Vice President Customer Success…</t>
+          <t>Senior Solutions Account Exec…</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Alpharetta</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Mergenthaler Sven</t>
+          <t>Sarah Taylor</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Global Head of Strategic Central Ser…</t>
+          <t>Solution Advisor</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Jereme Swoboda</t>
+          <t>Jorge Tercero</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Segment Director</t>
+          <t>Manager/H…</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Avvale, Inc.</t>
+          <t>Asociacion Mutual Sancor Salud</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Debra Syring</t>
+          <t>Michael Teti</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Senior IT Manager</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Entegris, Inc.</t>
+          <t>Carlisle Construction Materials</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Kai Szatkowski</t>
+          <t>Suji Thampi</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Head of Product Sales</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Natuvion GmbH</t>
+          <t>MINDSPRINT PTE. LTD.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>MARCO TOMBOLINI</t>
+          <t>Le Thanh Phong</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Global He…</t>
+          <t>Managing Direc…</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>DOLCE &amp; GABBANA BEAUTY SRL</t>
+          <t>FPT Japan Holdings Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>KAZUSHI TOYOMASU</t>
+          <t>Michael Theis</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Global Direct…</t>
+          <t>Senior Director, Healthcare Life Scien…</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>MOL Chemical Tankers Pte Ltd</t>
+          <t>Icertis</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Stacey Taborelli</t>
+          <t>Rene Theriault</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Executive Business Partn…</t>
+          <t>IT Program Director</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>BRP INC</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Ahmed Taher</t>
+          <t>Barbara Thrasher</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>SR STAFF ARCHITECT</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Al Daajan Trading</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Chieko Takahata</t>
+          <t>Nissim Titan</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Chief</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>BROTHER INDUSTRIES,LTD.</t>
+          <t>4CAST SYSTEMS LTD</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Arai Takahiro</t>
+          <t>James Tiwari</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Services Delivery Manag…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>Intellioz LLC</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Eiji Takashina</t>
+          <t>Shuhei Toba</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Associate Director</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Kyndryl Japan KK</t>
+          <t>Business Engineering Corporation</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Tetsushi Takino</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
+          <t>John Tocci</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
       <c r="C369" t="inlineStr">
         <is>
-          <t>大和ハウス工業株式会社</t>
+          <t>Cbs Corporate Business Solutions America In…</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Makoto Tamura</t>
+          <t>Oliver Toloui</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Alliance Group Director</t>
+          <t>Director - AI…</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>FUJITSU LIMITED</t>
+          <t>Ibase Operations Corp Qualitest</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Chiyuki Tanaka</t>
+          <t>Ray Toma</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Team leader</t>
+          <t>Senior Principal — Global Strategic Initia…</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Recruit Co., Ltd.</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Steve Tanaka</t>
+          <t>Yuko Tominaga</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Sr Vice Presid…</t>
+          <t>Research Writer</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Blommer Chocolate Company</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Yasuhiro Tanaka</t>
+          <t>Laura Tozzo</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>AI Product Lead SAP IBP</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Recuruit Co.,Ltd.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Kristin Taner</t>
+          <t>Eero Traagel</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Chief Marke…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Vortex Software Consulting, LLC</t>
+          <t>IBM Canada Limited</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Mitchell Tauer</t>
+          <t>Adam Trahan</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Services Account Execut…</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -6752,2379 +6748,1992 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Roxanna Tavares</t>
+          <t>Evgeny Treskin</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Director, Gl…</t>
+          <t>SAP Alliances Director</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>The Nielsen Company (US), LLC.</t>
+          <t>Argano</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Theo Tavrides</t>
+          <t>Chetan Tripathi</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Vice Presi…</t>
+          <t>oCFO Adoption expert</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>NTT Data Business Solutions, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Jamie Taylor</t>
+          <t>Seshagiri Tripurana</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Global VP, Strategic Partnerships</t>
+          <t>Senior Director</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Meghan Taylor</t>
+          <t>Masaru Tsukahira</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Industry Account Ex…</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>TOKYO ELECTRON LIMITED.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Samantha Taylor</t>
+          <t>Lindsay Tucker</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Senior Solutions Account Exec…</t>
+          <t>Solution Consultant</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>Docusign</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Sarah Taylor</t>
+          <t>Paul Turbes</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Solution Advisor</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>KPMG LLP</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Jorge Tercero</t>
+          <t>Treaver Tyler</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Manager/H…</t>
+          <t>Tech…</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Asociacion Mutual Sancor Salud</t>
+          <t>Meijer Great Lakes Limited Partnership</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Michael Teti</t>
+          <t>Kotaro Ueda</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Carlisle Construction Materials</t>
+          <t>JSUG</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Suji Thampi</t>
+          <t>Rajkishore Una</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>President/CEO</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>MINDSPRINT PTE. LTD.</t>
+          <t>GyanSys, Inc.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Le Thanh Phong</t>
+          <t>Bala Parameswara Rao Upadhyay…</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Managing Direc…</t>
+          <t>Associate Director</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>FPT Japan Holdings Co., Ltd.</t>
+          <t>Stefanini, Inc.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Michael Theis</t>
+          <t>Oscar Uribe</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Senior Director, Healthcare Life Scien…</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Icertis</t>
+          <t>EDUARDONO S A S</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Rene Theriault</t>
+          <t>SACHIN VAIDYA</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>IT Program Director</t>
+          <t>Director - Enterprise Commercial…</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>BRP INC</t>
+          <t>Pfizer, Inc.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Barbara Thrasher</t>
+          <t>Jonathan VON RUEDEN</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>SR STAFF ARCHITECT</t>
+          <t>Chief AI Officer</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Tyson Foods, Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Nissim Titan</t>
+          <t>Wagner Valentin</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Director of Regulated Indust…</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>4CAST SYSTEMS LTD</t>
+          <t>SAP Brasil Ltda.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>James Tiwari</t>
+          <t>Jorge Valles Velásquez</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>KMMP…</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Intellioz LLC</t>
+          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Shuhei Toba</t>
+          <t>Henri Vallet</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>VP Sales, Americas B2B</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Business Engineering Corporation</t>
+          <t>Mirakl</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>John Tocci</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr"/>
+          <t>Jeff Van Pelt</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Founder / Managing Dire…</t>
+        </is>
+      </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Cbs Corporate Business Solutions America In…</t>
+          <t>Javelin Consulting</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Oliver Toloui</t>
+          <t>Meredith Van Wyk</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Director - AI…</t>
+          <t>Americas Field Partner…</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Ibase Operations Corp Qualitest</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Ray Toma</t>
+          <t>Joris Van der Donck</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Senior Principal — Global Strategic Initia…</t>
+          <t>Sr Manag…</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Commscope Connectivity Belgium</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Yuko Tominaga</t>
+          <t>Vijay Varee</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Research Writer</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Petsmart LLC</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Laura Tozzo</t>
+          <t>Suman Varma</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>AI Product Lead SAP IBP</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Eero Traagel</t>
+          <t>Chris Vassalotti</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>IBM Canada Limited</t>
+          <t>Opentext</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Adam Trahan</t>
+          <t>Raju Vedala</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>CES Business Technologies, LLC</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Evgeny Treskin</t>
+          <t>Asier Vega Sanchez</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>SAP Alliances Director</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Argano</t>
+          <t>Arkyn</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Chetan Tripathi</t>
+          <t>Jennifer Veillon</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>oCFO Adoption expert</t>
+          <t>Dir Project Controls</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Fluor Corporation</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Seshagiri Tripurana</t>
+          <t>Ajay Reddy Velampudi</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Senior Director</t>
+          <t>Senior VP - Sa…</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Miracle Software Systems Inc.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Masaru Tsukahira</t>
+          <t>William Velastegui</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>JEFE DE TI Y PR…</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>TOKYO ELECTRON LIMITED.</t>
+          <t>Plasticaucho Industrial S.A.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Lindsay Tucker</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Solution Consultant</t>
-        </is>
-      </c>
+          <t>Rajiv Vemula</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Docusign</t>
+          <t>Cognizant Technology Solutions U.S. Corporat…</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Paul Turbes</t>
+          <t>Sundu Venkataramani</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Industry Val…</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>KPMG LLP</t>
+          <t>SAP Industries (Washington DC)</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Treaver Tyler</t>
+          <t>Venkat Venkataramani</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Tech…</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Meijer Great Lakes Limited Partnership</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Kotaro Ueda</t>
+          <t>Tom Venner-Crysell</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>JSUG</t>
+          <t>ERPeople Solutions Ltd</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Rajkishore Una</t>
+          <t>Eduardo Vergara</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>President/CEO</t>
+          <t>Manager/Head of Dept</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>GyanSys, Inc.</t>
+          <t>Agrosuper S.A.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Bala Parameswara Rao Upadhyay…</t>
+          <t>Amit Verma</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Associate Director</t>
+          <t>RVP, Head of CFO Advisory…</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Stefanini, Inc.</t>
+          <t>SAP ASIA Pte Ltd</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Oscar Uribe</t>
+          <t>Kumar Vidit</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>Product Marketing M…</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>EDUARDONO S A S</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>SACHIN VAIDYA</t>
+          <t>Lakshmi Vidyashankar</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Director - Enterprise Commercial…</t>
+          <t>VP of IT</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Pfizer, Inc.</t>
+          <t>Marvin Engineering Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Jonathan VON RUEDEN</t>
+          <t>Jayant Vikram</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Chief AI Officer</t>
+          <t>Cloud Delivery Lead</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Accenture LLP</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Wagner Valentin</t>
+          <t>Yeni Villanueva</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Director of Regulated Indust…</t>
+          <t>Supervisora…</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>SAP Brasil Ltda.</t>
+          <t>Compañia Minera Antamina S.A.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Jorge Valles Velásquez</t>
+          <t>Robert Vinyard</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>KMMP…</t>
+          <t>VP and Senior Partner</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Komatsu-Mitsui Maquinarias Peru S.A.</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Henri Vallet</t>
+          <t>Thomas Vioux</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>VP Sales, Americas B2B</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Mirakl</t>
+          <t>PwC</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Jeff Van Pelt</t>
+          <t>Anil Visal</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Founder / Managing Dire…</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Javelin Consulting</t>
+          <t>PricewaterhouseCoopers LLP</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Meredith Van Wyk</t>
+          <t>Clara Viscido</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Americas Field Partner…</t>
+          <t>Consulting Services Director</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>GEONOSIS</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Joris Van der Donck</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Sr Manag…</t>
-        </is>
-      </c>
+          <t>Paulo Vita Vita</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Commscope Connectivity Belgium</t>
+          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Vijay Varee</t>
+          <t>Ranjan Vitt</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>AI Compliance Governance Program…</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Petsmart LLC</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Suman Varma</t>
+          <t>Jose Voisin</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Global CIO</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Carmeuse</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Chris Vassalotti</t>
+          <t>Christina Volk</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Head of Strate…</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Opentext</t>
+          <t>SAP Deutschland SE &amp;Co.KG</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Raju Vedala</t>
+          <t>Jessica Voyles</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Account Executive, South</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>CES Business Technologies, LLC</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Asier Vega Sanchez</t>
+          <t>Sandeep Vyas</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Solutio…</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Arkyn</t>
+          <t>Incture Technologies Private Limited</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Jennifer Veillon</t>
+          <t>Thomas von Alm</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Dir Project Controls</t>
+          <t>SVP Cross-Solution Services</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Fluor Corporation</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Ajay Reddy Velampudi</t>
+          <t>Markus von Quast</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Senior VP - Sa…</t>
+          <t>Global Head Industry Ecosystem</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Miracle Software Systems Inc.</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>William Velastegui</t>
+          <t>TATSUO WATANABE</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>JEFE DE TI Y PR…</t>
+          <t>Principal Cons…</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Plasticaucho Industrial S.A.</t>
+          <t>D I SQUARE CORPORATION.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Rajiv Vemula</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr"/>
+          <t>Masayuki Wada</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SVP, Head of Corporate Digit…</t>
+        </is>
+      </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions U.S. Corporat…</t>
+          <t>Fujitsu Limited</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Sundu Venkataramani</t>
+          <t>Stephen Wagenheim</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Industry Val…</t>
+          <t>Senior Sales Executive - Suppl…</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>SAP Industries (Washington DC)</t>
+          <t>Dallas (Allen)</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Venkat Venkataramani</t>
+          <t>Neha Wahi</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>VP</t>
+          <t>Global Alliance Lead</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>A.T. Kearney, Inc.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Tom Venner-Crysell</t>
+          <t>Waka Wakabayashi</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Associate Partner</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>ERPeople Solutions Ltd</t>
+          <t>KPMG Consulting Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Eduardo Vergara</t>
+          <t>Gustavo Waldfogiel</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Manager/Head of Dept</t>
+          <t>LAC HCM Head</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Agrosuper S.A.</t>
+          <t>SAP Argentina - Buenos Aires</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Amit Verma</t>
+          <t>Shashikant Walimbe</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>RVP, Head of CFO Advisory…</t>
+          <t>Vice President &amp; Global Head -…</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>SAP ASIA Pte Ltd</t>
+          <t>LTM LIMITED</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Kumar Vidit</t>
+          <t>Julie Walker</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Product Marketing M…</t>
+          <t>Sr. Director, Enterprise Applicatio…</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>Armstrong</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Lakshmi Vidyashankar</t>
+          <t>Rob Wallace</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>VP of IT</t>
+          <t>Senior Manager Digital &amp; In…</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Marvin Engineering Co., Inc.</t>
+          <t>Jaguarlandrover</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Jayant Vikram</t>
+          <t>Enzhou Wang</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Cloud Delivery Lead</t>
+          <t>Chief Technology Officer</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Accenture LLP</t>
+          <t>City of Tacoma</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Yeni Villanueva</t>
+          <t>May Wang</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Supervisora…</t>
+          <t>Direc…</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Compañia Minera Antamina S.A.</t>
+          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Robert Vinyard</t>
+          <t>Adam Warner</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>VP and Senior Partner</t>
+          <t>Cost Analyst</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Marathon Cheese Corporation</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Thomas Vioux</t>
+          <t>Kosuke Watanabe</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Anil Visal</t>
+          <t>Takashi Watanabe</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>執行役員</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>PricewaterhouseCoopers LLP</t>
+          <t>JFE Systems,Inc.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Clara Viscido</t>
+          <t>Robert Watson</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Consulting Services Director</t>
+          <t>Sr Account Executive</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>GEONOSIS</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Paulo Vita Vita</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr"/>
+          <t>Ashley Waxman</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Strategic Sales Executive</t>
+        </is>
+      </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Get Servicos de Gestao, Tecnologia e Particip…</t>
+          <t>Aevitas IT LLC</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Ranjan Vitt</t>
+          <t>Christy Weaver</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>AI Compliance Governance Program…</t>
+          <t>Global Demand Generation Man…</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Vertex, Inc.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Jose Voisin</t>
+          <t>Mike Weaver</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Global CIO</t>
+          <t>Senior I…</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>True Commerce Inc. TrueCommerce</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Christina Volk</t>
+          <t>Chris Webster</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Head of Strate…</t>
+          <t>SVP IT Strategy &amp; Architecture</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>SAP Deutschland SE &amp;Co.KG</t>
+          <t>Ahold Delhaize</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Jessica Voyles</t>
+          <t>Matt Webster</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Account Executive, South</t>
+          <t>Director of…</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Gardner White Furniture Co., Inc.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Sandeep Vyas</t>
+          <t>Patrick Weil</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Solutio…</t>
+          <t>IT Director</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Incture Technologies Private Limited</t>
+          <t>Metrie Canada Ltd</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Thomas von Alm</t>
+          <t>Sarah Weiler</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>SVP Cross-Solution Services</t>
+          <t>Manager, Busine…</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Ball Horticultural Company</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Markus von Quast</t>
+          <t>Adam Werner</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Global Head Industry Ecosystem</t>
+          <t>VP, Corporate Technology</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>Crocs, Inc.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>TATSUO WATANABE</t>
+          <t>Maddie Werner</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Principal Cons…</t>
+          <t>Director of Delivery Solutions</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>D I SQUARE CORPORATION.</t>
+          <t>Robra IT</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Masayuki Wada</t>
+          <t>Katherine West</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>SVP, Head of Corporate Digit…</t>
+          <t>CX Account Executive</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Fujitsu Limited</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Stephen Wagenheim</t>
+          <t>Anja Wettling</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Senior Sales Executive - Suppl…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Dallas (Allen)</t>
+          <t>anuwo GmbH</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Neha Wahi</t>
+          <t>Charleen Wetzstein</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Global Alliance Lead</t>
+          <t>SAP Principal Architect</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>A.T. Kearney, Inc.</t>
+          <t>PROSPECTOR, LLC</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Waka Wakabayashi</t>
+          <t>Peter Wheatley</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Associate Partner</t>
+          <t>Enterprise Architect…</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>KPMG Consulting Co., Ltd.</t>
+          <t>SAP America (Houston)</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Gustavo Waldfogiel</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>LAC HCM Head</t>
-        </is>
-      </c>
+          <t>Robb White</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr">
         <is>
-          <t>SAP Argentina - Buenos Aires</t>
+          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Shashikant Walimbe</t>
+          <t>Peter Widmer</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Vice President &amp; Global Head -…</t>
+          <t>Chief of Staff to the Global Head of S…</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>LTM LIMITED</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Julie Walker</t>
+          <t>Chad Wiech</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Sr. Director, Enterprise Applicatio…</t>
+          <t>Director of Solution…</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Armstrong</t>
+          <t>Pittsburgh, SAP America</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Rob Wallace</t>
+          <t>Chamnida Wijetilleke</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Senior Manager Digital &amp; In…</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Jaguarlandrover</t>
+          <t>The Ducats Group LLC</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Enzhou Wang</t>
+          <t>Pete Wilkins</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Chief Technology Officer</t>
+          <t>NA Partner Manager</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>City of Tacoma</t>
+          <t>SAP America(Bellevue)</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>May Wang</t>
+          <t>Mark Willey</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Direc…</t>
+          <t>Vice…</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Adam Warner</t>
+          <t>Ed Williamson</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Cost Analyst</t>
+          <t>Client Services Lead</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Marathon Cheese Corporation</t>
+          <t>XMATERIA LTD</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Kosuke Watanabe</t>
+          <t>Monica Willis</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>HR Strategy and Value A…</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>SAP Japan Co., Ltd.</t>
+          <t>Plano- Legacy West</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Takashi Watanabe</t>
+          <t>Charlotte Wilson</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>執行役員</t>
+          <t>Senior Manager Strategic Cha…</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>JFE Systems,Inc.</t>
+          <t>Direct Energy</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Robert Watson</t>
+          <t>Emily Wisemiller</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Sr Account Executive</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>SAP AMERICA, INC.</t>
+          <t>Molex</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Ashley Waxman</t>
+          <t>Julia Wolfe</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Strategic Sales Executive</t>
+          <t>Analyst Relations Manager</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Aevitas IT LLC</t>
+          <t>IBM</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Christy Weaver</t>
+          <t>Jennifer Workman</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Global Demand Generation Man…</t>
+          <t>Techn…</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Vertex, Inc.</t>
+          <t>Universal Destinations &amp; Experiences</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Mike Weaver</t>
+          <t>Steven Wright Wright</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Senior I…</t>
+          <t>VP Sales</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>True Commerce Inc. TrueCommerce</t>
+          <t>Acuiti Labs Limited</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Chris Webster</t>
+          <t>Monty Wurth</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>SVP IT Strategy &amp; Architecture</t>
+          <t>VP of Operations</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Ahold Delhaize</t>
+          <t>Optima Consulting L.L.C.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Matt Webster</t>
+          <t>Brad Wylie</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Director of…</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Gardner White Furniture Co., Inc.</t>
+          <t>SAP Canada</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Patrick Weil</t>
+          <t>KAORI YASHIKI</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>IT Director</t>
+          <t>Business Resear…</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Metrie Canada Ltd</t>
+          <t>Hitachi Digital Services LLC</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Sarah Weiler</t>
+          <t>YOUNGHO YOO</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Manager, Busine…</t>
+          <t>Team Leader</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Ball Horticultural Company</t>
+          <t>LG CNS Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Adam Werner</t>
+          <t>Mohamed YUSUF</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>VP, Corporate Technology</t>
+          <t>Head of Integrated Toolchain</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Crocs, Inc.</t>
+          <t>SAP MENA LLC</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Maddie Werner</t>
+          <t>Hikaru Yafuso</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Director of Delivery Solutions</t>
+          <t>Senior Alliance Director</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Robra IT</t>
+          <t>Databricks</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Katherine West</t>
+          <t>Sonoko Yamamoto</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>CX Account Executive</t>
+          <t>Partner Business Manager</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>SAP Japan Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Anja Wettling</t>
+          <t>Osamu Yamazaki</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Co…</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>anuwo GmbH</t>
+          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Charleen Wetzstein</t>
+          <t>Kenji Yanagi</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>SAP Principal Architect</t>
+          <t>Group Leader</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>PROSPECTOR, LLC</t>
+          <t>ASAHI GROUP JAPAN, LTD.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Peter Wheatley</t>
+          <t>EJ Yang</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Enterprise Architect…</t>
+          <t>IT Deputy Director</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>SAP America (Houston)</t>
+          <t>MediaTek Inc.</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Robb White</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr"/>
+          <t>Kiran Yarlagadda Yarlagadda</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Managing…</t>
+        </is>
+      </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+          <t>Adroix Corp DBA CodeForce 360</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Peter Widmer</t>
+          <t>Takayuki Yasuda</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Chief of Staff to the Global Head of S…</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>JFE Systems, Inc.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Chad Wiech</t>
+          <t>Tomoki Yasuda</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Director of Solution…</t>
+          <t>AssistantMana…</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Pittsburgh, SAP America</t>
+          <t>NTT DATA Japan Corporation</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Chamnida Wijetilleke</t>
+          <t>Kazuhiro Yonekawa</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Chief/Proj…</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>The Ducats Group LLC</t>
+          <t>CANON MARKETING JAPAN INC.,</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Pete Wilkins</t>
+          <t>Sungeui Yoon</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>NA Partner Manager</t>
+          <t>Senior Specialist</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>SAP America(Bellevue)</t>
+          <t>Microsoft</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Mark Willey</t>
+          <t>Christopher Yope</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Vice…</t>
+          <t>SAP Supply C…</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+          <t>DXC Technology Services LLC</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Ed Williamson</t>
+          <t>Kohei Yoshimatsu</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Client Services Lead</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>XMATERIA LTD</t>
+          <t>アズビル株式会社</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Monica Willis</t>
+          <t>taichi yoshida</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>HR Strategy and Value A…</t>
+          <t>Senior Ma…</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Plano- Legacy West</t>
+          <t>BENIC SOLUTION CORPORATION</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Charlotte Wilson</t>
+          <t>nakajima yuki</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Senior Manager Strategic Cha…</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Direct Energy</t>
+          <t>Nitori Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Emily Wisemiller</t>
+          <t>Stefan Zach</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>VP Global IT</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Wieland Group</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Julia Wolfe</t>
+          <t>Beau Zaremski</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Analyst Relations Manager</t>
+          <t>VP of Sales</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SAP AMERICA, INC.</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Jennifer Workman</t>
+          <t>Yuan Zhang</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Techn…</t>
+          <t>Senior Project Manager, SAP AI RIG</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Universal Destinations &amp; Experiences</t>
+          <t>SAP SE</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Steven Wright Wright</t>
+          <t>Cathy Zhou</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>VP Sales</t>
+          <t>IT Director, EBS</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Acuiti Labs Limited</t>
+          <t>Ecolab Inc.</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Monty Wurth</t>
+          <t>Gustavo Zintak</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>VP of Operations</t>
+          <t>Manager/Head of Dept</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Optima Consulting L.L.C.</t>
+          <t>SWISS MEDICAL S.A.</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Brad Wylie</t>
+          <t>Alina Zuberi</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Global Content Strategist</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>SAP Canada</t>
+          <t>SAP MENA LLC</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>KAORI YASHIKI</t>
+          <t>Yoshiaki Agata 縣</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Business Resear…</t>
+          <t>consultant</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services LLC</t>
+          <t>AJS株式会社</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>YOUNGHO YOO</t>
+          <t>裕紀 阿保</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Team Leader</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>LG CNS Co., Ltd.</t>
+          <t>FORTIENCE CONSULTING INC.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Mohamed YUSUF</t>
+          <t>謙介 青木</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Head of Integrated Toolchain</t>
+          <t>Manager, Uvance Market Developme…</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
-        <is>
-          <t>SAP MENA LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>Hikaru Yafuso</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>Senior Alliance Director</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>Sonoko Yamamoto</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>Partner Business Manager</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>SAP Japan Co., Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>Osamu Yamazaki</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>Co…</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>Hitachi Industry &amp; Control Solutions, Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>Kenji Yanagi</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>Group Leader</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>ASAHI GROUP JAPAN, LTD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>EJ Yang</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>IT Deputy Director</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>MediaTek Inc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>Kiran Yarlagadda Yarlagadda</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>Managing…</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>Adroix Corp DBA CodeForce 360</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>Takayuki Yasuda</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>JFE Systems, Inc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>Tomoki Yasuda</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>AssistantMana…</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>NTT DATA Japan Corporation</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>Kazuhiro Yonekawa</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>Chief/Proj…</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>CANON MARKETING JAPAN INC.,</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>Sungeui Yoon</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>Senior Specialist</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>Christopher Yope</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>SAP Supply C…</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>DXC Technology Services LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>Kohei Yoshimatsu</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>アズビル株式会社</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>taichi yoshida</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>Senior Ma…</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>BENIC SOLUTION CORPORATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>nakajima yuki</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>Member</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>Nitori Co., Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>Stefan Zach</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>VP Global IT</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>Wieland Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>Beau Zaremski</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>VP of Sales</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>SAP AMERICA, INC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>Yuan Zhang</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>Senior Project Manager, SAP AI RIG</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>SAP SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>Cathy Zhou</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>IT Director, EBS</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>Ecolab Inc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>Gustavo Zintak</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>Manager/Head of Dept</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>SWISS MEDICAL S.A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>Alina Zuberi</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>Global Content Strategist</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>SAP MENA LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>Yoshiaki Agata 縣</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>consultant</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>AJS株式会社</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>裕紀 阿保</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>FORTIENCE CONSULTING INC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>謙介 青木</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>Manager, Uvance Market Developme…</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
         <is>
           <t>Fujitsu</t>
         </is>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C493"/>
+  <dimension ref="A1:C547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8739,6 +8739,908 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Sriram Hariharasubramanian</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Partner, Tech Consult…</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>EY Global Services Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Lori Harner</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Global Vice President, Pr…</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Melissa Harris</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>IT Program Manager</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Masco Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Paul Harris</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Senior Director, SAP Basi…</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Varsity Brands, LLC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Joe Hartnett</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>OpenText</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Richard Hatton</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>VP Platform Engin…</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>NBCUniversal Media, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Kishie Hattori</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Chief Partner Officer</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>SAP Japan Co., Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Chelsea Hebb</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Director, Cons…</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Collective Insights Consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Heiko Hecht</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>IBIS America Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Tess Heiligers</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Business Advisor to SVP ERP Tranfo…</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>BP P.L.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Christian Heinrich</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Chief Solutions Officer &amp; Membe…</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>sovanta AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>VALERIAN HARRIS</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Vice President</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>HCL America Solutions Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Angie Halderman</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Vice President, Sales</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Sarah Haley-Fuentes</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Director of Solution Engineering</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Vistex Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Callie Hall</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr"/>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>SAP Global Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Deborah Hamilton</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Head of Global Marketing</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Bristlecone, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Joe Hamilton</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Sr. Director AME Mfg. Technology</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Sean Hamlin</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Value Advisor</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Youngshin Han</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>IT Team Manager</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>i-SENS. Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Rebecca Hanna</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Head of Services, ANZ</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>SAP AUSTRALIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Manoj Harbhajanka</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Acuiti Labs Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Hadi Hares</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Global Lead Product Manager</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Ajay Gupta</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Mana…</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Reliance Comfort Limited Partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Anupam Gupta Gupta</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Celebal Technologies Americas, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Niladri Gupta</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Deloitte Consulting LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Piyush Gupta</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Global Head -…</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Celebal Technologies Pvt Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Raj Gupta</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Intellioz LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Varun Gupta</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>American Water Works Service Company, Inc.…</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Vishal Gupta</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Head of Finance &amp; Spe…</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>SAP Australia Pty Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>David Gust</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Nestor Guzman</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Dire…</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Aerovias Del Continente Americano S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Kalman Gyula</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Karthik Gobi gobimayilsamygound…</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Service Owner (…</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Nicole Griffith</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Sr. Director, SAP Alliance</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Protera</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Tim Grochowski</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Senior Cloud Executive</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Anette Grossmueller</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Head of Cross Product Management,…</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Scott Groth</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Directir, ERP Architect</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Pfizer, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>John Grzybek</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Senior SAP Projec…</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Fujitsu North America, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Rodolfo Guerrero</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>GBM Dominicana</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Alex Guglielmetti</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>VP - IT Advisor</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Pantexan Deterrence</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Patricia Guillermo</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>It Lead</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Kellanova/Mars</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Dmitri Guinzbourg</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Team Lead/Supervisor</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Air Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Timothy Guizon</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Finance Manager</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Henry Company LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Moises Gonzalez</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Client Engagement Manag…</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Veritas Prime, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Oziel Gonzalez</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>VA Head Mexico</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>SAP Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Nelson González</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Subgerente e Operaciones…</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Grupo Kaufmann</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Senthil Gopalan</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>D-1 (SVP</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>The United Nations</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Pooven Govender</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>APAC CLOUD ARCHITE…</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>SAP Australia Pty Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Christine Graham</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Lakeview Farms, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Geoff Gray</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Head of Product</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>The Config Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Andrew Greaves</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Sen…</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>SAPOCOM Technologies Private Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Samuel Grenade</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Coveo Solutions Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Betsy Griffin</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Senior Account Executive</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Paula Griffin</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Seni…</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Medical College of Virginia Foundation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C547"/>
+  <dimension ref="A1:C597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9641,6 +9641,856 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Gordon Folz</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Bristlecone, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Sandra Liliana Forero Cifuentes</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>SAP Product Manag…</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Softtek Renovation SAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Nina Forlenza</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Team Lead, Senior HRBP</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>ADP, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Chris Foti</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Director, ISV Alliances</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Basware Oyj</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Jeff Foy</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Vice President, Supply C…</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Luciana Franquet</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Galicia Seguros S.A.U.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Andreas Franz</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>He…</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Heraeus Consulting &amp; IT Solutions GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Tom Frederick</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Senior Director</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>GlobalSource IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Alan Freedman</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>VP Sales - Central…</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>The Addmore Group Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Jeremy Freeman</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Director, Technology</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Aritzia</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Brian Freymann</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Director, SAP Strategic Acco…</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Bristlecone, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Patrick Friday</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Alokai</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Lionel Fridman</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>VP SCM MCLAC</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>SAP Argentina - Buenos Aires</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Joakim Frisberg</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Oliver Froehlich</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>SAP Partner Manager Europe</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Vertex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Takeshi Fukushima</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>大和ハウス工業株式会社</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Sean Furukawa</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Deputy CEO</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>BearingPoint NA LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Anindya Gaine</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Program Director SAP Imp…</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Fluor Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Suresh Gali</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>IT Solutions Architect</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>NRG Energy, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Francisco Galindo</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Sr Director IT finance</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>George Galindo</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Account Director</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>SAP Industries, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Glenn Gammon</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Director of S…</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>TLP Management Services LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Joanne Gammon</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Ariba US Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Suman Gandhe</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>FICO Consultant</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Gary Gang</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Client Engagement Manag…</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Veritas Prime, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Javier Garcia</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Commercial Dir…</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Smartshift Technologies, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Jose Garcia</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Sr. Director, SAP Practice Lead</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Nsight, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Amit Garussi</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>VP Product</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Panaya Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Patti Gary</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Senior Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Tyson Foods, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Satyanarayana Gade</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Enterprise Archi…</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Simpson Strong-Tie Co., Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>NISHANT GAUTAM</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>www.innovise-it.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Dino Gattola</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Senior Account Executive, Sup…</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>SAP CANADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Boris Gebhardt</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Manager…</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>STARTEAM Global Germany GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Frank Genevieve</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>SAP Sales Executive</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>NTT DATA Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Brent George</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>SAP Advisor</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Tricentis GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Jacob George</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Raytheon</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Mark George</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Program Direct…</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Delaware North America LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Eliza Georgescu</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Senior Manager, Partner…</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Collibra Belgium BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Kimberly Gershenzon</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Finance Account Executi…</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Deana Gervais</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Strategic Sales Support Specialist</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Pferd Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Stefanie Geßler</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>SAP EWM Expert</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>4flow SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Keya Gholap</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>KATBOTZ LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Benedikt Gieger</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Strategic Projects, SAP SCM</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Richard Gilbert</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Head of B2B Partner…</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Worldpay (UK) Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Stacey Gilbert</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Merck</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Don Gillespie</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Senior Director Strategic Alliances</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>ADP, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Joe Golemba</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Global Head, Strategic Alliances…</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Vistex, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Raul Gomez</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>VP of IT</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Hexagon AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Santiago Julian Gomez</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Supply Chain Regional Man…</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>INTERPACK S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>SANJAY KUMAR GUPTA</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>VICE PRESIDENT</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Limited</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1077"/>
+  <dimension ref="A1:C1102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -18579,6 +18579,431 @@
         </is>
       </c>
     </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Jennifer Ertler</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Jose Esparza</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Director…</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>BFS Ingenieria Aplicada S.A. de C.V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>Jose Manuel Estevz Estevez</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Technology Consulta…</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>EY Global Services Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Brandon Evans</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Managing Dire…</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>PricewaterhouseCoopers LLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>SHIGEHIRO FUJIKI</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Chief Info…</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Mitsubishi Corporation (Americas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>SATOSHI FUJITA</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>EY Global Services Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>Luciano Fanti Bianco</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Kimberly Farino</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>MIT Lincoln Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>John Farr</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Value Advis…</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>SAP Industries (Washington DC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Jonathan Farrell</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Enterprise Account Executive</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Panaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Tim Faubert</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Executive Director,…</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>BeiGene (Beijing) Co., Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Angelo Fazio</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Global Sales</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>IBM Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Beth Feaster</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Sr Business Develop…</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>INSPYR Solutions, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Craig Fee</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Sr. Business A…</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Purdue University Global, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Richard Ferling</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Sourcing ma…</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>The Pittsburgh Paints Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>Alejandro Ferreira</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Bintech, S.A. de C.V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>Jeff Fillegar</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Sr Director Solution Engineering</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Tricentis</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>Rich Filler</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Sr. Mgr IT</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Exelon Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>Colin Finley</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Kearney &amp; Company, P.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>JP Finnell</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Senior Director Strategic…</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Jack Fiorini</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Senior Business Development…</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Onapsis Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Kurt Fischbach</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Director of Data Governa…</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>ScottsMiracle-Gro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Cedric Fiske</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Sales Development Representative</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Coveo</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>Kieran Fitzgerald</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Software Sales Lead</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>The Config Team Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Susana Flores Cabrera</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Contracts Coordinator</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Cheney Bros, Inc.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1102"/>
+  <dimension ref="A1:C1156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -19004,6 +19004,920 @@
         </is>
       </c>
     </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Bonnie Davies</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>VP Finance &amp; Spend</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Wendy Davis</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Solution Customer S…</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>SAP America (Houston)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Rebecca Day</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>IS ERP and Revenu…</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>The Health and Hospital</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Andrea De Colle</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Enterprise Arc…</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>SAP Argentina - Buenos Aires</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Jeff DeHulsters</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Business Consultant</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Travis County, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>Adrian DeSantis</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Sales Engineer</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>TrueCommerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>Sushil Debare</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>ECS Regional Delivery H…</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>Larry Deille</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Senior Manager Digital Transf…</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Lam Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>Drew Delaney</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Business P…</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>The Scotts Miracle-Gro Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>Amy Delise</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Walgreens</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Meghan Demo</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Director of Marketing</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Cognitus Consulting LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>James Dender</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Account Director</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>Sven Denecken</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>SVP SAP Industries</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>Urnav Desai</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Prin…</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Deloitte Touche Tohmatsu Services, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>Alan Detlif</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Director Business Sys…</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>The Crosby Group LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>Holly Devine</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Industry Advisor</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>Andrea Devroy Devroy</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Senior Dire…</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>PT Intermediate Holdings III,  LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>Raman Dhooria</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Vice President</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Celebal Technologies Pvt Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>Aboubacar Diallo</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>AI Governance Program Co-Lead</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>SAP SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>Sofia Diaz</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>SR. Manager Inside Sales</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Globant</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>Kathrin Dorothea Diederich</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr"/>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>KPMG AG Wirtschaftsprüfungsgesellschaft -…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>Linda Dietzel</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Director, IT Supply C…</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>The Hershey Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>Guillermina Digregorio</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Global Head of GCO Private Clo…</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>SAP Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Ralf Dillmann</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Partner &amp; C…</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>BearingPoint North America LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>Michael Dillon</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Global Platform Leader</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>IBM Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>Haricharan Dingari</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Enterprise Arc…</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Bob's Discount Furniture, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Everett Dittman</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Strategic Customer Advisor, A…</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Databricks Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>Pankaj Diwan</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Senior Director</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>ArchLynk, LLC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>Ralph Dommes</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Dommes Consulting, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>Mari Doroud</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>HRIS Manager</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Nucor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>Amisha Doshi</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Industry Account Executi…</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>Rakesh Doshi</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Architecture Advisor</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>Chris Dougherty</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Senior Director</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Pfizer, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Ryan Doyle</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Principal Co…</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>SAP Industries (Washington DC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Adam Drent</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>GlobalSource IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>Shannon Drost</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Vice President Technology Soluti…</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>Erasmo Duarte</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>IT Manager</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Ford Motor Company Brasil Ltda</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>Nicolas Duchesneau</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Analyst TI</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Portefeuille Soucy Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Leah Dudley</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Senior Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Onapsis Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Barbara Duffey</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>VP, North America C…</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Lakeland Industries Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Damodhar Dyava</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>SAP SD Manag…</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Bob's Discount Furniture, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Willard Dyck</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Sr. Enterprise…</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>IGM Financial/Financière IGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>Jan de Leeuw</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Executive Director Central Fina…</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Ingram Micro</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Erin Earl</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Executive  Industry Advi…</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>SAP AMERICA, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Norihiro Egawa</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>ABeam Aystems</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>Kenji Eguchi</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Basis Consulta…</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>NTT DATA Japan Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>Onyi Egunjobi</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Value Advisor Senior</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>SAP Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Marci Ehrhart</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Global Practice Leader</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>ADP, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>Pauleen Elasio</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Field Finance, Asia Paci…</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>SAP Philippines, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>Mark Elkin</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>SVP, Global Head of Solution…</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>SAP CANADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>Stephen Elkins</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Manager Enterprise Business…</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Basin Electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Barry Emptage</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Director, SAP E…</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>RHOMBI HOLDINGS LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>Martha Enriquez Carrola</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Customer Engagement and Ado…</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>SAP Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>Lander Errasti</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>BFS Ingenieria Aplicada S.A. de C.V.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1156"/>
+  <dimension ref="A1:C1166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -19918,6 +19918,176 @@
         </is>
       </c>
     </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>Matt Curtin</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>OneRail, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>Thomas Czichowsky</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Business Consulting Retail | S…</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Schwarz IT KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>Beth clarkin</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Director…</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>True Commerce Inc. TrueCommerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>Nick DAVIS</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Global Process Owner Order…</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Elanco US Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>Abdelhalim Dadouche</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>SAP Product Specialist</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Databricks Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Chung DaeYoung</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Head of Enterprise 2</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>SAP Korea Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>Gerardo Dall'Orso</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>ADECO AGROPECUARIA S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Madhu Raju Dandu</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Director, Dig…</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>RELEASEOWL PRIVATE LIMITED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Nicolas Daniels</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Global Account Director</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Mediafly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Sushovan Datta</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Vice President</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Tech Mahindra (americas) Inc.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCDD2"/>
+        <bgColor rgb="00FFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,11 +74,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,17 +507,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Katrina Acebedo</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Data Architect</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>The Hershey Company</t>
         </is>
@@ -605,17 +626,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Saritha Aguru</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Service Delivery &amp; Product M…</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Ernst &amp; Young</t>
         </is>
@@ -690,17 +711,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Ebenezer Aladeojebi</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Product Manager</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>J.P Morgan Chase &amp; Co.</t>
         </is>
@@ -826,17 +847,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Salazar del Rio Alma Aurora</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Functional leader</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Bachoco, S.A. de C.V.</t>
         </is>
@@ -894,17 +915,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>David Amiot</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
@@ -1383,17 +1404,17 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Jin Seon Baek</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>ERP Manager</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>H Mart Companies, Inc.</t>
         </is>
@@ -1434,17 +1455,17 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Staci Baker</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers LLP</t>
         </is>
@@ -1536,17 +1557,17 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Paul Baraniuk</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Global Solution…</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Florida Crystals Corporation</t>
         </is>
@@ -1757,17 +1778,17 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Marissa Bennett</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Director, Global People Solutio…</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>PepsiCo, Inc</t>
         </is>
@@ -1872,17 +1893,17 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Kerry Jo Berger</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Executive Director</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Chase Bank, NA</t>
         </is>
@@ -2127,17 +2148,17 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Beverley Den Boestert</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>Director - Technology…</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>EY Global Services Ltd</t>
         </is>
@@ -2195,17 +2216,17 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Patrick Boruta</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>Partner - Business Consultin…</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>Grant Thornton</t>
         </is>
@@ -2365,13 +2386,13 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Adam Breiterman</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Maryland &amp; Virginia Milk Producers Cooperati…</t>
         </is>
@@ -2829,17 +2850,17 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>Lisa Cabarcos</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>America's SAP Allianc…</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>Ernst &amp; Young U.S. LLP</t>
         </is>
@@ -2965,34 +2986,34 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Pat Carmody</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Senior Manag…</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>Sharp Electronics Corporation</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>Tyler Carr</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>Sr. Capabilities Manag…</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
@@ -3254,17 +3275,17 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Greg Chamberland</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>IT, Enterprise…</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>Ocean Spray Cranberries, Inc.</t>
         </is>
@@ -3288,17 +3309,17 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Prasanna Chand</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Director - Enterprise Tech</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>Wayfair</t>
         </is>
@@ -3322,17 +3343,17 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Matt Charleston</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Sr Manager Fi…</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>Performance Food Group, Inc.</t>
         </is>
@@ -3407,34 +3428,34 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>Abraham Cherian</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Director Security Govern…</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>Kontoor Brands Inc</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Venu Cherupillil</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>Systems Engineer Sr Princi…</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>The Home Depot</t>
         </is>
@@ -3556,34 +3577,34 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>Parinda Choksi</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>CIO - Enablement</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>Ball Horticultural Co.</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>Sanjay Choubey</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Global Chief Digital an…</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>Sylvamo Corporation</t>
         </is>
@@ -3807,17 +3828,17 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>Colin Cole</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>IT Director</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>JBS USA Food Company Holdings</t>
         </is>
@@ -3875,17 +3896,17 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="3" t="inlineStr">
         <is>
           <t>Oisin Collins</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="3" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
@@ -4045,17 +4066,17 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>Juan Correa</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
         <is>
           <t>Employee</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="C215" s="2" t="inlineStr">
         <is>
           <t>Sharp Corporation</t>
         </is>
@@ -4096,17 +4117,17 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="3" t="inlineStr">
         <is>
           <t>Maryanne Coughlin</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C218" s="3" t="inlineStr">
         <is>
           <t>PwC</t>
         </is>
@@ -4343,17 +4364,17 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="3" t="inlineStr">
         <is>
           <t>Yuki Sato</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="3" t="inlineStr">
         <is>
           <t>Business Consulting…</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C233" s="3" t="inlineStr">
         <is>
           <t>EY Global Services Ltd</t>
         </is>
@@ -4479,17 +4500,17 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="3" t="inlineStr">
         <is>
           <t>Kathrin Schmalzing</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" s="3" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C241" s="3" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers LLP</t>
         </is>
@@ -4836,17 +4857,17 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="2" t="inlineStr">
         <is>
           <t>Dawn Shakeshaft</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="2" t="inlineStr">
         <is>
           <t>Controller</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C262" s="2" t="inlineStr">
         <is>
           <t>Associated Feed &amp; Supply Co.</t>
         </is>
@@ -5589,17 +5610,17 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
+      <c r="A307" s="3" t="inlineStr">
         <is>
           <t>Meik Spanowsky</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B307" s="3" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
+      <c r="C307" s="3" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers LLP</t>
         </is>
@@ -5768,17 +5789,17 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
+      <c r="A318" s="4" t="inlineStr">
         <is>
           <t>Robert Stemmler</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B318" s="4" t="inlineStr">
         <is>
           <t>Global Alliances &amp; Ec…</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
+      <c r="C318" s="4" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
@@ -5917,17 +5938,17 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
+      <c r="A327" s="2" t="inlineStr">
         <is>
           <t>Kevin Stupp</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B327" s="2" t="inlineStr">
         <is>
           <t>Director S4 Platform</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
+      <c r="C327" s="2" t="inlineStr">
         <is>
           <t>The Hershey Company</t>
         </is>
@@ -6002,17 +6023,17 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
+      <c r="A332" s="3" t="inlineStr">
         <is>
           <t>Som Suresh</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B332" s="3" t="inlineStr">
         <is>
           <t>Man…</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
+      <c r="C332" s="3" t="inlineStr">
         <is>
           <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
@@ -6291,17 +6312,17 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
+      <c r="A349" s="2" t="inlineStr">
         <is>
           <t>Steve Tanaka</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B349" s="2" t="inlineStr">
         <is>
           <t>Sr Vice Presid…</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
+      <c r="C349" s="2" t="inlineStr">
         <is>
           <t>Blommer Chocolate Company</t>
         </is>
@@ -6563,17 +6584,17 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
+      <c r="A365" s="2" t="inlineStr">
         <is>
           <t>Barbara Thrasher</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B365" s="2" t="inlineStr">
         <is>
           <t>SR STAFF ARCHITECT</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
+      <c r="C365" s="2" t="inlineStr">
         <is>
           <t>Tyson Foods, Inc.</t>
         </is>
@@ -6831,17 +6852,17 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
+      <c r="A381" s="3" t="inlineStr">
         <is>
           <t>Paul Turbes</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
+      <c r="B381" s="3" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
+      <c r="C381" s="3" t="inlineStr">
         <is>
           <t>KPMG LLP</t>
         </is>
@@ -7069,17 +7090,17 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
+      <c r="A395" s="2" t="inlineStr">
         <is>
           <t>Vijay Varee</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
+      <c r="B395" s="2" t="inlineStr">
         <is>
           <t>Senior Manager</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr">
+      <c r="C395" s="2" t="inlineStr">
         <is>
           <t>Petsmart LLC</t>
         </is>
@@ -7388,34 +7409,34 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
+      <c r="A414" s="3" t="inlineStr">
         <is>
           <t>Thomas Vioux</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B414" s="3" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C414" s="3" t="inlineStr">
         <is>
           <t>PwC</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
+      <c r="A415" s="3" t="inlineStr">
         <is>
           <t>Anil Visal</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
+      <c r="B415" s="3" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr">
+      <c r="C415" s="3" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers LLP</t>
         </is>
@@ -7639,17 +7660,17 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr">
+      <c r="A429" s="3" t="inlineStr">
         <is>
           <t>Waka Wakabayashi</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
+      <c r="B429" s="3" t="inlineStr">
         <is>
           <t>Associate Partner</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr">
+      <c r="C429" s="3" t="inlineStr">
         <is>
           <t>KPMG Consulting Co., Ltd.</t>
         </is>
@@ -7741,34 +7762,34 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr">
+      <c r="A435" s="3" t="inlineStr">
         <is>
           <t>May Wang</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr">
+      <c r="B435" s="3" t="inlineStr">
         <is>
           <t>Direc…</t>
         </is>
       </c>
-      <c r="C435" t="inlineStr">
+      <c r="C435" s="3" t="inlineStr">
         <is>
           <t>Deloitte Consulting (Shanghai) Co., Ltd.</t>
         </is>
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr">
+      <c r="A436" s="2" t="inlineStr">
         <is>
           <t>Adam Warner</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
+      <c r="B436" s="2" t="inlineStr">
         <is>
           <t>Cost Analyst</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr">
+      <c r="C436" s="2" t="inlineStr">
         <is>
           <t>Marathon Cheese Corporation</t>
         </is>
@@ -7877,34 +7898,34 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr">
+      <c r="A443" s="2" t="inlineStr">
         <is>
           <t>Chris Webster</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr">
+      <c r="B443" s="2" t="inlineStr">
         <is>
           <t>SVP IT Strategy &amp; Architecture</t>
         </is>
       </c>
-      <c r="C443" t="inlineStr">
+      <c r="C443" s="2" t="inlineStr">
         <is>
           <t>Ahold Delhaize</t>
         </is>
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr">
+      <c r="A444" s="2" t="inlineStr">
         <is>
           <t>Matt Webster</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
+      <c r="B444" s="2" t="inlineStr">
         <is>
           <t>Director of…</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr">
+      <c r="C444" s="2" t="inlineStr">
         <is>
           <t>Gardner White Furniture Co., Inc.</t>
         </is>
@@ -7928,34 +7949,34 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
+      <c r="A446" s="2" t="inlineStr">
         <is>
           <t>Sarah Weiler</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
+      <c r="B446" s="2" t="inlineStr">
         <is>
           <t>Manager, Busine…</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr">
+      <c r="C446" s="2" t="inlineStr">
         <is>
           <t>Ball Horticultural Company</t>
         </is>
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
+      <c r="A447" s="2" t="inlineStr">
         <is>
           <t>Adam Werner</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
+      <c r="B447" s="2" t="inlineStr">
         <is>
           <t>VP, Corporate Technology</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr">
+      <c r="C447" s="2" t="inlineStr">
         <is>
           <t>Crocs, Inc.</t>
         </is>
@@ -8047,13 +8068,13 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
+      <c r="A453" s="2" t="inlineStr">
         <is>
           <t>Robb White</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr"/>
-      <c r="C453" t="inlineStr">
+      <c r="B453" s="2" t="inlineStr"/>
+      <c r="C453" s="2" t="inlineStr">
         <is>
           <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
         </is>
@@ -8128,17 +8149,17 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
+      <c r="A458" s="3" t="inlineStr">
         <is>
           <t>Mark Willey</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr">
+      <c r="B458" s="3" t="inlineStr">
         <is>
           <t>Vice…</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr">
+      <c r="C458" s="3" t="inlineStr">
         <is>
           <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
@@ -8859,17 +8880,17 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
+      <c r="A501" s="3" t="inlineStr">
         <is>
           <t>Araja Reddy</t>
         </is>
       </c>
-      <c r="B501" t="inlineStr">
+      <c r="B501" s="3" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
+      <c r="C501" s="3" t="inlineStr">
         <is>
           <t>Deloitte Consulting</t>
         </is>
@@ -8893,13 +8914,13 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
+      <c r="A503" s="3" t="inlineStr">
         <is>
           <t>Nico Reichen</t>
         </is>
       </c>
-      <c r="B503" t="inlineStr"/>
-      <c r="C503" t="inlineStr">
+      <c r="B503" s="3" t="inlineStr"/>
+      <c r="C503" s="3" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers GmbH Wirtschaftsp...</t>
         </is>
@@ -9234,17 +9255,17 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
+      <c r="A524" s="3" t="inlineStr">
         <is>
           <t>Diana Romaya</t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B524" s="3" t="inlineStr">
         <is>
           <t>SAP...</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
+      <c r="C524" s="3" t="inlineStr">
         <is>
           <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
@@ -9370,13 +9391,13 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr">
+      <c r="A532" s="3" t="inlineStr">
         <is>
           <t>Frank Ruland</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr"/>
-      <c r="C532" t="inlineStr">
+      <c r="B532" s="3" t="inlineStr"/>
+      <c r="C532" s="3" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers GmbH Wirtschaftsp...</t>
         </is>
@@ -9434,17 +9455,17 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr">
+      <c r="A536" s="4" t="inlineStr">
         <is>
           <t>Natalie Röthel</t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
+      <c r="B536" s="4" t="inlineStr">
         <is>
           <t>Executive Assistant</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr">
+      <c r="C536" s="4" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
@@ -9774,17 +9795,17 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" t="inlineStr">
+      <c r="A556" s="2" t="inlineStr">
         <is>
           <t>Rogério Peres</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B556" s="2" t="inlineStr">
         <is>
           <t>CIO</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C556" s="2" t="inlineStr">
         <is>
           <t>JBS USA</t>
         </is>
@@ -9876,17 +9897,17 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr">
+      <c r="A562" s="3" t="inlineStr">
         <is>
           <t>Catherine Perry-Robertson</t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B562" s="3" t="inlineStr">
         <is>
           <t>Partner, Natio...</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C562" s="3" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers LLP</t>
         </is>
@@ -10093,17 +10114,17 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr">
+      <c r="A575" s="3" t="inlineStr">
         <is>
           <t>Franck Poisson</t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B575" s="3" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr">
+      <c r="C575" s="3" t="inlineStr">
         <is>
           <t>PWC US Group LLP</t>
         </is>
@@ -10892,17 +10913,17 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" t="inlineStr">
+      <c r="A622" s="2" t="inlineStr">
         <is>
           <t>Pavel Nouel</t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B622" s="2" t="inlineStr">
         <is>
           <t>Vice President,...</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C622" s="2" t="inlineStr">
         <is>
           <t>Colgate-Palmolive Company</t>
         </is>
@@ -11636,17 +11657,17 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr">
+      <c r="A666" s="2" t="inlineStr">
         <is>
           <t>Mark Meanwell</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B666" s="2" t="inlineStr">
         <is>
           <t>Senior Manager Data &amp; Analytics</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C666" s="2" t="inlineStr">
         <is>
           <t>Sylvamo</t>
         </is>
@@ -11921,17 +11942,17 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr">
+      <c r="A683" s="3" t="inlineStr">
         <is>
           <t>Piyush Mistry</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B683" s="3" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C683" t="inlineStr">
+      <c r="C683" s="3" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
@@ -12576,17 +12597,17 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" t="inlineStr">
+      <c r="A722" s="2" t="inlineStr">
         <is>
           <t>Tammy Louie</t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B722" s="2" t="inlineStr">
         <is>
           <t>Senior Financial Systems Analyst</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C722" s="2" t="inlineStr">
         <is>
           <t>AutoZone</t>
         </is>
@@ -12729,17 +12750,17 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" t="inlineStr">
+      <c r="A731" s="4" t="inlineStr">
         <is>
           <t>Nicolas Löwe</t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B731" s="4" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
+      <c r="C731" s="4" t="inlineStr">
         <is>
           <t>BearingPoint GmbH</t>
         </is>
@@ -12916,17 +12937,17 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" t="inlineStr">
+      <c r="A742" s="3" t="inlineStr">
         <is>
           <t>Naresh Makhijani Makhijani</t>
         </is>
       </c>
-      <c r="B742" t="inlineStr">
+      <c r="B742" s="3" t="inlineStr">
         <is>
           <t>Glo...</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr">
+      <c r="C742" s="3" t="inlineStr">
         <is>
           <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
@@ -12950,17 +12971,17 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" t="inlineStr">
+      <c r="A744" s="3" t="inlineStr">
         <is>
           <t>Melissa Marchetti</t>
         </is>
       </c>
-      <c r="B744" t="inlineStr">
+      <c r="B744" s="3" t="inlineStr">
         <is>
           <t>SAP...</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C744" s="3" t="inlineStr">
         <is>
           <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
@@ -13409,17 +13430,17 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" t="inlineStr">
+      <c r="A771" s="3" t="inlineStr">
         <is>
           <t>Denise McGuigan</t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
+      <c r="B771" s="3" t="inlineStr">
         <is>
           <t>Part...</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr">
+      <c r="C771" s="3" t="inlineStr">
         <is>
           <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
@@ -13473,17 +13494,17 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" t="inlineStr">
+      <c r="A775" s="2" t="inlineStr">
         <is>
           <t>Siddhi Kshatriya</t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
+      <c r="B775" s="2" t="inlineStr">
         <is>
           <t>Organizational Change Managem...</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr">
+      <c r="C775" s="2" t="inlineStr">
         <is>
           <t>AutoZone</t>
         </is>
@@ -13605,17 +13626,17 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" t="inlineStr">
+      <c r="A783" s="3" t="inlineStr">
         <is>
           <t>Dennis Kurlandski</t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
+      <c r="B783" s="3" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="C783" t="inlineStr">
+      <c r="C783" s="3" t="inlineStr">
         <is>
           <t>KPMG</t>
         </is>
@@ -14880,17 +14901,17 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" t="inlineStr">
+      <c r="A858" s="3" t="inlineStr">
         <is>
           <t>Ron King</t>
         </is>
       </c>
-      <c r="B858" t="inlineStr">
+      <c r="B858" s="3" t="inlineStr">
         <is>
           <t>VP, Sales Executive</t>
         </is>
       </c>
-      <c r="C858" t="inlineStr">
+      <c r="C858" s="3" t="inlineStr">
         <is>
           <t>Deloitte Consulting LLP</t>
         </is>
@@ -14914,17 +14935,17 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" t="inlineStr">
+      <c r="A860" s="3" t="inlineStr">
         <is>
           <t>Hiroshi Kitano</t>
         </is>
       </c>
-      <c r="B860" t="inlineStr">
+      <c r="B860" s="3" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C860" t="inlineStr">
+      <c r="C860" s="3" t="inlineStr">
         <is>
           <t>EY Strategy and Consulting Co., Ltd.</t>
         </is>
@@ -15063,17 +15084,17 @@
       </c>
     </row>
     <row r="869">
-      <c r="A869" t="inlineStr">
+      <c r="A869" s="4" t="inlineStr">
         <is>
           <t>Christian Koestler</t>
         </is>
       </c>
-      <c r="B869" t="inlineStr">
+      <c r="B869" s="4" t="inlineStr">
         <is>
           <t>Global Director, Client...</t>
         </is>
       </c>
-      <c r="C869" t="inlineStr">
+      <c r="C869" s="4" t="inlineStr">
         <is>
           <t>McKinsey &amp; Company</t>
         </is>
@@ -15646,17 +15667,17 @@
       </c>
     </row>
     <row r="904">
-      <c r="A904" t="inlineStr">
+      <c r="A904" s="3" t="inlineStr">
         <is>
           <t>Armin Kaltenmeier</t>
         </is>
       </c>
-      <c r="B904" t="inlineStr">
+      <c r="B904" s="3" t="inlineStr">
         <is>
           <t>Partner, Global Chief...</t>
         </is>
       </c>
-      <c r="C904" t="inlineStr">
+      <c r="C904" s="3" t="inlineStr">
         <is>
           <t>Ernst &amp; Young U.S. LLP</t>
         </is>
@@ -15748,17 +15769,17 @@
       </c>
     </row>
     <row r="910">
-      <c r="A910" t="inlineStr">
+      <c r="A910" s="2" t="inlineStr">
         <is>
           <t>Francisco Galindo</t>
         </is>
       </c>
-      <c r="B910" t="inlineStr">
+      <c r="B910" s="2" t="inlineStr">
         <is>
           <t>Sr Director IT finance</t>
         </is>
       </c>
-      <c r="C910" t="inlineStr">
+      <c r="C910" s="2" t="inlineStr">
         <is>
           <t>Colgate Palmolive</t>
         </is>
@@ -15901,17 +15922,17 @@
       </c>
     </row>
     <row r="919">
-      <c r="A919" t="inlineStr">
+      <c r="A919" s="2" t="inlineStr">
         <is>
           <t>Patti Gary</t>
         </is>
       </c>
-      <c r="B919" t="inlineStr">
+      <c r="B919" s="2" t="inlineStr">
         <is>
           <t>Senior Enterprise Architect</t>
         </is>
       </c>
-      <c r="C919" t="inlineStr">
+      <c r="C919" s="2" t="inlineStr">
         <is>
           <t>Tyson Foods, Inc.</t>
         </is>
@@ -16309,17 +16330,17 @@
       </c>
     </row>
     <row r="943">
-      <c r="A943" t="inlineStr">
+      <c r="A943" s="2" t="inlineStr">
         <is>
           <t>Christine Graham</t>
         </is>
       </c>
-      <c r="B943" t="inlineStr">
+      <c r="B943" s="2" t="inlineStr">
         <is>
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="C943" t="inlineStr">
+      <c r="C943" s="2" t="inlineStr">
         <is>
           <t>Lakeview Farms, LLC</t>
         </is>
@@ -16526,17 +16547,17 @@
       </c>
     </row>
     <row r="956">
-      <c r="A956" t="inlineStr">
+      <c r="A956" s="2" t="inlineStr">
         <is>
           <t>Patricia Guillermo</t>
         </is>
       </c>
-      <c r="B956" t="inlineStr">
+      <c r="B956" s="2" t="inlineStr">
         <is>
           <t>It Lead</t>
         </is>
       </c>
-      <c r="C956" t="inlineStr">
+      <c r="C956" s="2" t="inlineStr">
         <is>
           <t>Kellanova/Mars</t>
         </is>
@@ -16577,17 +16598,17 @@
       </c>
     </row>
     <row r="959">
-      <c r="A959" t="inlineStr">
+      <c r="A959" s="3" t="inlineStr">
         <is>
           <t>Sriram Hariharasubramanian</t>
         </is>
       </c>
-      <c r="B959" t="inlineStr">
+      <c r="B959" s="3" t="inlineStr">
         <is>
           <t>Partner, Tech Consult...</t>
         </is>
       </c>
-      <c r="C959" t="inlineStr">
+      <c r="C959" s="3" t="inlineStr">
         <is>
           <t>EY Global Services Ltd</t>
         </is>
@@ -16628,17 +16649,17 @@
       </c>
     </row>
     <row r="962">
-      <c r="A962" t="inlineStr">
+      <c r="A962" s="2" t="inlineStr">
         <is>
           <t>Paul Harris</t>
         </is>
       </c>
-      <c r="B962" t="inlineStr">
+      <c r="B962" s="2" t="inlineStr">
         <is>
           <t>Senior Director, SAP Basi...</t>
         </is>
       </c>
-      <c r="C962" t="inlineStr">
+      <c r="C962" s="2" t="inlineStr">
         <is>
           <t>Varsity Brands, LLC.</t>
         </is>
@@ -16832,17 +16853,17 @@
       </c>
     </row>
     <row r="974">
-      <c r="A974" t="inlineStr">
+      <c r="A974" s="2" t="inlineStr">
         <is>
           <t>Adriana Hernandez</t>
         </is>
       </c>
-      <c r="B974" t="inlineStr">
+      <c r="B974" s="2" t="inlineStr">
         <is>
           <t>Head Architecture</t>
         </is>
       </c>
-      <c r="C974" t="inlineStr">
+      <c r="C974" s="2" t="inlineStr">
         <is>
           <t>Bachoco, S.A. de C.V.</t>
         </is>
@@ -17049,17 +17070,17 @@
       </c>
     </row>
     <row r="987">
-      <c r="A987" t="inlineStr">
+      <c r="A987" s="4" t="inlineStr">
         <is>
           <t>Michael Hom</t>
         </is>
       </c>
-      <c r="B987" t="inlineStr">
+      <c r="B987" s="4" t="inlineStr">
         <is>
           <t>Global Head of Digit...</t>
         </is>
       </c>
-      <c r="C987" t="inlineStr">
+      <c r="C987" s="4" t="inlineStr">
         <is>
           <t>Jpmorgan Chase &amp; Co.</t>
         </is>
@@ -17334,17 +17355,17 @@
       </c>
     </row>
     <row r="1004">
-      <c r="A1004" t="inlineStr">
+      <c r="A1004" s="2" t="inlineStr">
         <is>
           <t>Omar Hussein Olmedo</t>
         </is>
       </c>
-      <c r="B1004" t="inlineStr">
+      <c r="B1004" s="2" t="inlineStr">
         <is>
           <t>Poject Manager</t>
         </is>
       </c>
-      <c r="C1004" t="inlineStr">
+      <c r="C1004" s="2" t="inlineStr">
         <is>
           <t>Bachoco, S.A. de C.V.</t>
         </is>
@@ -17691,17 +17712,17 @@
       </c>
     </row>
     <row r="1025">
-      <c r="A1025" t="inlineStr">
+      <c r="A1025" s="3" t="inlineStr">
         <is>
           <t>Naren Jain</t>
         </is>
       </c>
-      <c r="B1025" t="inlineStr">
+      <c r="B1025" s="3" t="inlineStr">
         <is>
           <t>Managing Dire...</t>
         </is>
       </c>
-      <c r="C1025" t="inlineStr">
+      <c r="C1025" s="3" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers LLP</t>
         </is>
@@ -17895,17 +17916,17 @@
       </c>
     </row>
     <row r="1037">
-      <c r="A1037" t="inlineStr">
+      <c r="A1037" s="3" t="inlineStr">
         <is>
           <t>Angie Halderman</t>
         </is>
       </c>
-      <c r="B1037" t="inlineStr">
+      <c r="B1037" s="3" t="inlineStr">
         <is>
           <t>Vice President, Sales</t>
         </is>
       </c>
-      <c r="C1037" t="inlineStr">
+      <c r="C1037" s="3" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
@@ -18095,17 +18116,17 @@
       </c>
     </row>
     <row r="1049">
-      <c r="A1049" t="inlineStr">
+      <c r="A1049" s="3" t="inlineStr">
         <is>
           <t>Niladri Gupta</t>
         </is>
       </c>
-      <c r="B1049" t="inlineStr">
+      <c r="B1049" s="3" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="C1049" t="inlineStr">
+      <c r="C1049" s="3" t="inlineStr">
         <is>
           <t>Deloitte Consulting LLP</t>
         </is>
@@ -18210,13 +18231,13 @@
       </c>
     </row>
     <row r="1056">
-      <c r="A1056" t="inlineStr">
+      <c r="A1056" s="2" t="inlineStr">
         <is>
           <t>Kalman Gyula</t>
         </is>
       </c>
-      <c r="B1056" t="inlineStr"/>
-      <c r="C1056" t="inlineStr">
+      <c r="B1056" s="2" t="inlineStr"/>
+      <c r="C1056" s="2" t="inlineStr">
         <is>
           <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
         </is>
@@ -18393,17 +18414,17 @@
       </c>
     </row>
     <row r="1067">
-      <c r="A1067" t="inlineStr">
+      <c r="A1067" s="2" t="inlineStr">
         <is>
           <t>Jeremy Freeman</t>
         </is>
       </c>
-      <c r="B1067" t="inlineStr">
+      <c r="B1067" s="2" t="inlineStr">
         <is>
           <t>Director, Technology</t>
         </is>
       </c>
-      <c r="C1067" t="inlineStr">
+      <c r="C1067" s="2" t="inlineStr">
         <is>
           <t>Aritzia</t>
         </is>
@@ -18512,17 +18533,17 @@
       </c>
     </row>
     <row r="1074">
-      <c r="A1074" t="inlineStr">
+      <c r="A1074" s="4" t="inlineStr">
         <is>
           <t>Sean Furukawa</t>
         </is>
       </c>
-      <c r="B1074" t="inlineStr">
+      <c r="B1074" s="4" t="inlineStr">
         <is>
           <t>Deputy CEO</t>
         </is>
       </c>
-      <c r="C1074" t="inlineStr">
+      <c r="C1074" s="4" t="inlineStr">
         <is>
           <t>BearingPoint NA LLC</t>
         </is>
@@ -18580,17 +18601,17 @@
       </c>
     </row>
     <row r="1078">
-      <c r="A1078" t="inlineStr">
+      <c r="A1078" s="3" t="inlineStr">
         <is>
           <t>Jennifer Ertler</t>
         </is>
       </c>
-      <c r="B1078" t="inlineStr">
+      <c r="B1078" s="3" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="C1078" t="inlineStr">
+      <c r="C1078" s="3" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
@@ -18614,34 +18635,34 @@
       </c>
     </row>
     <row r="1080">
-      <c r="A1080" t="inlineStr">
+      <c r="A1080" s="3" t="inlineStr">
         <is>
           <t>Jose Manuel Estevz Estevez</t>
         </is>
       </c>
-      <c r="B1080" t="inlineStr">
+      <c r="B1080" s="3" t="inlineStr">
         <is>
           <t>Technology Consulta…</t>
         </is>
       </c>
-      <c r="C1080" t="inlineStr">
+      <c r="C1080" s="3" t="inlineStr">
         <is>
           <t>EY Global Services Ltd</t>
         </is>
       </c>
     </row>
     <row r="1081">
-      <c r="A1081" t="inlineStr">
+      <c r="A1081" s="3" t="inlineStr">
         <is>
           <t>Brandon Evans</t>
         </is>
       </c>
-      <c r="B1081" t="inlineStr">
+      <c r="B1081" s="3" t="inlineStr">
         <is>
           <t>Managing Dire…</t>
         </is>
       </c>
-      <c r="C1081" t="inlineStr">
+      <c r="C1081" s="3" t="inlineStr">
         <is>
           <t>PricewaterhouseCoopers LLP</t>
         </is>
@@ -18665,17 +18686,17 @@
       </c>
     </row>
     <row r="1083">
-      <c r="A1083" t="inlineStr">
+      <c r="A1083" s="3" t="inlineStr">
         <is>
           <t>SATOSHI FUJITA</t>
         </is>
       </c>
-      <c r="B1083" t="inlineStr">
+      <c r="B1083" s="3" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="C1083" t="inlineStr">
+      <c r="C1083" s="3" t="inlineStr">
         <is>
           <t>EY Global Services Ltd</t>
         </is>
@@ -18988,17 +19009,17 @@
       </c>
     </row>
     <row r="1102">
-      <c r="A1102" t="inlineStr">
+      <c r="A1102" s="2" t="inlineStr">
         <is>
           <t>Susana Flores Cabrera</t>
         </is>
       </c>
-      <c r="B1102" t="inlineStr">
+      <c r="B1102" s="2" t="inlineStr">
         <is>
           <t>Contracts Coordinator</t>
         </is>
       </c>
-      <c r="C1102" t="inlineStr">
+      <c r="C1102" s="2" t="inlineStr">
         <is>
           <t>Cheney Bros, Inc.</t>
         </is>
@@ -19158,17 +19179,17 @@
       </c>
     </row>
     <row r="1112">
-      <c r="A1112" t="inlineStr">
+      <c r="A1112" s="2" t="inlineStr">
         <is>
           <t>Amy Delise</t>
         </is>
       </c>
-      <c r="B1112" t="inlineStr">
+      <c r="B1112" s="2" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="C1112" t="inlineStr">
+      <c r="C1112" s="2" t="inlineStr">
         <is>
           <t>Walgreens</t>
         </is>
@@ -19226,17 +19247,17 @@
       </c>
     </row>
     <row r="1116">
-      <c r="A1116" t="inlineStr">
+      <c r="A1116" s="3" t="inlineStr">
         <is>
           <t>Urnav Desai</t>
         </is>
       </c>
-      <c r="B1116" t="inlineStr">
+      <c r="B1116" s="3" t="inlineStr">
         <is>
           <t>Prin…</t>
         </is>
       </c>
-      <c r="C1116" t="inlineStr">
+      <c r="C1116" s="3" t="inlineStr">
         <is>
           <t>Deloitte Touche Tohmatsu Services, LLC</t>
         </is>
@@ -19345,30 +19366,30 @@
       </c>
     </row>
     <row r="1123">
-      <c r="A1123" t="inlineStr">
+      <c r="A1123" s="3" t="inlineStr">
         <is>
           <t>Kathrin Dorothea Diederich</t>
         </is>
       </c>
-      <c r="B1123" t="inlineStr"/>
-      <c r="C1123" t="inlineStr">
+      <c r="B1123" s="3" t="inlineStr"/>
+      <c r="C1123" s="3" t="inlineStr">
         <is>
           <t>KPMG AG Wirtschaftsprüfungsgesellschaft -…</t>
         </is>
       </c>
     </row>
     <row r="1124">
-      <c r="A1124" t="inlineStr">
+      <c r="A1124" s="2" t="inlineStr">
         <is>
           <t>Linda Dietzel</t>
         </is>
       </c>
-      <c r="B1124" t="inlineStr">
+      <c r="B1124" s="2" t="inlineStr">
         <is>
           <t>Director, IT Supply C…</t>
         </is>
       </c>
-      <c r="C1124" t="inlineStr">
+      <c r="C1124" s="2" t="inlineStr">
         <is>
           <t>The Hershey Company</t>
         </is>
@@ -19392,17 +19413,17 @@
       </c>
     </row>
     <row r="1126">
-      <c r="A1126" t="inlineStr">
+      <c r="A1126" s="4" t="inlineStr">
         <is>
           <t>Ralf Dillmann</t>
         </is>
       </c>
-      <c r="B1126" t="inlineStr">
+      <c r="B1126" s="4" t="inlineStr">
         <is>
           <t>Partner &amp; C…</t>
         </is>
       </c>
-      <c r="C1126" t="inlineStr">
+      <c r="C1126" s="4" t="inlineStr">
         <is>
           <t>BearingPoint North America LLC</t>
         </is>
@@ -19426,17 +19447,17 @@
       </c>
     </row>
     <row r="1128">
-      <c r="A1128" t="inlineStr">
+      <c r="A1128" s="2" t="inlineStr">
         <is>
           <t>Haricharan Dingari</t>
         </is>
       </c>
-      <c r="B1128" t="inlineStr">
+      <c r="B1128" s="2" t="inlineStr">
         <is>
           <t>Enterprise Arc…</t>
         </is>
       </c>
-      <c r="C1128" t="inlineStr">
+      <c r="C1128" s="2" t="inlineStr">
         <is>
           <t>Bob's Discount Furniture, LLC</t>
         </is>
@@ -19681,17 +19702,17 @@
       </c>
     </row>
     <row r="1143">
-      <c r="A1143" t="inlineStr">
+      <c r="A1143" s="2" t="inlineStr">
         <is>
           <t>Damodhar Dyava</t>
         </is>
       </c>
-      <c r="B1143" t="inlineStr">
+      <c r="B1143" s="2" t="inlineStr">
         <is>
           <t>SAP SD Manag…</t>
         </is>
       </c>
-      <c r="C1143" t="inlineStr">
+      <c r="C1143" s="2" t="inlineStr">
         <is>
           <t>Bob's Discount Furniture, LLC</t>
         </is>

--- a/attendees.xlsx
+++ b/attendees.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -45,8 +45,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-        <bgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,6 +59,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00BBDEFB"/>
         <bgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -82,6 +88,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -847,17 +854,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Salazar del Rio Alma Aurora</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Functional leader</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Bachoco, S.A. de C.V.</t>
         </is>
@@ -1404,17 +1411,17 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Jin Seon Baek</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>ERP Manager</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>H Mart Companies, Inc.</t>
         </is>
@@ -1557,17 +1564,17 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Paul Baraniuk</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Global Solution…</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Florida Crystals Corporation</t>
         </is>
@@ -2386,13 +2393,13 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>Adam Breiterman</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr"/>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="B115" s="5" t="inlineStr"/>
+      <c r="C115" s="5" t="inlineStr">
         <is>
           <t>Maryland &amp; Virginia Milk Producers Cooperati…</t>
         </is>
@@ -3275,17 +3282,17 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" s="5" t="inlineStr">
         <is>
           <t>Greg Chamberland</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B168" s="5" t="inlineStr">
         <is>
           <t>IT, Enterprise…</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C168" s="5" t="inlineStr">
         <is>
           <t>Ocean Spray Cranberries, Inc.</t>
         </is>
@@ -3428,17 +3435,17 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>Abraham Cherian</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B177" s="5" t="inlineStr">
         <is>
           <t>Director Security Govern…</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C177" s="5" t="inlineStr">
         <is>
           <t>Kontoor Brands Inc</t>
         </is>
@@ -3577,34 +3584,34 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
         <is>
           <t>Parinda Choksi</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>CIO - Enablement</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
         <is>
           <t>Ball Horticultural Co.</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+      <c r="A187" s="5" t="inlineStr">
         <is>
           <t>Sanjay Choubey</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>Global Chief Digital an…</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
         <is>
           <t>Sylvamo Corporation</t>
         </is>
@@ -4857,17 +4864,17 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="inlineStr">
+      <c r="A262" s="5" t="inlineStr">
         <is>
           <t>Dawn Shakeshaft</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
+      <c r="B262" s="5" t="inlineStr">
         <is>
           <t>Controller</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="C262" s="5" t="inlineStr">
         <is>
           <t>Associated Feed &amp; Supply Co.</t>
         </is>
@@ -6312,17 +6319,17 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="inlineStr">
+      <c r="A349" s="5" t="inlineStr">
         <is>
           <t>Steve Tanaka</t>
         </is>
       </c>
-      <c r="B349" s="2" t="inlineStr">
+      <c r="B349" s="5" t="inlineStr">
         <is>
           <t>Sr Vice Presid…</t>
         </is>
       </c>
-      <c r="C349" s="2" t="inlineStr">
+      <c r="C349" s="5" t="inlineStr">
         <is>
           <t>Blommer Chocolate Company</t>
         </is>
@@ -7779,17 +7786,17 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="inlineStr">
+      <c r="A436" s="5" t="inlineStr">
         <is>
           <t>Adam Warner</t>
         </is>
       </c>
-      <c r="B436" s="2" t="inlineStr">
+      <c r="B436" s="5" t="inlineStr">
         <is>
           <t>Cost Analyst</t>
         </is>
       </c>
-      <c r="C436" s="2" t="inlineStr">
+      <c r="C436" s="5" t="inlineStr">
         <is>
           <t>Marathon Cheese Corporation</t>
         </is>
@@ -7915,17 +7922,17 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="inlineStr">
+      <c r="A444" s="5" t="inlineStr">
         <is>
           <t>Matt Webster</t>
         </is>
       </c>
-      <c r="B444" s="2" t="inlineStr">
+      <c r="B444" s="5" t="inlineStr">
         <is>
           <t>Director of…</t>
         </is>
       </c>
-      <c r="C444" s="2" t="inlineStr">
+      <c r="C444" s="5" t="inlineStr">
         <is>
           <t>Gardner White Furniture Co., Inc.</t>
         </is>
@@ -7949,34 +7956,34 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="inlineStr">
+      <c r="A446" s="5" t="inlineStr">
         <is>
           <t>Sarah Weiler</t>
         </is>
       </c>
-      <c r="B446" s="2" t="inlineStr">
+      <c r="B446" s="5" t="inlineStr">
         <is>
           <t>Manager, Busine…</t>
         </is>
       </c>
-      <c r="C446" s="2" t="inlineStr">
+      <c r="C446" s="5" t="inlineStr">
         <is>
           <t>Ball Horticultural Company</t>
         </is>
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="inlineStr">
+      <c r="A447" s="5" t="inlineStr">
         <is>
           <t>Adam Werner</t>
         </is>
       </c>
-      <c r="B447" s="2" t="inlineStr">
+      <c r="B447" s="5" t="inlineStr">
         <is>
           <t>VP, Corporate Technology</t>
         </is>
       </c>
-      <c r="C447" s="2" t="inlineStr">
+      <c r="C447" s="5" t="inlineStr">
         <is>
           <t>Crocs, Inc.</t>
         </is>
@@ -8068,13 +8075,13 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="inlineStr">
+      <c r="A453" s="5" t="inlineStr">
         <is>
           <t>Robb White</t>
         </is>
       </c>
-      <c r="B453" s="2" t="inlineStr"/>
-      <c r="C453" s="2" t="inlineStr">
+      <c r="B453" s="5" t="inlineStr"/>
+      <c r="C453" s="5" t="inlineStr">
         <is>
           <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
         </is>
@@ -11657,17 +11664,17 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" s="2" t="inlineStr">
+      <c r="A666" s="5" t="inlineStr">
         <is>
           <t>Mark Meanwell</t>
         </is>
       </c>
-      <c r="B666" s="2" t="inlineStr">
+      <c r="B666" s="5" t="inlineStr">
         <is>
           <t>Senior Manager Data &amp; Analytics</t>
         </is>
       </c>
-      <c r="C666" s="2" t="inlineStr">
+      <c r="C666" s="5" t="inlineStr">
         <is>
           <t>Sylvamo</t>
         </is>
@@ -16330,17 +16337,17 @@
       </c>
     </row>
     <row r="943">
-      <c r="A943" s="2" t="inlineStr">
+      <c r="A943" s="5" t="inlineStr">
         <is>
           <t>Christine Graham</t>
         </is>
       </c>
-      <c r="B943" s="2" t="inlineStr">
+      <c r="B943" s="5" t="inlineStr">
         <is>
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="C943" s="2" t="inlineStr">
+      <c r="C943" s="5" t="inlineStr">
         <is>
           <t>Lakeview Farms, LLC</t>
         </is>
@@ -16649,17 +16656,17 @@
       </c>
     </row>
     <row r="962">
-      <c r="A962" s="2" t="inlineStr">
+      <c r="A962" s="5" t="inlineStr">
         <is>
           <t>Paul Harris</t>
         </is>
       </c>
-      <c r="B962" s="2" t="inlineStr">
+      <c r="B962" s="5" t="inlineStr">
         <is>
           <t>Senior Director, SAP Basi...</t>
         </is>
       </c>
-      <c r="C962" s="2" t="inlineStr">
+      <c r="C962" s="5" t="inlineStr">
         <is>
           <t>Varsity Brands, LLC.</t>
         </is>
@@ -16853,17 +16860,17 @@
       </c>
     </row>
     <row r="974">
-      <c r="A974" s="2" t="inlineStr">
+      <c r="A974" s="5" t="inlineStr">
         <is>
           <t>Adriana Hernandez</t>
         </is>
       </c>
-      <c r="B974" s="2" t="inlineStr">
+      <c r="B974" s="5" t="inlineStr">
         <is>
           <t>Head Architecture</t>
         </is>
       </c>
-      <c r="C974" s="2" t="inlineStr">
+      <c r="C974" s="5" t="inlineStr">
         <is>
           <t>Bachoco, S.A. de C.V.</t>
         </is>
@@ -17355,17 +17362,17 @@
       </c>
     </row>
     <row r="1004">
-      <c r="A1004" s="2" t="inlineStr">
+      <c r="A1004" s="5" t="inlineStr">
         <is>
           <t>Omar Hussein Olmedo</t>
         </is>
       </c>
-      <c r="B1004" s="2" t="inlineStr">
+      <c r="B1004" s="5" t="inlineStr">
         <is>
           <t>Poject Manager</t>
         </is>
       </c>
-      <c r="C1004" s="2" t="inlineStr">
+      <c r="C1004" s="5" t="inlineStr">
         <is>
           <t>Bachoco, S.A. de C.V.</t>
         </is>
@@ -18231,13 +18238,13 @@
       </c>
     </row>
     <row r="1056">
-      <c r="A1056" s="2" t="inlineStr">
+      <c r="A1056" s="5" t="inlineStr">
         <is>
           <t>Kalman Gyula</t>
         </is>
       </c>
-      <c r="B1056" s="2" t="inlineStr"/>
-      <c r="C1056" s="2" t="inlineStr">
+      <c r="B1056" s="5" t="inlineStr"/>
+      <c r="C1056" s="5" t="inlineStr">
         <is>
           <t>BSN SPORTS, LLC f/k/n Sports Supply Group,…</t>
         </is>
@@ -18414,17 +18421,17 @@
       </c>
     </row>
     <row r="1067">
-      <c r="A1067" s="2" t="inlineStr">
+      <c r="A1067" s="5" t="inlineStr">
         <is>
           <t>Jeremy Freeman</t>
         </is>
       </c>
-      <c r="B1067" s="2" t="inlineStr">
+      <c r="B1067" s="5" t="inlineStr">
         <is>
           <t>Director, Technology</t>
         </is>
       </c>
-      <c r="C1067" s="2" t="inlineStr">
+      <c r="C1067" s="5" t="inlineStr">
         <is>
           <t>Aritzia</t>
         </is>
@@ -19009,17 +19016,17 @@
       </c>
     </row>
     <row r="1102">
-      <c r="A1102" s="2" t="inlineStr">
+      <c r="A1102" s="5" t="inlineStr">
         <is>
           <t>Susana Flores Cabrera</t>
         </is>
       </c>
-      <c r="B1102" s="2" t="inlineStr">
+      <c r="B1102" s="5" t="inlineStr">
         <is>
           <t>Contracts Coordinator</t>
         </is>
       </c>
-      <c r="C1102" s="2" t="inlineStr">
+      <c r="C1102" s="5" t="inlineStr">
         <is>
           <t>Cheney Bros, Inc.</t>
         </is>
@@ -19447,17 +19454,17 @@
       </c>
     </row>
     <row r="1128">
-      <c r="A1128" s="2" t="inlineStr">
+      <c r="A1128" s="5" t="inlineStr">
         <is>
           <t>Haricharan Dingari</t>
         </is>
       </c>
-      <c r="B1128" s="2" t="inlineStr">
+      <c r="B1128" s="5" t="inlineStr">
         <is>
           <t>Enterprise Arc…</t>
         </is>
       </c>
-      <c r="C1128" s="2" t="inlineStr">
+      <c r="C1128" s="5" t="inlineStr">
         <is>
           <t>Bob's Discount Furniture, LLC</t>
         </is>
@@ -19702,17 +19709,17 @@
       </c>
     </row>
     <row r="1143">
-      <c r="A1143" s="2" t="inlineStr">
+      <c r="A1143" s="5" t="inlineStr">
         <is>
           <t>Damodhar Dyava</t>
         </is>
       </c>
-      <c r="B1143" s="2" t="inlineStr">
+      <c r="B1143" s="5" t="inlineStr">
         <is>
           <t>SAP SD Manag…</t>
         </is>
       </c>
-      <c r="C1143" s="2" t="inlineStr">
+      <c r="C1143" s="5" t="inlineStr">
         <is>
           <t>Bob's Discount Furniture, LLC</t>
         </is>
